--- a/excel/ogrenciler.xlsx
+++ b/excel/ogrenciler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esad\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B56FF42-06D6-4DD3-AAF1-E7FF80F3B8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE38739-F43E-4F16-A269-15F31A93866A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E-SINAV " sheetId="182" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="346">
   <si>
     <t>E-SINAV</t>
   </si>
@@ -1069,6 +1069,12 @@
   </si>
   <si>
     <t>10,04</t>
+  </si>
+  <si>
+    <t>E SINAV HARCI</t>
+  </si>
+  <si>
+    <t>DİREKSİYON SINAV HARCI</t>
   </si>
 </sst>
 </file>
@@ -12743,618 +12749,714 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FAF04F-9884-43A0-9917-06CA88427D31}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" customWidth="1"/>
+    <col min="2" max="4" width="29.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="77" t="s">
         <v>321</v>
       </c>
       <c r="B1" s="78"/>
       <c r="C1" s="78"/>
       <c r="D1" s="78"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="79"/>
       <c r="B2" s="80"/>
       <c r="C2" s="80"/>
       <c r="D2" s="80"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
         <v>322</v>
       </c>
       <c r="B3" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>345</v>
+      </c>
+      <c r="E3" s="64" t="s">
         <v>323</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="F3" s="65" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="66">
         <v>1</v>
       </c>
       <c r="B4" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="68"/>
+      <c r="D4" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="D4" s="72">
+      <c r="E4" s="68"/>
+      <c r="F4" s="72">
         <v>46113</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="66">
         <v>2</v>
       </c>
       <c r="B5" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="68"/>
+      <c r="D5" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="D5" s="72">
+      <c r="E5" s="68"/>
+      <c r="F5" s="72">
         <v>46113</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="66">
         <v>3</v>
       </c>
       <c r="B6" s="67" t="s">
         <v>215</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="68"/>
+      <c r="D6" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="D6" s="72">
+      <c r="E6" s="68"/>
+      <c r="F6" s="72">
         <v>46117</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="66">
         <v>4</v>
       </c>
       <c r="B7" s="67" t="s">
         <v>262</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="68" t="s">
         <v>326</v>
       </c>
-      <c r="D7" s="72">
+      <c r="F7" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="66">
         <v>5</v>
       </c>
       <c r="B8" s="67" t="s">
         <v>327</v>
       </c>
-      <c r="C8" s="68" t="s">
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="68" t="s">
         <v>328</v>
       </c>
-      <c r="D8" s="72">
+      <c r="F8" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="66">
         <v>6</v>
       </c>
       <c r="B9" s="67" t="s">
         <v>329</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="68" t="s">
         <v>330</v>
       </c>
-      <c r="D9" s="72">
+      <c r="F9" s="72">
         <v>46118</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="66">
         <v>7</v>
       </c>
       <c r="B10" s="67" t="s">
         <v>331</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="68" t="s">
         <v>328</v>
       </c>
-      <c r="D10" s="72">
+      <c r="F10" s="72">
         <v>46118</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="66">
         <v>8</v>
       </c>
       <c r="B11" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="68" t="s">
         <v>330</v>
       </c>
-      <c r="D11" s="72">
+      <c r="F11" s="72">
         <v>46119</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="66">
         <v>9</v>
       </c>
       <c r="B12" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="68" t="s">
         <v>328</v>
       </c>
-      <c r="D12" s="72">
+      <c r="F12" s="72">
         <v>46118</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="66">
         <v>10</v>
       </c>
       <c r="B13" s="67" t="s">
         <v>334</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="68" t="s">
         <v>335</v>
       </c>
-      <c r="D13" s="72">
+      <c r="F13" s="72">
         <v>46119</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="66">
         <v>11</v>
       </c>
       <c r="B14" s="67" t="s">
         <v>336</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="68" t="s">
         <v>326</v>
       </c>
-      <c r="D14" s="72">
+      <c r="F14" s="72">
         <v>46119</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="66">
         <v>12</v>
       </c>
       <c r="B15" s="67" t="s">
         <v>337</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="68" t="s">
         <v>338</v>
       </c>
-      <c r="D15" s="72">
+      <c r="F15" s="72">
         <v>46118</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="66">
         <v>13</v>
       </c>
       <c r="B16" s="67" t="s">
         <v>229</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="67"/>
+      <c r="D16" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="D16" s="72">
+      <c r="E16" s="68"/>
+      <c r="F16" s="72">
         <v>46118</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="66">
         <v>14</v>
       </c>
       <c r="B17" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="68" t="s">
         <v>335</v>
       </c>
-      <c r="D17" s="72">
+      <c r="F17" s="72">
         <v>46118</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="66">
         <v>15</v>
       </c>
       <c r="B18" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="68" t="s">
         <v>330</v>
       </c>
-      <c r="D18" s="72">
+      <c r="F18" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="66">
         <v>16</v>
       </c>
       <c r="B19" s="67" t="s">
         <v>233</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="67"/>
+      <c r="D19" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="D19" s="72">
+      <c r="E19" s="68"/>
+      <c r="F19" s="72">
         <v>46120</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="66">
         <v>17</v>
       </c>
       <c r="B20" s="67" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="67"/>
+      <c r="D20" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="D20" s="72">
+      <c r="E20" s="68"/>
+      <c r="F20" s="72">
         <v>46120</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="66">
         <v>18</v>
       </c>
       <c r="B21" s="67" t="s">
         <v>186</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="67"/>
+      <c r="D21" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="D21" s="72">
+      <c r="E21" s="68"/>
+      <c r="F21" s="72">
         <v>46120</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="66">
         <v>19</v>
       </c>
       <c r="B22" s="67" t="s">
         <v>186</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="68" t="s">
         <v>335</v>
       </c>
-      <c r="D22" s="72">
+      <c r="F22" s="72">
         <v>46118</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="66">
         <v>20</v>
       </c>
       <c r="B23" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="67"/>
+      <c r="D23" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="D23" s="72">
+      <c r="E23" s="68"/>
+      <c r="F23" s="72">
         <v>46120</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="66">
         <v>21</v>
       </c>
       <c r="B24" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="67"/>
+      <c r="D24" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D24" s="72">
+      <c r="E24" s="68"/>
+      <c r="F24" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="66">
         <v>22</v>
       </c>
       <c r="B25" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="68" t="s">
+      <c r="C25" s="67"/>
+      <c r="D25" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D25" s="72">
+      <c r="E25" s="68"/>
+      <c r="F25" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="66">
         <v>23</v>
       </c>
       <c r="B26" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="67"/>
+      <c r="D26" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D26" s="72">
+      <c r="E26" s="68"/>
+      <c r="F26" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="66">
         <v>24</v>
       </c>
       <c r="B27" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="67"/>
+      <c r="D27" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D27" s="72">
+      <c r="E27" s="68"/>
+      <c r="F27" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="66">
         <v>25</v>
       </c>
       <c r="B28" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="67"/>
+      <c r="D28" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D28" s="72">
+      <c r="E28" s="68"/>
+      <c r="F28" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="66">
         <v>26</v>
       </c>
       <c r="B29" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="67"/>
+      <c r="D29" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D29" s="72">
+      <c r="E29" s="68"/>
+      <c r="F29" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="66">
         <v>27</v>
       </c>
       <c r="B30" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="67"/>
+      <c r="D30" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D30" s="72">
+      <c r="E30" s="68"/>
+      <c r="F30" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="66">
         <v>28</v>
       </c>
       <c r="B31" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="67"/>
+      <c r="D31" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D31" s="72">
+      <c r="E31" s="68"/>
+      <c r="F31" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="66">
         <v>29</v>
       </c>
       <c r="B32" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="67"/>
+      <c r="D32" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D32" s="72">
+      <c r="E32" s="68"/>
+      <c r="F32" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="66">
         <v>30</v>
       </c>
       <c r="B33" s="67" t="s">
         <v>189</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="67"/>
+      <c r="D33" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D33" s="72">
+      <c r="E33" s="68"/>
+      <c r="F33" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="66">
         <v>31</v>
       </c>
       <c r="B34" s="67" t="s">
         <v>191</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="67"/>
+      <c r="D34" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D34" s="72">
+      <c r="E34" s="68"/>
+      <c r="F34" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="66">
         <v>32</v>
       </c>
       <c r="B35" s="67" t="s">
         <v>193</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="67"/>
+      <c r="D35" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D35" s="72">
+      <c r="E35" s="68"/>
+      <c r="F35" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="66">
         <v>33</v>
       </c>
       <c r="B36" s="67" t="s">
         <v>195</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="67"/>
+      <c r="D36" s="68" t="s">
         <v>340</v>
       </c>
-      <c r="D36" s="72">
+      <c r="E36" s="68"/>
+      <c r="F36" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="66">
         <v>34</v>
       </c>
       <c r="B37" s="67" t="s">
         <v>196</v>
       </c>
-      <c r="C37" s="68" t="s">
+      <c r="C37" s="67"/>
+      <c r="D37" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D37" s="72">
+      <c r="E37" s="68"/>
+      <c r="F37" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="66">
         <v>35</v>
       </c>
       <c r="B38" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="C38" s="68" t="s">
+      <c r="C38" s="67"/>
+      <c r="D38" s="68" t="s">
         <v>339</v>
       </c>
-      <c r="D38" s="72">
+      <c r="E38" s="68"/>
+      <c r="F38" s="72">
         <v>46122</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="66">
         <v>36</v>
       </c>
       <c r="B39" s="67"/>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="D39" s="72"/>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F39" s="72"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="66">
         <v>37</v>
       </c>
       <c r="B40" s="67"/>
-      <c r="C40" s="68" t="s">
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="D40" s="72"/>
-    </row>
-    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F40" s="72"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="66">
         <v>38</v>
       </c>
       <c r="B41" s="67"/>
-      <c r="C41" s="68" t="s">
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="D41" s="72"/>
-    </row>
-    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F41" s="72"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="66">
         <v>39</v>
       </c>
       <c r="B42" s="67"/>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="D42" s="72"/>
-    </row>
-    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F42" s="72"/>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="66">
         <v>40</v>
       </c>
       <c r="B43" s="67"/>
-      <c r="C43" s="68" t="s">
+      <c r="C43" s="67"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="D43" s="72"/>
-    </row>
-    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F43" s="72"/>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="66">
         <v>41</v>
       </c>
       <c r="B44" s="67"/>
-      <c r="C44" s="68" t="s">
+      <c r="C44" s="67"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="D44" s="72"/>
-    </row>
-    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F44" s="72"/>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="66">
         <v>42</v>
       </c>
       <c r="B45" s="67"/>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="67"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="D45" s="72"/>
-    </row>
-    <row r="46" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F45" s="72"/>
+    </row>
+    <row r="46" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A46" s="66">
         <v>43</v>
       </c>
       <c r="B46" s="69"/>
-      <c r="C46" s="70" t="s">
+      <c r="C46" s="69"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="70" t="s">
         <v>342</v>
       </c>
-      <c r="D46" s="71">
+      <c r="F46" s="71">
         <v>213</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="A1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel/ogrenciler.xlsx
+++ b/excel/ogrenciler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esad\surucu-kursu-app\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F231C4D-A3A0-41B7-8F8A-89E95C888FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F13D8C-30A3-430A-B27B-D08691BF8B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E-SINAV " sheetId="182" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="352">
   <si>
     <t>E-SINAV</t>
   </si>
@@ -1629,9 +1629,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1694,6 +1691,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2025,16 +2025,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="69"/>
       <c r="I1" s="54"/>
       <c r="J1" s="54"/>
       <c r="K1" s="54"/>
@@ -2054,7 +2054,7 @@
       <c r="B2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="71" t="s">
+      <c r="C2" s="70" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="55" t="s">
@@ -2066,16 +2066,16 @@
       <c r="F2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="71" t="s">
+      <c r="G2" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="72" t="s">
+      <c r="H2" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="58" t="s">
+      <c r="J2" s="57" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="54"/>
@@ -2092,30 +2092,30 @@
       <c r="A3" s="55">
         <v>1</v>
       </c>
-      <c r="B3" s="73">
+      <c r="B3" s="72">
         <v>12847240198</v>
       </c>
       <c r="C3" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59" t="s">
+      <c r="D3" s="58"/>
+      <c r="E3" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="59"/>
-      <c r="G3" s="66" t="s">
+      <c r="F3" s="58"/>
+      <c r="G3" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="63" t="s">
+      <c r="H3" s="62" t="s">
         <v>323</v>
       </c>
-      <c r="I3" s="59">
+      <c r="I3" s="58">
         <v>9.0299999999999994</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K3" s="59"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="54"/>
       <c r="M3" s="54"/>
       <c r="N3" s="54"/>
@@ -2129,30 +2129,30 @@
       <c r="A4" s="55">
         <v>2</v>
       </c>
-      <c r="B4" s="73">
+      <c r="B4" s="72">
         <v>30265941886</v>
       </c>
       <c r="C4" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59" t="s">
+      <c r="D4" s="58"/>
+      <c r="E4" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="59"/>
-      <c r="G4" s="66" t="s">
+      <c r="F4" s="58"/>
+      <c r="G4" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="63" t="s">
+      <c r="H4" s="62" t="s">
         <v>324</v>
       </c>
-      <c r="I4" s="59">
+      <c r="I4" s="58">
         <v>19.02</v>
       </c>
-      <c r="J4" s="64">
+      <c r="J4" s="63">
         <v>0.75</v>
       </c>
-      <c r="K4" s="59"/>
+      <c r="K4" s="58"/>
       <c r="L4" s="54"/>
       <c r="M4" s="54"/>
       <c r="N4" s="54"/>
@@ -2166,26 +2166,26 @@
       <c r="A5" s="55">
         <v>3</v>
       </c>
-      <c r="B5" s="74">
+      <c r="B5" s="73">
         <v>22096643282</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59" t="s">
+      <c r="D5" s="58"/>
+      <c r="E5" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="65"/>
-      <c r="G5" s="76" t="s">
+      <c r="F5" s="64"/>
+      <c r="G5" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="63" t="s">
+      <c r="H5" s="62" t="s">
         <v>325</v>
       </c>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="74" t="s">
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="73" t="s">
         <v>326</v>
       </c>
       <c r="L5" s="54"/>
@@ -2201,30 +2201,30 @@
       <c r="A6" s="55">
         <v>4</v>
       </c>
-      <c r="B6" s="65">
+      <c r="B6" s="64">
         <v>11110087492</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="77" t="s">
+      <c r="D6" s="58"/>
+      <c r="E6" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="60"/>
-      <c r="G6" s="66" t="s">
+      <c r="F6" s="59"/>
+      <c r="G6" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="63" t="s">
+      <c r="H6" s="62" t="s">
         <v>327</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="58">
         <v>14.04</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K6" s="59"/>
+      <c r="K6" s="58"/>
       <c r="L6" s="54"/>
       <c r="M6" s="54"/>
       <c r="N6" s="54"/>
@@ -2238,30 +2238,30 @@
       <c r="A7" s="55">
         <v>5</v>
       </c>
-      <c r="B7" s="65">
+      <c r="B7" s="64">
         <v>18115063162</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="59"/>
-      <c r="E7" s="77" t="s">
+      <c r="D7" s="58"/>
+      <c r="E7" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="65"/>
-      <c r="G7" s="66" t="s">
+      <c r="F7" s="64"/>
+      <c r="G7" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="63" t="s">
+      <c r="H7" s="62" t="s">
         <v>328</v>
       </c>
-      <c r="I7" s="59">
+      <c r="I7" s="58">
         <v>14.04</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K7" s="59"/>
+      <c r="K7" s="58"/>
       <c r="L7" s="54"/>
       <c r="M7" s="54"/>
       <c r="N7" s="54"/>
@@ -2275,30 +2275,30 @@
       <c r="A8" s="55">
         <v>6</v>
       </c>
-      <c r="B8" s="73">
+      <c r="B8" s="72">
         <v>14314192016</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59" t="s">
+      <c r="D8" s="58"/>
+      <c r="E8" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="59"/>
-      <c r="G8" s="66" t="s">
+      <c r="F8" s="58"/>
+      <c r="G8" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="63" t="s">
+      <c r="H8" s="62" t="s">
         <v>329</v>
       </c>
-      <c r="I8" s="59">
+      <c r="I8" s="58">
         <v>3.04</v>
       </c>
-      <c r="J8" s="64">
+      <c r="J8" s="63">
         <v>0.75</v>
       </c>
-      <c r="K8" s="59"/>
+      <c r="K8" s="58"/>
       <c r="L8" s="54"/>
       <c r="M8" s="54"/>
       <c r="N8" s="54"/>
@@ -2312,30 +2312,30 @@
       <c r="A9" s="55">
         <v>7</v>
       </c>
-      <c r="B9" s="73">
+      <c r="B9" s="72">
         <v>99144164198</v>
       </c>
       <c r="C9" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59" t="s">
+      <c r="D9" s="58"/>
+      <c r="E9" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="59"/>
-      <c r="G9" s="66" t="s">
+      <c r="F9" s="58"/>
+      <c r="G9" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="63" t="s">
+      <c r="H9" s="62" t="s">
         <v>330</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="58">
         <v>26.03</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K9" s="59"/>
+      <c r="K9" s="58"/>
       <c r="L9" s="54"/>
       <c r="M9" s="54"/>
       <c r="N9" s="54"/>
@@ -2349,26 +2349,26 @@
       <c r="A10" s="55">
         <v>8</v>
       </c>
-      <c r="B10" s="74">
+      <c r="B10" s="73">
         <v>32632300470</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59" t="s">
+      <c r="D10" s="58"/>
+      <c r="E10" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="60"/>
-      <c r="G10" s="66" t="s">
+      <c r="F10" s="59"/>
+      <c r="G10" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="63" t="s">
+      <c r="H10" s="62" t="s">
         <v>331</v>
       </c>
-      <c r="I10" s="59"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="74" t="s">
+      <c r="I10" s="58"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73" t="s">
         <v>332</v>
       </c>
       <c r="L10" s="54"/>
@@ -2384,30 +2384,30 @@
       <c r="A11" s="55">
         <v>9</v>
       </c>
-      <c r="B11" s="65">
+      <c r="B11" s="64">
         <v>10813947058</v>
       </c>
       <c r="C11" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="77" t="s">
+      <c r="D11" s="58"/>
+      <c r="E11" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="65"/>
-      <c r="G11" s="66" t="s">
+      <c r="F11" s="64"/>
+      <c r="G11" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="63" t="s">
+      <c r="H11" s="62" t="s">
         <v>333</v>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="58">
         <v>14.04</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K11" s="59"/>
+      <c r="K11" s="58"/>
       <c r="L11" s="54"/>
       <c r="M11" s="54"/>
       <c r="N11" s="54"/>
@@ -2421,26 +2421,26 @@
       <c r="A12" s="55">
         <v>10</v>
       </c>
-      <c r="B12" s="74">
+      <c r="B12" s="73">
         <v>10078164894</v>
       </c>
-      <c r="C12" s="78" t="s">
+      <c r="C12" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59" t="s">
+      <c r="D12" s="58"/>
+      <c r="E12" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="59"/>
-      <c r="G12" s="66" t="s">
+      <c r="F12" s="58"/>
+      <c r="G12" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="63" t="s">
+      <c r="H12" s="62" t="s">
         <v>334</v>
       </c>
-      <c r="I12" s="59"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="60" t="s">
+      <c r="I12" s="58"/>
+      <c r="J12" s="58"/>
+      <c r="K12" s="59" t="s">
         <v>335</v>
       </c>
       <c r="L12" s="54"/>
@@ -2456,26 +2456,26 @@
       <c r="A13" s="55">
         <v>11</v>
       </c>
-      <c r="B13" s="74">
+      <c r="B13" s="73">
         <v>12419592328</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="58"/>
+      <c r="E13" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="66" t="s">
+      <c r="F13" s="58"/>
+      <c r="G13" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="63" t="s">
+      <c r="H13" s="62" t="s">
         <v>336</v>
       </c>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="59"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
       <c r="L13" s="54"/>
       <c r="M13" s="54"/>
       <c r="N13" s="54"/>
@@ -2489,26 +2489,26 @@
       <c r="A14" s="55">
         <v>12</v>
       </c>
-      <c r="B14" s="74">
+      <c r="B14" s="73">
         <v>39115862296</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59" t="s">
+      <c r="D14" s="58"/>
+      <c r="E14" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="66" t="s">
+      <c r="F14" s="58"/>
+      <c r="G14" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="63" t="s">
+      <c r="H14" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="58"/>
       <c r="L14" s="54"/>
       <c r="M14" s="54"/>
       <c r="N14" s="54"/>
@@ -2526,7 +2526,7 @@
       <c r="E15" s="54"/>
       <c r="F15" s="54"/>
       <c r="G15" s="28"/>
-      <c r="H15" s="70"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="54"/>
       <c r="J15" s="54"/>
       <c r="K15" s="54"/>
@@ -2540,29 +2540,29 @@
       <c r="S15" s="54"/>
     </row>
     <row r="16" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="59">
+      <c r="A16" s="58">
         <v>1</v>
       </c>
-      <c r="B16" s="59">
+      <c r="B16" s="58">
         <v>49627120258</v>
       </c>
       <c r="C16" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59" t="s">
+      <c r="D16" s="58"/>
+      <c r="E16" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="66" t="s">
+      <c r="F16" s="64"/>
+      <c r="G16" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>338</v>
       </c>
-      <c r="I16" s="59"/>
-      <c r="J16" s="59"/>
-      <c r="K16" s="59"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
       <c r="L16" s="54"/>
       <c r="M16" s="54"/>
       <c r="N16" s="54"/>
@@ -2573,29 +2573,29 @@
       <c r="S16" s="54"/>
     </row>
     <row r="17" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="59">
+      <c r="A17" s="58">
         <v>2</v>
       </c>
-      <c r="B17" s="59">
+      <c r="B17" s="58">
         <v>14038775274</v>
       </c>
-      <c r="C17" s="78" t="s">
+      <c r="C17" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59" t="s">
+      <c r="D17" s="58"/>
+      <c r="E17" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="59"/>
-      <c r="G17" s="66" t="s">
+      <c r="F17" s="58"/>
+      <c r="G17" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="63" t="s">
+      <c r="H17" s="62" t="s">
         <v>339</v>
       </c>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="60" t="s">
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="59" t="s">
         <v>335</v>
       </c>
       <c r="L17" s="54"/>
@@ -2608,29 +2608,29 @@
       <c r="S17" s="54"/>
     </row>
     <row r="18" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="59">
+      <c r="A18" s="58">
         <v>3</v>
       </c>
-      <c r="B18" s="59">
+      <c r="B18" s="58">
         <v>14527184440</v>
       </c>
       <c r="C18" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59" t="s">
+      <c r="D18" s="58"/>
+      <c r="E18" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="59"/>
-      <c r="G18" s="66" t="s">
+      <c r="F18" s="58"/>
+      <c r="G18" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="63" t="s">
+      <c r="H18" s="62" t="s">
         <v>340</v>
       </c>
-      <c r="I18" s="59"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="59"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
       <c r="L18" s="54"/>
       <c r="M18" s="54"/>
       <c r="N18" s="54"/>
@@ -2641,29 +2641,29 @@
       <c r="S18" s="54"/>
     </row>
     <row r="19" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="59">
+      <c r="A19" s="58">
         <v>4</v>
       </c>
-      <c r="B19" s="59">
+      <c r="B19" s="58">
         <v>10312320574</v>
       </c>
-      <c r="C19" s="78" t="s">
+      <c r="C19" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59" t="s">
+      <c r="D19" s="58"/>
+      <c r="E19" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="59"/>
-      <c r="G19" s="66" t="s">
+      <c r="F19" s="58"/>
+      <c r="G19" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="63" t="s">
+      <c r="H19" s="62" t="s">
         <v>341</v>
       </c>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="60" t="s">
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="59" t="s">
         <v>342</v>
       </c>
       <c r="L19" s="54"/>
@@ -2676,29 +2676,29 @@
       <c r="S19" s="54"/>
     </row>
     <row r="20" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="59">
+      <c r="A20" s="58">
         <v>5</v>
       </c>
-      <c r="B20" s="59">
+      <c r="B20" s="58">
         <v>13351060166</v>
       </c>
-      <c r="C20" s="78" t="s">
+      <c r="C20" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59" t="s">
+      <c r="D20" s="58"/>
+      <c r="E20" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="59"/>
-      <c r="G20" s="66" t="s">
+      <c r="F20" s="58"/>
+      <c r="G20" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="63" t="s">
+      <c r="H20" s="62" t="s">
         <v>343</v>
       </c>
-      <c r="I20" s="59"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="60" t="s">
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="59" t="s">
         <v>335</v>
       </c>
       <c r="L20" s="54"/>
@@ -2711,29 +2711,29 @@
       <c r="S20" s="54"/>
     </row>
     <row r="21" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="59">
+      <c r="A21" s="58">
         <v>6</v>
       </c>
-      <c r="B21" s="59">
+      <c r="B21" s="58">
         <v>13939204012</v>
       </c>
       <c r="C21" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59" t="s">
+      <c r="D21" s="58"/>
+      <c r="E21" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="59"/>
-      <c r="G21" s="66" t="s">
+      <c r="F21" s="58"/>
+      <c r="G21" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="H21" s="63" t="s">
+      <c r="H21" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="I21" s="59"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
       <c r="L21" s="54"/>
       <c r="M21" s="54"/>
       <c r="N21" s="54"/>
@@ -2744,29 +2744,29 @@
       <c r="S21" s="54"/>
     </row>
     <row r="22" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="59">
+      <c r="A22" s="58">
         <v>7</v>
       </c>
-      <c r="B22" s="59">
+      <c r="B22" s="58">
         <v>10042247202</v>
       </c>
-      <c r="C22" s="78" t="s">
+      <c r="C22" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59" t="s">
+      <c r="D22" s="58"/>
+      <c r="E22" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="59"/>
-      <c r="G22" s="66" t="s">
+      <c r="F22" s="58"/>
+      <c r="G22" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="63" t="s">
+      <c r="H22" s="62" t="s">
         <v>345</v>
       </c>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="60" t="s">
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="59" t="s">
         <v>335</v>
       </c>
       <c r="L22" s="54"/>
@@ -2779,29 +2779,29 @@
       <c r="S22" s="54"/>
     </row>
     <row r="23" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="59">
+      <c r="A23" s="58">
         <v>8</v>
       </c>
-      <c r="B23" s="59">
+      <c r="B23" s="58">
         <v>11209295852</v>
       </c>
       <c r="C23" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59" t="s">
+      <c r="D23" s="58"/>
+      <c r="E23" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="59"/>
-      <c r="G23" s="66" t="s">
+      <c r="F23" s="58"/>
+      <c r="G23" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="H23" s="63" t="s">
+      <c r="H23" s="62" t="s">
         <v>346</v>
       </c>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
       <c r="L23" s="54"/>
       <c r="M23" s="54"/>
       <c r="N23" s="54"/>
@@ -2812,29 +2812,29 @@
       <c r="S23" s="54"/>
     </row>
     <row r="24" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="59">
+      <c r="A24" s="58">
         <v>9</v>
       </c>
-      <c r="B24" s="59">
+      <c r="B24" s="58">
         <v>10042247370</v>
       </c>
-      <c r="C24" s="78" t="s">
+      <c r="C24" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59" t="s">
+      <c r="D24" s="58"/>
+      <c r="E24" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="59"/>
-      <c r="G24" s="66" t="s">
+      <c r="F24" s="58"/>
+      <c r="G24" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="H24" s="63" t="s">
+      <c r="H24" s="62" t="s">
         <v>347</v>
       </c>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="60" t="s">
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="59" t="s">
         <v>335</v>
       </c>
       <c r="L24" s="54"/>
@@ -2847,29 +2847,29 @@
       <c r="S24" s="54"/>
     </row>
     <row r="25" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="59">
+      <c r="A25" s="58">
         <v>10</v>
       </c>
-      <c r="B25" s="59">
+      <c r="B25" s="58">
         <v>10242156304</v>
       </c>
       <c r="C25" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59" t="s">
+      <c r="D25" s="58"/>
+      <c r="E25" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="65"/>
-      <c r="G25" s="66" t="s">
+      <c r="F25" s="64"/>
+      <c r="G25" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="63" t="s">
+      <c r="H25" s="62" t="s">
         <v>348</v>
       </c>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
       <c r="L25" s="54"/>
       <c r="M25" s="54"/>
       <c r="N25" s="54"/>
@@ -2880,29 +2880,29 @@
       <c r="S25" s="54"/>
     </row>
     <row r="26" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="59">
+      <c r="A26" s="58">
         <v>11</v>
       </c>
-      <c r="B26" s="59">
+      <c r="B26" s="58">
         <v>10688046160</v>
       </c>
       <c r="C26" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59" t="s">
+      <c r="D26" s="58"/>
+      <c r="E26" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="59"/>
-      <c r="G26" s="66" t="s">
+      <c r="F26" s="58"/>
+      <c r="G26" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="H26" s="63" t="s">
+      <c r="H26" s="62" t="s">
         <v>349</v>
       </c>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
       <c r="L26" s="54"/>
       <c r="M26" s="54"/>
       <c r="N26" s="54"/>
@@ -2913,29 +2913,29 @@
       <c r="S26" s="54"/>
     </row>
     <row r="27" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59">
+      <c r="A27" s="58">
         <v>12</v>
       </c>
-      <c r="B27" s="59">
+      <c r="B27" s="58">
         <v>10051120886</v>
       </c>
       <c r="C27" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59" t="s">
+      <c r="D27" s="58"/>
+      <c r="E27" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="59"/>
-      <c r="G27" s="66" t="s">
+      <c r="F27" s="58"/>
+      <c r="G27" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="H27" s="63" t="s">
+      <c r="H27" s="62" t="s">
         <v>350</v>
       </c>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="58"/>
       <c r="L27" s="54"/>
       <c r="M27" s="54"/>
       <c r="N27" s="54"/>
@@ -2946,29 +2946,29 @@
       <c r="S27" s="54"/>
     </row>
     <row r="28" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="59">
+      <c r="A28" s="58">
         <v>13</v>
       </c>
-      <c r="B28" s="59">
+      <c r="B28" s="58">
         <v>38486042184</v>
       </c>
       <c r="C28" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59" t="s">
+      <c r="D28" s="58"/>
+      <c r="E28" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="59"/>
-      <c r="G28" s="66" t="s">
+      <c r="F28" s="58"/>
+      <c r="G28" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="H28" s="63" t="s">
+      <c r="H28" s="62" t="s">
         <v>351</v>
       </c>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
       <c r="L28" s="54"/>
       <c r="M28" s="54"/>
       <c r="N28" s="54"/>
@@ -3008,14 +3008,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="69"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
       <c r="G1" s="52"/>
       <c r="H1" s="53"/>
       <c r="I1" s="54"/>
@@ -3040,1531 +3040,1533 @@
         <v>6</v>
       </c>
       <c r="G2" s="56"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="H2" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
       <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59">
+      <c r="A3" s="58">
         <v>1</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="59">
         <v>12961026456</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59" t="s">
+      <c r="D3" s="58"/>
+      <c r="E3" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="59"/>
-      <c r="G3" s="62" t="s">
+      <c r="F3" s="58"/>
+      <c r="G3" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="63" t="s">
+      <c r="H3" s="62" t="s">
         <v>247</v>
       </c>
-      <c r="I3" s="59">
+      <c r="I3" s="58">
         <v>8.01</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K3" s="59"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="59">
+      <c r="A4" s="58">
         <v>2</v>
       </c>
-      <c r="B4" s="60">
+      <c r="B4" s="59">
         <v>14254194606</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59" t="s">
+      <c r="D4" s="58"/>
+      <c r="E4" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="65"/>
-      <c r="G4" s="66" t="s">
+      <c r="F4" s="64"/>
+      <c r="G4" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="63" t="s">
+      <c r="H4" s="62" t="s">
         <v>248</v>
       </c>
-      <c r="I4" s="59">
+      <c r="I4" s="58">
         <v>28.01</v>
       </c>
-      <c r="J4" s="64">
+      <c r="J4" s="63">
         <v>0.75</v>
       </c>
-      <c r="K4" s="59"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="59">
+      <c r="A5" s="58">
         <v>3</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="59">
         <v>10306113588</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59" t="s">
+      <c r="D5" s="58"/>
+      <c r="E5" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="65"/>
-      <c r="G5" s="66" t="s">
+      <c r="F5" s="64"/>
+      <c r="G5" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="63" t="s">
+      <c r="H5" s="62" t="s">
         <v>249</v>
       </c>
-      <c r="I5" s="59">
+      <c r="I5" s="58">
         <v>5.0199999999999996</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K5" s="59"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59">
+      <c r="A6" s="58">
         <v>4</v>
       </c>
-      <c r="B6" s="60">
+      <c r="B6" s="59">
         <v>12787254972</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59" t="s">
+      <c r="D6" s="58"/>
+      <c r="E6" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="59"/>
-      <c r="G6" s="66" t="s">
+      <c r="F6" s="58"/>
+      <c r="G6" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="63" t="s">
+      <c r="H6" s="62" t="s">
         <v>250</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="58">
         <v>18.02</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="63">
         <v>0.75</v>
       </c>
-      <c r="K6" s="59"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="59">
+      <c r="A7" s="58">
         <v>5</v>
       </c>
-      <c r="B7" s="60">
+      <c r="B7" s="59">
         <v>11374289342</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59" t="s">
+      <c r="D7" s="58"/>
+      <c r="E7" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="65"/>
-      <c r="G7" s="66" t="s">
+      <c r="F7" s="64"/>
+      <c r="G7" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="63" t="s">
+      <c r="H7" s="62" t="s">
         <v>251</v>
       </c>
-      <c r="I7" s="59">
+      <c r="I7" s="58">
         <v>18.02</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="63">
         <v>0.75</v>
       </c>
-      <c r="K7" s="59"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="59">
+      <c r="A8" s="58">
         <v>6</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="59">
         <v>19702011528</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59" t="s">
+      <c r="D8" s="58"/>
+      <c r="E8" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="65"/>
-      <c r="G8" s="66" t="s">
+      <c r="F8" s="64"/>
+      <c r="G8" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="63" t="s">
+      <c r="H8" s="62" t="s">
         <v>252</v>
       </c>
-      <c r="I8" s="59">
+      <c r="I8" s="58">
         <v>18.02</v>
       </c>
-      <c r="J8" s="64">
+      <c r="J8" s="63">
         <v>0.75</v>
       </c>
-      <c r="K8" s="59"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="59">
+      <c r="A9" s="58">
         <v>7</v>
       </c>
-      <c r="B9" s="60">
+      <c r="B9" s="59">
         <v>14299193176</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59" t="s">
+      <c r="D9" s="58"/>
+      <c r="E9" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="59"/>
-      <c r="G9" s="66" t="s">
+      <c r="F9" s="58"/>
+      <c r="G9" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="63" t="s">
+      <c r="H9" s="62" t="s">
         <v>253</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="58">
         <v>19.02</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K9" s="59"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="59">
+      <c r="A10" s="58">
         <v>8</v>
       </c>
-      <c r="B10" s="60">
+      <c r="B10" s="59">
         <v>10039248120</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59" t="s">
+      <c r="D10" s="58"/>
+      <c r="E10" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="59"/>
-      <c r="G10" s="66" t="s">
+      <c r="F10" s="58"/>
+      <c r="G10" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="H10" s="63" t="s">
+      <c r="H10" s="62" t="s">
         <v>254</v>
       </c>
-      <c r="I10" s="59">
+      <c r="I10" s="58">
         <v>23.02</v>
       </c>
-      <c r="J10" s="64">
+      <c r="J10" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K10" s="59"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="59">
+      <c r="A11" s="58">
         <v>9</v>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="59">
         <v>11323292362</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="58"/>
+      <c r="E11" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="59"/>
-      <c r="G11" s="66" t="s">
+      <c r="F11" s="58"/>
+      <c r="G11" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H11" s="63" t="s">
+      <c r="H11" s="62" t="s">
         <v>255</v>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="58">
         <v>23.02</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K11" s="59"/>
+      <c r="K11" s="58"/>
     </row>
     <row r="12" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="59">
+      <c r="A12" s="58">
         <v>10</v>
       </c>
-      <c r="B12" s="60">
+      <c r="B12" s="59">
         <v>10147121568</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59" t="s">
+      <c r="D12" s="58"/>
+      <c r="E12" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="65"/>
-      <c r="G12" s="66" t="s">
+      <c r="F12" s="64"/>
+      <c r="G12" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="H12" s="63" t="s">
+      <c r="H12" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="I12" s="59">
+      <c r="I12" s="58">
         <v>23.02</v>
       </c>
-      <c r="J12" s="64">
+      <c r="J12" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K12" s="59"/>
+      <c r="K12" s="58"/>
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="59">
+      <c r="A13" s="58">
         <v>11</v>
       </c>
-      <c r="B13" s="60">
+      <c r="B13" s="59">
         <v>33668101604</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="58"/>
+      <c r="E13" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="65"/>
-      <c r="G13" s="66" t="s">
+      <c r="F13" s="64"/>
+      <c r="G13" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="63" t="s">
+      <c r="H13" s="62" t="s">
         <v>257</v>
       </c>
-      <c r="I13" s="59">
+      <c r="I13" s="58">
         <v>23.02</v>
       </c>
-      <c r="J13" s="64">
+      <c r="J13" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K13" s="59"/>
+      <c r="K13" s="58"/>
     </row>
     <row r="14" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="59">
+      <c r="A14" s="58">
         <v>12</v>
       </c>
-      <c r="B14" s="60">
+      <c r="B14" s="59">
         <v>11867067624</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59" t="s">
+      <c r="D14" s="58"/>
+      <c r="E14" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="65"/>
-      <c r="G14" s="66" t="s">
+      <c r="F14" s="64"/>
+      <c r="G14" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="63" t="s">
+      <c r="H14" s="62" t="s">
         <v>258</v>
       </c>
-      <c r="I14" s="59">
+      <c r="I14" s="58">
         <v>23.02</v>
       </c>
-      <c r="J14" s="64">
+      <c r="J14" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K14" s="59"/>
+      <c r="K14" s="58"/>
     </row>
     <row r="15" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="59">
+      <c r="A15" s="58">
         <v>13</v>
       </c>
-      <c r="B15" s="60">
+      <c r="B15" s="59">
         <v>10031847734</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59" t="s">
+      <c r="D15" s="58"/>
+      <c r="E15" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="66" t="s">
+      <c r="F15" s="58"/>
+      <c r="G15" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="63" t="s">
+      <c r="H15" s="62" t="s">
         <v>259</v>
       </c>
-      <c r="I15" s="59">
+      <c r="I15" s="58">
         <v>23.02</v>
       </c>
-      <c r="J15" s="64">
+      <c r="J15" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K15" s="59"/>
+      <c r="K15" s="58"/>
     </row>
     <row r="16" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="59">
+      <c r="A16" s="58">
         <v>14</v>
       </c>
-      <c r="B16" s="60">
+      <c r="B16" s="59">
         <v>12985235612</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59" t="s">
+      <c r="D16" s="58"/>
+      <c r="E16" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="59"/>
-      <c r="G16" s="66" t="s">
+      <c r="F16" s="58"/>
+      <c r="G16" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>260</v>
       </c>
-      <c r="I16" s="59">
+      <c r="I16" s="58">
         <v>23.02</v>
       </c>
-      <c r="J16" s="64">
+      <c r="J16" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K16" s="59"/>
+      <c r="K16" s="58"/>
     </row>
     <row r="17" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="59">
+      <c r="A17" s="58">
         <v>15</v>
       </c>
-      <c r="B17" s="60">
+      <c r="B17" s="59">
         <v>14791267894</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59" t="s">
+      <c r="D17" s="58"/>
+      <c r="E17" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="59"/>
-      <c r="G17" s="66" t="s">
+      <c r="F17" s="58"/>
+      <c r="G17" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="63" t="s">
+      <c r="H17" s="62" t="s">
         <v>261</v>
       </c>
-      <c r="I17" s="59">
+      <c r="I17" s="58">
         <v>25.02</v>
       </c>
-      <c r="J17" s="64">
+      <c r="J17" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K17" s="59"/>
+      <c r="K17" s="58"/>
     </row>
     <row r="18" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="59">
+      <c r="A18" s="58">
         <v>16</v>
       </c>
-      <c r="B18" s="60">
+      <c r="B18" s="59">
         <v>26996448794</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="60" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59" t="s">
+      <c r="D18" s="58"/>
+      <c r="E18" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="66" t="s">
+      <c r="F18" s="64"/>
+      <c r="G18" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="H18" s="63" t="s">
+      <c r="H18" s="62" t="s">
         <v>262</v>
       </c>
-      <c r="I18" s="59"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="59"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
     </row>
     <row r="19" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="59">
+      <c r="A19" s="58">
         <v>17</v>
       </c>
-      <c r="B19" s="60">
+      <c r="B19" s="59">
         <v>34198316858</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59" t="s">
+      <c r="D19" s="58"/>
+      <c r="E19" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="59"/>
-      <c r="G19" s="66" t="s">
+      <c r="F19" s="58"/>
+      <c r="G19" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="H19" s="63" t="s">
+      <c r="H19" s="62" t="s">
         <v>263</v>
       </c>
-      <c r="I19" s="59">
+      <c r="I19" s="58">
         <v>11.03</v>
       </c>
-      <c r="J19" s="64">
+      <c r="J19" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K19" s="59"/>
+      <c r="K19" s="58"/>
     </row>
     <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="59">
+      <c r="A20" s="58">
         <v>18</v>
       </c>
-      <c r="B20" s="60">
+      <c r="B20" s="59">
         <v>16261043632</v>
       </c>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59" t="s">
+      <c r="D20" s="58"/>
+      <c r="E20" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="65"/>
-      <c r="G20" s="66" t="s">
+      <c r="F20" s="64"/>
+      <c r="G20" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="H20" s="63" t="s">
+      <c r="H20" s="62" t="s">
         <v>264</v>
       </c>
-      <c r="I20" s="59">
+      <c r="I20" s="58">
         <v>23.03</v>
       </c>
-      <c r="J20" s="64">
+      <c r="J20" s="63">
         <v>0.75</v>
       </c>
-      <c r="K20" s="59"/>
+      <c r="K20" s="58"/>
     </row>
     <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="59">
+      <c r="A21" s="58">
         <v>19</v>
       </c>
-      <c r="B21" s="60">
+      <c r="B21" s="59">
         <v>62251054904</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59" t="s">
+      <c r="D21" s="58"/>
+      <c r="E21" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="65"/>
-      <c r="G21" s="66" t="s">
+      <c r="F21" s="64"/>
+      <c r="G21" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="63" t="s">
+      <c r="H21" s="62" t="s">
         <v>265</v>
       </c>
-      <c r="I21" s="59">
+      <c r="I21" s="58">
         <v>23.03</v>
       </c>
-      <c r="J21" s="64">
+      <c r="J21" s="63">
         <v>0.75</v>
       </c>
-      <c r="K21" s="59"/>
+      <c r="K21" s="58"/>
     </row>
     <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="59">
+      <c r="A22" s="58">
         <v>20</v>
       </c>
-      <c r="B22" s="60">
+      <c r="B22" s="59">
         <v>10162209012</v>
       </c>
-      <c r="C22" s="61" t="s">
+      <c r="C22" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59" t="s">
+      <c r="D22" s="58"/>
+      <c r="E22" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="59"/>
-      <c r="G22" s="66" t="s">
+      <c r="F22" s="58"/>
+      <c r="G22" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="H22" s="63" t="s">
+      <c r="H22" s="62" t="s">
         <v>266</v>
       </c>
-      <c r="I22" s="59">
+      <c r="I22" s="58">
         <v>23.03</v>
       </c>
-      <c r="J22" s="64">
+      <c r="J22" s="63">
         <v>0.75</v>
       </c>
-      <c r="K22" s="59"/>
+      <c r="K22" s="58"/>
     </row>
     <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="59">
+      <c r="A23" s="58">
         <v>21</v>
       </c>
-      <c r="B23" s="60">
+      <c r="B23" s="59">
         <v>15247077586</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59" t="s">
+      <c r="D23" s="58"/>
+      <c r="E23" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="65"/>
-      <c r="G23" s="66" t="s">
+      <c r="F23" s="64"/>
+      <c r="G23" s="65" t="s">
         <v>103</v>
       </c>
-      <c r="H23" s="63" t="s">
+      <c r="H23" s="62" t="s">
         <v>267</v>
       </c>
-      <c r="I23" s="59">
+      <c r="I23" s="58">
         <v>23.03</v>
       </c>
-      <c r="J23" s="64">
+      <c r="J23" s="63">
         <v>0.75</v>
       </c>
-      <c r="K23" s="59"/>
+      <c r="K23" s="58"/>
     </row>
     <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="59">
+      <c r="A24" s="58">
         <v>22</v>
       </c>
-      <c r="B24" s="60">
+      <c r="B24" s="59">
         <v>12484081840</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59" t="s">
+      <c r="D24" s="58"/>
+      <c r="E24" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="65"/>
-      <c r="G24" s="66" t="s">
+      <c r="F24" s="64"/>
+      <c r="G24" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="H24" s="63" t="s">
+      <c r="H24" s="62" t="s">
         <v>268</v>
       </c>
-      <c r="I24" s="59">
+      <c r="I24" s="58">
         <v>23.03</v>
       </c>
-      <c r="J24" s="64">
+      <c r="J24" s="63">
         <v>0.75</v>
       </c>
-      <c r="K24" s="59"/>
+      <c r="K24" s="58"/>
     </row>
     <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="59">
+      <c r="A25" s="58">
         <v>23</v>
       </c>
-      <c r="B25" s="60">
+      <c r="B25" s="59">
         <v>11749111162</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59" t="s">
+      <c r="D25" s="58"/>
+      <c r="E25" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="65"/>
-      <c r="G25" s="66" t="s">
+      <c r="F25" s="64"/>
+      <c r="G25" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="H25" s="63" t="s">
+      <c r="H25" s="62" t="s">
         <v>269</v>
       </c>
-      <c r="I25" s="59">
+      <c r="I25" s="58">
         <v>23.03</v>
       </c>
-      <c r="J25" s="64">
+      <c r="J25" s="63">
         <v>0.75</v>
       </c>
-      <c r="K25" s="59"/>
+      <c r="K25" s="58"/>
     </row>
     <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="59">
+      <c r="A26" s="58">
         <v>24</v>
       </c>
-      <c r="B26" s="60">
+      <c r="B26" s="59">
         <v>10078077392</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59" t="s">
+      <c r="D26" s="58"/>
+      <c r="E26" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="65"/>
-      <c r="G26" s="66" t="s">
+      <c r="F26" s="64"/>
+      <c r="G26" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="H26" s="63" t="s">
+      <c r="H26" s="62" t="s">
         <v>270</v>
       </c>
-      <c r="I26" s="59">
+      <c r="I26" s="58">
         <v>23.03</v>
       </c>
-      <c r="J26" s="64">
+      <c r="J26" s="63">
         <v>0.75</v>
       </c>
-      <c r="K26" s="59"/>
+      <c r="K26" s="58"/>
     </row>
     <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59">
+      <c r="A27" s="58">
         <v>25</v>
       </c>
-      <c r="B27" s="60">
+      <c r="B27" s="59">
         <v>10156079256</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59" t="s">
+      <c r="D27" s="58"/>
+      <c r="E27" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="65"/>
-      <c r="G27" s="66" t="s">
+      <c r="F27" s="64"/>
+      <c r="G27" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="H27" s="63" t="s">
+      <c r="H27" s="62" t="s">
         <v>271</v>
       </c>
-      <c r="I27" s="59">
+      <c r="I27" s="58">
         <v>24.03</v>
       </c>
-      <c r="J27" s="64">
+      <c r="J27" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K27" s="59"/>
+      <c r="K27" s="58"/>
     </row>
     <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="59">
+      <c r="A28" s="58">
         <v>26</v>
       </c>
-      <c r="B28" s="60">
+      <c r="B28" s="59">
         <v>49288319060</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59" t="s">
+      <c r="D28" s="58"/>
+      <c r="E28" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="65"/>
-      <c r="G28" s="66" t="s">
+      <c r="F28" s="64"/>
+      <c r="G28" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="H28" s="63" t="s">
+      <c r="H28" s="62" t="s">
         <v>272</v>
       </c>
-      <c r="I28" s="59">
+      <c r="I28" s="58">
         <v>25.03</v>
       </c>
-      <c r="J28" s="64">
+      <c r="J28" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K28" s="59"/>
+      <c r="K28" s="58"/>
     </row>
     <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="59">
+      <c r="A29" s="58">
         <v>27</v>
       </c>
-      <c r="B29" s="60">
+      <c r="B29" s="59">
         <v>19198002550</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59" t="s">
+      <c r="D29" s="58"/>
+      <c r="E29" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="66" t="s">
+      <c r="F29" s="64"/>
+      <c r="G29" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="H29" s="63" t="s">
+      <c r="H29" s="62" t="s">
         <v>273</v>
       </c>
-      <c r="I29" s="59">
+      <c r="I29" s="58">
         <v>26.03</v>
       </c>
-      <c r="J29" s="64">
+      <c r="J29" s="63">
         <v>0.75</v>
       </c>
-      <c r="K29" s="59"/>
+      <c r="K29" s="58"/>
     </row>
     <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="59">
+      <c r="A30" s="58">
         <v>28</v>
       </c>
-      <c r="B30" s="60">
+      <c r="B30" s="59">
         <v>14992068672</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C30" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59" t="s">
+      <c r="D30" s="58"/>
+      <c r="E30" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="65"/>
-      <c r="G30" s="66" t="s">
+      <c r="F30" s="64"/>
+      <c r="G30" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>274</v>
       </c>
-      <c r="I30" s="59">
+      <c r="I30" s="58">
         <v>26.03</v>
       </c>
-      <c r="J30" s="64">
+      <c r="J30" s="63">
         <v>0.75</v>
       </c>
-      <c r="K30" s="59"/>
+      <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="59">
+      <c r="A31" s="58">
         <v>29</v>
       </c>
-      <c r="B31" s="60">
+      <c r="B31" s="59">
         <v>12649536826</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="60" t="s">
         <v>115</v>
       </c>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59" t="s">
+      <c r="D31" s="58"/>
+      <c r="E31" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="65"/>
-      <c r="G31" s="66" t="s">
+      <c r="F31" s="64"/>
+      <c r="G31" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="H31" s="63" t="s">
+      <c r="H31" s="62" t="s">
         <v>275</v>
       </c>
-      <c r="I31" s="59">
+      <c r="I31" s="58">
         <v>26.03</v>
       </c>
-      <c r="J31" s="64">
+      <c r="J31" s="63">
         <v>0.75</v>
       </c>
-      <c r="K31" s="59"/>
+      <c r="K31" s="58"/>
     </row>
     <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="59">
+      <c r="A32" s="58">
         <v>30</v>
       </c>
-      <c r="B32" s="60">
+      <c r="B32" s="59">
         <v>34123446490</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59" t="s">
+      <c r="D32" s="58"/>
+      <c r="E32" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="65"/>
-      <c r="G32" s="66" t="s">
+      <c r="F32" s="64"/>
+      <c r="G32" s="65" t="s">
         <v>118</v>
       </c>
-      <c r="H32" s="63" t="s">
+      <c r="H32" s="62" t="s">
         <v>276</v>
       </c>
-      <c r="I32" s="59">
+      <c r="I32" s="58">
         <v>26.03</v>
       </c>
-      <c r="J32" s="64">
+      <c r="J32" s="63">
         <v>0.75</v>
       </c>
-      <c r="K32" s="59"/>
+      <c r="K32" s="58"/>
     </row>
     <row r="33" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="59">
+      <c r="A33" s="58">
         <v>31</v>
       </c>
-      <c r="B33" s="60">
+      <c r="B33" s="59">
         <v>11144234640</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="59"/>
-      <c r="E33" s="59" t="s">
+      <c r="D33" s="58"/>
+      <c r="E33" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="65"/>
-      <c r="G33" s="66" t="s">
+      <c r="F33" s="64"/>
+      <c r="G33" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="H33" s="63" t="s">
+      <c r="H33" s="62" t="s">
         <v>277</v>
       </c>
-      <c r="I33" s="59">
+      <c r="I33" s="58">
         <v>26.03</v>
       </c>
-      <c r="J33" s="64">
+      <c r="J33" s="63">
         <v>0.75</v>
       </c>
-      <c r="K33" s="59"/>
+      <c r="K33" s="58"/>
     </row>
     <row r="34" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="59">
+      <c r="A34" s="58">
         <v>32</v>
       </c>
-      <c r="B34" s="60">
+      <c r="B34" s="59">
         <v>10015118164</v>
       </c>
-      <c r="C34" s="61" t="s">
+      <c r="C34" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="D34" s="59"/>
-      <c r="E34" s="59" t="s">
+      <c r="D34" s="58"/>
+      <c r="E34" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="65"/>
-      <c r="G34" s="66" t="s">
+      <c r="F34" s="64"/>
+      <c r="G34" s="65" t="s">
         <v>122</v>
       </c>
-      <c r="H34" s="63" t="s">
+      <c r="H34" s="62" t="s">
         <v>278</v>
       </c>
-      <c r="I34" s="59">
+      <c r="I34" s="58">
         <v>26.03</v>
       </c>
-      <c r="J34" s="64">
+      <c r="J34" s="63">
         <v>0.75</v>
       </c>
-      <c r="K34" s="59"/>
+      <c r="K34" s="58"/>
     </row>
     <row r="35" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="59">
+      <c r="A35" s="58">
         <v>33</v>
       </c>
-      <c r="B35" s="60">
+      <c r="B35" s="59">
         <v>11482575542</v>
       </c>
-      <c r="C35" s="61" t="s">
+      <c r="C35" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59" t="s">
+      <c r="D35" s="58"/>
+      <c r="E35" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="65"/>
-      <c r="G35" s="66" t="s">
+      <c r="F35" s="64"/>
+      <c r="G35" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="H35" s="63" t="s">
+      <c r="H35" s="62" t="s">
         <v>279</v>
       </c>
-      <c r="I35" s="59">
+      <c r="I35" s="58">
         <v>26.03</v>
       </c>
-      <c r="J35" s="64">
+      <c r="J35" s="63">
         <v>0.75</v>
       </c>
-      <c r="K35" s="59"/>
+      <c r="K35" s="58"/>
     </row>
     <row r="36" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="59">
+      <c r="A36" s="58">
         <v>34</v>
       </c>
-      <c r="B36" s="60">
+      <c r="B36" s="59">
         <v>11144234718</v>
       </c>
-      <c r="C36" s="61" t="s">
+      <c r="C36" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59" t="s">
+      <c r="D36" s="58"/>
+      <c r="E36" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F36" s="65"/>
-      <c r="G36" s="66" t="s">
+      <c r="F36" s="64"/>
+      <c r="G36" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="H36" s="63" t="s">
+      <c r="H36" s="62" t="s">
         <v>280</v>
       </c>
-      <c r="I36" s="59">
+      <c r="I36" s="58">
         <v>26.03</v>
       </c>
-      <c r="J36" s="64">
+      <c r="J36" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K36" s="59"/>
+      <c r="K36" s="58"/>
     </row>
     <row r="37" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="59">
+      <c r="A37" s="58">
         <v>35</v>
       </c>
-      <c r="B37" s="60">
+      <c r="B37" s="59">
         <v>10403070678</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59" t="s">
+      <c r="D37" s="58"/>
+      <c r="E37" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F37" s="65"/>
-      <c r="G37" s="66" t="s">
+      <c r="F37" s="64"/>
+      <c r="G37" s="65" t="s">
         <v>127</v>
       </c>
-      <c r="H37" s="63" t="s">
+      <c r="H37" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="I37" s="59">
+      <c r="I37" s="58">
         <v>26.03</v>
       </c>
-      <c r="J37" s="64">
+      <c r="J37" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K37" s="59"/>
+      <c r="K37" s="58"/>
     </row>
     <row r="38" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="59">
+      <c r="A38" s="58">
         <v>36</v>
       </c>
-      <c r="B38" s="60">
+      <c r="B38" s="59">
         <v>10009120968</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="C38" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59" t="s">
+      <c r="D38" s="58"/>
+      <c r="E38" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="59"/>
-      <c r="G38" s="66" t="s">
+      <c r="F38" s="58"/>
+      <c r="G38" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="H38" s="63" t="s">
+      <c r="H38" s="62" t="s">
         <v>282</v>
       </c>
-      <c r="I38" s="59">
+      <c r="I38" s="58">
         <v>26.03</v>
       </c>
-      <c r="J38" s="64">
+      <c r="J38" s="63">
         <v>0.75</v>
       </c>
-      <c r="K38" s="59"/>
+      <c r="K38" s="58"/>
     </row>
     <row r="39" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="59">
+      <c r="A39" s="58">
         <v>37</v>
       </c>
-      <c r="B39" s="60">
+      <c r="B39" s="59">
         <v>10051120268</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59" t="s">
+      <c r="D39" s="58"/>
+      <c r="E39" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="65"/>
-      <c r="G39" s="66" t="s">
+      <c r="F39" s="64"/>
+      <c r="G39" s="65" t="s">
         <v>130</v>
       </c>
-      <c r="H39" s="63" t="s">
+      <c r="H39" s="62" t="s">
         <v>283</v>
       </c>
-      <c r="I39" s="59">
+      <c r="I39" s="58">
         <v>26.03</v>
       </c>
-      <c r="J39" s="64">
+      <c r="J39" s="63">
         <v>0.75</v>
       </c>
-      <c r="K39" s="59"/>
+      <c r="K39" s="58"/>
     </row>
     <row r="40" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="59">
+      <c r="A40" s="58">
         <v>38</v>
       </c>
-      <c r="B40" s="60">
+      <c r="B40" s="59">
         <v>13507217994</v>
       </c>
-      <c r="C40" s="61" t="s">
+      <c r="C40" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59" t="s">
+      <c r="D40" s="58"/>
+      <c r="E40" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="65"/>
-      <c r="G40" s="66" t="s">
+      <c r="F40" s="64"/>
+      <c r="G40" s="65" t="s">
         <v>132</v>
       </c>
-      <c r="H40" s="63" t="s">
+      <c r="H40" s="62" t="s">
         <v>284</v>
       </c>
-      <c r="I40" s="59">
+      <c r="I40" s="58">
         <v>26.03</v>
       </c>
-      <c r="J40" s="64">
+      <c r="J40" s="63">
         <v>0.75</v>
       </c>
-      <c r="K40" s="59"/>
+      <c r="K40" s="58"/>
     </row>
     <row r="41" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="59">
+      <c r="A41" s="58">
         <v>39</v>
       </c>
-      <c r="B41" s="60">
+      <c r="B41" s="59">
         <v>12068013786</v>
       </c>
-      <c r="C41" s="61" t="s">
+      <c r="C41" s="60" t="s">
         <v>133</v>
       </c>
-      <c r="D41" s="59"/>
-      <c r="E41" s="59" t="s">
+      <c r="D41" s="58"/>
+      <c r="E41" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="65"/>
-      <c r="G41" s="66" t="s">
+      <c r="F41" s="64"/>
+      <c r="G41" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="H41" s="63" t="s">
+      <c r="H41" s="62" t="s">
         <v>285</v>
       </c>
-      <c r="I41" s="59">
+      <c r="I41" s="58">
         <v>26.03</v>
       </c>
-      <c r="J41" s="64">
+      <c r="J41" s="63">
         <v>0.75</v>
       </c>
-      <c r="K41" s="59"/>
+      <c r="K41" s="58"/>
     </row>
     <row r="42" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="59">
+      <c r="A42" s="58">
         <v>40</v>
       </c>
-      <c r="B42" s="60">
+      <c r="B42" s="59">
         <v>14377140894</v>
       </c>
-      <c r="C42" s="61" t="s">
+      <c r="C42" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="D42" s="59"/>
-      <c r="E42" s="59" t="s">
+      <c r="D42" s="58"/>
+      <c r="E42" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="65"/>
-      <c r="G42" s="66" t="s">
+      <c r="F42" s="64"/>
+      <c r="G42" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="H42" s="63" t="s">
+      <c r="H42" s="62" t="s">
         <v>286</v>
       </c>
-      <c r="I42" s="59">
+      <c r="I42" s="58">
         <v>26.03</v>
       </c>
-      <c r="J42" s="64">
+      <c r="J42" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K42" s="59"/>
+      <c r="K42" s="58"/>
     </row>
     <row r="43" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="59">
+      <c r="A43" s="58">
         <v>41</v>
       </c>
-      <c r="B43" s="60">
+      <c r="B43" s="59">
         <v>14695010084</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59" t="s">
+      <c r="D43" s="58"/>
+      <c r="E43" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="66" t="s">
+      <c r="F43" s="64"/>
+      <c r="G43" s="65" t="s">
         <v>137</v>
       </c>
-      <c r="H43" s="63" t="s">
+      <c r="H43" s="62" t="s">
         <v>287</v>
       </c>
-      <c r="I43" s="59">
+      <c r="I43" s="58">
         <v>26.03</v>
       </c>
-      <c r="J43" s="64">
+      <c r="J43" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K43" s="59"/>
+      <c r="K43" s="58"/>
     </row>
     <row r="44" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="59">
+      <c r="A44" s="58">
         <v>42</v>
       </c>
-      <c r="B44" s="60">
+      <c r="B44" s="59">
         <v>10048117608</v>
       </c>
-      <c r="C44" s="61" t="s">
+      <c r="C44" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="D44" s="59"/>
-      <c r="E44" s="59" t="s">
+      <c r="D44" s="58"/>
+      <c r="E44" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F44" s="65"/>
-      <c r="G44" s="66" t="s">
+      <c r="F44" s="64"/>
+      <c r="G44" s="65" t="s">
         <v>139</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>288</v>
       </c>
-      <c r="I44" s="59">
+      <c r="I44" s="58">
         <v>31.03</v>
       </c>
-      <c r="J44" s="64">
+      <c r="J44" s="63">
         <v>0.75</v>
       </c>
-      <c r="K44" s="59"/>
+      <c r="K44" s="58"/>
     </row>
     <row r="45" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="59">
+      <c r="A45" s="58">
         <v>43</v>
       </c>
-      <c r="B45" s="60">
+      <c r="B45" s="59">
         <v>23336716810</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59" t="s">
+      <c r="D45" s="58"/>
+      <c r="E45" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F45" s="65"/>
-      <c r="G45" s="66" t="s">
+      <c r="F45" s="64"/>
+      <c r="G45" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="63" t="s">
+      <c r="H45" s="62" t="s">
         <v>289</v>
       </c>
-      <c r="I45" s="59">
+      <c r="I45" s="58">
         <v>31.03</v>
       </c>
-      <c r="J45" s="64">
+      <c r="J45" s="63">
         <v>0.75</v>
       </c>
-      <c r="K45" s="59"/>
+      <c r="K45" s="58"/>
     </row>
     <row r="46" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="59">
+      <c r="A46" s="58">
         <v>44</v>
       </c>
-      <c r="B46" s="60">
+      <c r="B46" s="59">
         <v>11734411192</v>
       </c>
-      <c r="C46" s="61" t="s">
+      <c r="C46" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59" t="s">
+      <c r="D46" s="58"/>
+      <c r="E46" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F46" s="65"/>
-      <c r="G46" s="66" t="s">
+      <c r="F46" s="64"/>
+      <c r="G46" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="H46" s="63" t="s">
+      <c r="H46" s="62" t="s">
         <v>290</v>
       </c>
-      <c r="I46" s="59">
+      <c r="I46" s="58">
         <v>31.03</v>
       </c>
-      <c r="J46" s="64">
+      <c r="J46" s="63">
         <v>0.75</v>
       </c>
-      <c r="K46" s="59"/>
+      <c r="K46" s="58"/>
     </row>
     <row r="47" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="59">
+      <c r="A47" s="58">
         <v>45</v>
       </c>
-      <c r="B47" s="60">
+      <c r="B47" s="59">
         <v>14449188076</v>
       </c>
-      <c r="C47" s="61" t="s">
+      <c r="C47" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59" t="s">
+      <c r="D47" s="58"/>
+      <c r="E47" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F47" s="65"/>
-      <c r="G47" s="66" t="s">
+      <c r="F47" s="64"/>
+      <c r="G47" s="65" t="s">
         <v>143</v>
       </c>
-      <c r="H47" s="63" t="s">
+      <c r="H47" s="62" t="s">
         <v>291</v>
       </c>
-      <c r="I47" s="59">
+      <c r="I47" s="58">
         <v>31.03</v>
       </c>
-      <c r="J47" s="64">
+      <c r="J47" s="63">
         <v>0.75</v>
       </c>
-      <c r="K47" s="59"/>
+      <c r="K47" s="58"/>
     </row>
     <row r="48" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="59">
+      <c r="A48" s="58">
         <v>46</v>
       </c>
-      <c r="B48" s="60">
+      <c r="B48" s="59">
         <v>11108938898</v>
       </c>
-      <c r="C48" s="61" t="s">
+      <c r="C48" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59" t="s">
+      <c r="D48" s="58"/>
+      <c r="E48" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F48" s="65"/>
-      <c r="G48" s="66" t="s">
+      <c r="F48" s="64"/>
+      <c r="G48" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="H48" s="63" t="s">
+      <c r="H48" s="62" t="s">
         <v>292</v>
       </c>
-      <c r="I48" s="59">
+      <c r="I48" s="58">
         <v>31.03</v>
       </c>
-      <c r="J48" s="64">
+      <c r="J48" s="63">
         <v>0.75</v>
       </c>
-      <c r="K48" s="59"/>
+      <c r="K48" s="58"/>
     </row>
     <row r="49" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="59">
+      <c r="A49" s="58">
         <v>47</v>
       </c>
-      <c r="B49" s="60">
+      <c r="B49" s="59">
         <v>14458187930</v>
       </c>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="D49" s="59"/>
-      <c r="E49" s="59" t="s">
+      <c r="D49" s="58"/>
+      <c r="E49" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F49" s="65"/>
-      <c r="G49" s="66" t="s">
+      <c r="F49" s="64"/>
+      <c r="G49" s="65" t="s">
         <v>147</v>
       </c>
-      <c r="H49" s="63" t="s">
+      <c r="H49" s="62" t="s">
         <v>293</v>
       </c>
-      <c r="I49" s="59">
+      <c r="I49" s="58">
         <v>31.03</v>
       </c>
-      <c r="J49" s="64">
+      <c r="J49" s="63">
         <v>0.75</v>
       </c>
-      <c r="K49" s="59"/>
+      <c r="K49" s="58"/>
     </row>
     <row r="50" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="59">
+      <c r="A50" s="58">
         <v>48</v>
       </c>
-      <c r="B50" s="60">
+      <c r="B50" s="59">
         <v>10271074204</v>
       </c>
-      <c r="C50" s="61" t="s">
+      <c r="C50" s="60" t="s">
         <v>148</v>
       </c>
-      <c r="D50" s="59"/>
-      <c r="E50" s="59" t="s">
+      <c r="D50" s="58"/>
+      <c r="E50" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F50" s="65"/>
-      <c r="G50" s="66" t="s">
+      <c r="F50" s="64"/>
+      <c r="G50" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="H50" s="63" t="s">
+      <c r="H50" s="62" t="s">
         <v>294</v>
       </c>
-      <c r="I50" s="59">
+      <c r="I50" s="58">
         <v>31.03</v>
       </c>
-      <c r="J50" s="64">
+      <c r="J50" s="63">
         <v>0.75</v>
       </c>
-      <c r="K50" s="59"/>
+      <c r="K50" s="58"/>
     </row>
     <row r="51" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="59">
+      <c r="A51" s="58">
         <v>49</v>
       </c>
-      <c r="B51" s="60">
+      <c r="B51" s="59">
         <v>31768855328</v>
       </c>
-      <c r="C51" s="61" t="s">
+      <c r="C51" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="D51" s="59"/>
-      <c r="E51" s="59" t="s">
+      <c r="D51" s="58"/>
+      <c r="E51" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F51" s="65"/>
-      <c r="G51" s="66" t="s">
+      <c r="F51" s="64"/>
+      <c r="G51" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="H51" s="63" t="s">
+      <c r="H51" s="62" t="s">
         <v>295</v>
       </c>
-      <c r="I51" s="59">
+      <c r="I51" s="58">
         <v>31.03</v>
       </c>
-      <c r="J51" s="64">
+      <c r="J51" s="63">
         <v>0.75</v>
       </c>
-      <c r="K51" s="59"/>
+      <c r="K51" s="58"/>
     </row>
     <row r="52" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="59">
+      <c r="A52" s="58">
         <v>50</v>
       </c>
-      <c r="B52" s="60">
+      <c r="B52" s="59">
         <v>29573323330</v>
       </c>
-      <c r="C52" s="61" t="s">
+      <c r="C52" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59" t="s">
+      <c r="D52" s="58"/>
+      <c r="E52" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F52" s="65"/>
-      <c r="G52" s="66" t="s">
+      <c r="F52" s="64"/>
+      <c r="G52" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="H52" s="63" t="s">
+      <c r="H52" s="62" t="s">
         <v>296</v>
       </c>
-      <c r="I52" s="59">
+      <c r="I52" s="58">
         <v>31.03</v>
       </c>
-      <c r="J52" s="64">
+      <c r="J52" s="63">
         <v>0.75</v>
       </c>
-      <c r="K52" s="59"/>
+      <c r="K52" s="58"/>
     </row>
     <row r="53" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="59">
+      <c r="A53" s="58">
         <v>51</v>
       </c>
-      <c r="B53" s="60">
+      <c r="B53" s="59">
         <v>10300318804</v>
       </c>
-      <c r="C53" s="61" t="s">
+      <c r="C53" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="D53" s="59"/>
-      <c r="E53" s="59" t="s">
+      <c r="D53" s="58"/>
+      <c r="E53" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="F53" s="59"/>
-      <c r="G53" s="66" t="s">
+      <c r="F53" s="58"/>
+      <c r="G53" s="65" t="s">
         <v>153</v>
       </c>
-      <c r="H53" s="63" t="s">
+      <c r="H53" s="62" t="s">
         <v>297</v>
       </c>
-      <c r="I53" s="59"/>
-      <c r="J53" s="59"/>
-      <c r="K53" s="59"/>
+      <c r="I53" s="58"/>
+      <c r="J53" s="58"/>
+      <c r="K53" s="58"/>
     </row>
     <row r="54" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="59">
+      <c r="A54" s="58">
         <v>52</v>
       </c>
-      <c r="B54" s="60">
+      <c r="B54" s="59">
         <v>15505896638</v>
       </c>
-      <c r="C54" s="61" t="s">
+      <c r="C54" s="60" t="s">
         <v>154</v>
       </c>
-      <c r="D54" s="59"/>
-      <c r="E54" s="59" t="s">
+      <c r="D54" s="58"/>
+      <c r="E54" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="F54" s="59"/>
-      <c r="G54" s="66" t="s">
+      <c r="F54" s="58"/>
+      <c r="G54" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="H54" s="63" t="s">
+      <c r="H54" s="62" t="s">
         <v>298</v>
       </c>
-      <c r="I54" s="59"/>
-      <c r="J54" s="59"/>
-      <c r="K54" s="59"/>
+      <c r="I54" s="58"/>
+      <c r="J54" s="58"/>
+      <c r="K54" s="58"/>
     </row>
     <row r="55" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="59">
+      <c r="A55" s="58">
         <v>53</v>
       </c>
-      <c r="B55" s="60">
+      <c r="B55" s="59">
         <v>17960854932</v>
       </c>
-      <c r="C55" s="61" t="s">
+      <c r="C55" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="D55" s="59"/>
-      <c r="E55" s="59" t="s">
+      <c r="D55" s="58"/>
+      <c r="E55" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="F55" s="65"/>
-      <c r="G55" s="66" t="s">
+      <c r="F55" s="64"/>
+      <c r="G55" s="65" t="s">
         <v>156</v>
       </c>
-      <c r="H55" s="63" t="s">
+      <c r="H55" s="62" t="s">
         <v>299</v>
       </c>
-      <c r="I55" s="59"/>
-      <c r="J55" s="59"/>
-      <c r="K55" s="59"/>
+      <c r="I55" s="58"/>
+      <c r="J55" s="58"/>
+      <c r="K55" s="58"/>
     </row>
     <row r="56" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="54"/>
@@ -4622,490 +4624,490 @@
       <c r="A60" s="55">
         <v>1</v>
       </c>
-      <c r="B60" s="60">
+      <c r="B60" s="59">
         <v>15865049750</v>
       </c>
-      <c r="C60" s="61" t="s">
+      <c r="C60" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="59"/>
-      <c r="E60" s="59" t="s">
+      <c r="D60" s="58"/>
+      <c r="E60" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F60" s="59"/>
-      <c r="G60" s="66" t="s">
+      <c r="F60" s="58"/>
+      <c r="G60" s="65" t="s">
         <v>158</v>
       </c>
-      <c r="H60" s="63" t="s">
+      <c r="H60" s="62" t="s">
         <v>300</v>
       </c>
-      <c r="I60" s="59"/>
-      <c r="J60" s="59"/>
-      <c r="K60" s="59"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="58"/>
+      <c r="K60" s="58"/>
     </row>
     <row r="61" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="55">
         <v>2</v>
       </c>
-      <c r="B61" s="60">
+      <c r="B61" s="59">
         <v>15616146684</v>
       </c>
-      <c r="C61" s="61" t="s">
+      <c r="C61" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="D61" s="59"/>
-      <c r="E61" s="59" t="s">
+      <c r="D61" s="58"/>
+      <c r="E61" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F61" s="59"/>
-      <c r="G61" s="66" t="s">
+      <c r="F61" s="58"/>
+      <c r="G61" s="65" t="s">
         <v>158</v>
       </c>
-      <c r="H61" s="63" t="s">
+      <c r="H61" s="62" t="s">
         <v>301</v>
       </c>
-      <c r="I61" s="59">
+      <c r="I61" s="58">
         <v>16.02</v>
       </c>
-      <c r="J61" s="64">
+      <c r="J61" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K61" s="59"/>
+      <c r="K61" s="58"/>
     </row>
     <row r="62" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="55">
         <v>3</v>
       </c>
-      <c r="B62" s="60">
+      <c r="B62" s="59">
         <v>14300484194</v>
       </c>
-      <c r="C62" s="61" t="s">
+      <c r="C62" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="D62" s="59"/>
-      <c r="E62" s="59" t="s">
+      <c r="D62" s="58"/>
+      <c r="E62" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F62" s="59"/>
-      <c r="G62" s="66" t="s">
+      <c r="F62" s="58"/>
+      <c r="G62" s="65" t="s">
         <v>161</v>
       </c>
-      <c r="H62" s="63" t="s">
+      <c r="H62" s="62" t="s">
         <v>302</v>
       </c>
-      <c r="I62" s="59">
+      <c r="I62" s="58">
         <v>18.02</v>
       </c>
-      <c r="J62" s="64">
+      <c r="J62" s="63">
         <v>0.75</v>
       </c>
-      <c r="K62" s="59"/>
+      <c r="K62" s="58"/>
     </row>
     <row r="63" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="55">
         <v>4</v>
       </c>
-      <c r="B63" s="60">
+      <c r="B63" s="59">
         <v>29896460262</v>
       </c>
-      <c r="C63" s="61" t="s">
+      <c r="C63" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="D63" s="59"/>
-      <c r="E63" s="59" t="s">
+      <c r="D63" s="58"/>
+      <c r="E63" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F63" s="59"/>
-      <c r="G63" s="66" t="s">
+      <c r="F63" s="58"/>
+      <c r="G63" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="H63" s="63" t="s">
+      <c r="H63" s="62" t="s">
         <v>303</v>
       </c>
-      <c r="I63" s="59">
+      <c r="I63" s="58">
         <v>19.02</v>
       </c>
-      <c r="J63" s="64">
+      <c r="J63" s="63">
         <v>0.75</v>
       </c>
-      <c r="K63" s="59"/>
+      <c r="K63" s="58"/>
     </row>
     <row r="64" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="55">
         <v>5</v>
       </c>
-      <c r="B64" s="60">
+      <c r="B64" s="59">
         <v>17633210058</v>
       </c>
-      <c r="C64" s="61" t="s">
+      <c r="C64" s="60" t="s">
         <v>163</v>
       </c>
-      <c r="D64" s="59"/>
-      <c r="E64" s="59" t="s">
+      <c r="D64" s="58"/>
+      <c r="E64" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F64" s="59"/>
-      <c r="G64" s="66" t="s">
+      <c r="F64" s="58"/>
+      <c r="G64" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="H64" s="63" t="s">
+      <c r="H64" s="62" t="s">
         <v>304</v>
       </c>
-      <c r="I64" s="59">
+      <c r="I64" s="58">
         <v>19.02</v>
       </c>
-      <c r="J64" s="64">
+      <c r="J64" s="63">
         <v>0.75</v>
       </c>
-      <c r="K64" s="59"/>
+      <c r="K64" s="58"/>
     </row>
     <row r="65" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="55">
         <v>6</v>
       </c>
-      <c r="B65" s="60">
+      <c r="B65" s="59">
         <v>10169029378</v>
       </c>
-      <c r="C65" s="61" t="s">
+      <c r="C65" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="D65" s="59"/>
-      <c r="E65" s="59" t="s">
+      <c r="D65" s="58"/>
+      <c r="E65" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F65" s="59"/>
-      <c r="G65" s="66" t="s">
+      <c r="F65" s="58"/>
+      <c r="G65" s="65" t="s">
         <v>165</v>
       </c>
-      <c r="H65" s="63" t="s">
+      <c r="H65" s="62" t="s">
         <v>305</v>
       </c>
-      <c r="I65" s="59">
+      <c r="I65" s="58">
         <v>19.02</v>
       </c>
-      <c r="J65" s="64">
+      <c r="J65" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K65" s="59"/>
+      <c r="K65" s="58"/>
     </row>
     <row r="66" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="55">
         <v>7</v>
       </c>
-      <c r="B66" s="60">
+      <c r="B66" s="59">
         <v>13264143598</v>
       </c>
-      <c r="C66" s="61" t="s">
+      <c r="C66" s="60" t="s">
         <v>166</v>
       </c>
-      <c r="D66" s="59"/>
-      <c r="E66" s="59" t="s">
+      <c r="D66" s="58"/>
+      <c r="E66" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F66" s="65"/>
-      <c r="G66" s="66" t="s">
+      <c r="F66" s="64"/>
+      <c r="G66" s="65" t="s">
         <v>167</v>
       </c>
-      <c r="H66" s="63" t="s">
+      <c r="H66" s="62" t="s">
         <v>306</v>
       </c>
-      <c r="I66" s="59">
+      <c r="I66" s="58">
         <v>23.03</v>
       </c>
-      <c r="J66" s="64">
+      <c r="J66" s="63">
         <v>0.75</v>
       </c>
-      <c r="K66" s="59"/>
+      <c r="K66" s="58"/>
     </row>
     <row r="67" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="55">
         <v>8</v>
       </c>
-      <c r="B67" s="60">
+      <c r="B67" s="59">
         <v>24808561532</v>
       </c>
-      <c r="C67" s="61" t="s">
+      <c r="C67" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="D67" s="59"/>
-      <c r="E67" s="59" t="s">
+      <c r="D67" s="58"/>
+      <c r="E67" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F67" s="65"/>
-      <c r="G67" s="66" t="s">
+      <c r="F67" s="64"/>
+      <c r="G67" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="H67" s="63" t="s">
+      <c r="H67" s="62" t="s">
         <v>307</v>
       </c>
-      <c r="I67" s="59">
+      <c r="I67" s="58">
         <v>24.03</v>
       </c>
-      <c r="J67" s="64">
+      <c r="J67" s="63">
         <v>0.75</v>
       </c>
-      <c r="K67" s="59"/>
+      <c r="K67" s="58"/>
     </row>
     <row r="68" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="55">
         <v>9</v>
       </c>
-      <c r="B68" s="60">
+      <c r="B68" s="59">
         <v>22706535594</v>
       </c>
-      <c r="C68" s="61" t="s">
+      <c r="C68" s="60" t="s">
         <v>169</v>
       </c>
-      <c r="D68" s="59"/>
-      <c r="E68" s="59" t="s">
+      <c r="D68" s="58"/>
+      <c r="E68" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F68" s="65"/>
-      <c r="G68" s="66" t="s">
+      <c r="F68" s="64"/>
+      <c r="G68" s="65" t="s">
         <v>170</v>
       </c>
-      <c r="H68" s="63" t="s">
+      <c r="H68" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="I68" s="59">
+      <c r="I68" s="58">
         <v>26.03</v>
       </c>
-      <c r="J68" s="64">
+      <c r="J68" s="63">
         <v>0.75</v>
       </c>
-      <c r="K68" s="59"/>
+      <c r="K68" s="58"/>
     </row>
     <row r="69" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="55">
         <v>10</v>
       </c>
-      <c r="B69" s="60">
+      <c r="B69" s="59">
         <v>11899063052</v>
       </c>
-      <c r="C69" s="61" t="s">
+      <c r="C69" s="60" t="s">
         <v>171</v>
       </c>
-      <c r="D69" s="59"/>
-      <c r="E69" s="59" t="s">
+      <c r="D69" s="58"/>
+      <c r="E69" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F69" s="65"/>
-      <c r="G69" s="66" t="s">
+      <c r="F69" s="64"/>
+      <c r="G69" s="65" t="s">
         <v>172</v>
       </c>
-      <c r="H69" s="63" t="s">
+      <c r="H69" s="62" t="s">
         <v>309</v>
       </c>
-      <c r="I69" s="59">
+      <c r="I69" s="58">
         <v>26.03</v>
       </c>
-      <c r="J69" s="64">
+      <c r="J69" s="63">
         <v>0.75</v>
       </c>
-      <c r="K69" s="59"/>
+      <c r="K69" s="58"/>
     </row>
     <row r="70" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="55">
         <v>11</v>
       </c>
-      <c r="B70" s="60">
+      <c r="B70" s="59">
         <v>11230082704</v>
       </c>
-      <c r="C70" s="61" t="s">
+      <c r="C70" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="D70" s="59"/>
-      <c r="E70" s="59" t="s">
+      <c r="D70" s="58"/>
+      <c r="E70" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F70" s="65"/>
-      <c r="G70" s="66" t="s">
+      <c r="F70" s="64"/>
+      <c r="G70" s="65" t="s">
         <v>174</v>
       </c>
-      <c r="H70" s="63" t="s">
+      <c r="H70" s="62" t="s">
         <v>310</v>
       </c>
-      <c r="I70" s="59">
+      <c r="I70" s="58">
         <v>26.03</v>
       </c>
-      <c r="J70" s="64">
+      <c r="J70" s="63">
         <v>0.75</v>
       </c>
-      <c r="K70" s="59"/>
+      <c r="K70" s="58"/>
     </row>
     <row r="71" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="55">
         <v>12</v>
       </c>
-      <c r="B71" s="60">
+      <c r="B71" s="59">
         <v>11407300792</v>
       </c>
-      <c r="C71" s="61" t="s">
+      <c r="C71" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="D71" s="59"/>
-      <c r="E71" s="59" t="s">
+      <c r="D71" s="58"/>
+      <c r="E71" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F71" s="65"/>
-      <c r="G71" s="66" t="s">
+      <c r="F71" s="64"/>
+      <c r="G71" s="65" t="s">
         <v>176</v>
       </c>
-      <c r="H71" s="63" t="s">
+      <c r="H71" s="62" t="s">
         <v>311</v>
       </c>
-      <c r="I71" s="59">
+      <c r="I71" s="58">
         <v>26.03</v>
       </c>
-      <c r="J71" s="64">
+      <c r="J71" s="63">
         <v>0.75</v>
       </c>
-      <c r="K71" s="59"/>
+      <c r="K71" s="58"/>
     </row>
     <row r="72" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="55">
         <v>13</v>
       </c>
-      <c r="B72" s="60">
+      <c r="B72" s="59">
         <v>11221210932</v>
       </c>
-      <c r="C72" s="61" t="s">
+      <c r="C72" s="60" t="s">
         <v>177</v>
       </c>
-      <c r="D72" s="59"/>
-      <c r="E72" s="59" t="s">
+      <c r="D72" s="58"/>
+      <c r="E72" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F72" s="65"/>
-      <c r="G72" s="66" t="s">
+      <c r="F72" s="64"/>
+      <c r="G72" s="65" t="s">
         <v>178</v>
       </c>
-      <c r="H72" s="63" t="s">
+      <c r="H72" s="62" t="s">
         <v>312</v>
       </c>
-      <c r="I72" s="59">
+      <c r="I72" s="58">
         <v>26.03</v>
       </c>
-      <c r="J72" s="64">
+      <c r="J72" s="63">
         <v>0.75</v>
       </c>
-      <c r="K72" s="59"/>
+      <c r="K72" s="58"/>
     </row>
     <row r="73" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="55">
         <v>14</v>
       </c>
-      <c r="B73" s="60">
+      <c r="B73" s="59">
         <v>13327145668</v>
       </c>
-      <c r="C73" s="61" t="s">
+      <c r="C73" s="60" t="s">
         <v>179</v>
       </c>
-      <c r="D73" s="59"/>
-      <c r="E73" s="59" t="s">
+      <c r="D73" s="58"/>
+      <c r="E73" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F73" s="65"/>
-      <c r="G73" s="66" t="s">
+      <c r="F73" s="64"/>
+      <c r="G73" s="65" t="s">
         <v>180</v>
       </c>
-      <c r="H73" s="63" t="s">
+      <c r="H73" s="62" t="s">
         <v>313</v>
       </c>
-      <c r="I73" s="59">
+      <c r="I73" s="58">
         <v>26.03</v>
       </c>
-      <c r="J73" s="64">
+      <c r="J73" s="63">
         <v>0.75</v>
       </c>
-      <c r="K73" s="59"/>
+      <c r="K73" s="58"/>
     </row>
     <row r="74" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="55">
         <v>15</v>
       </c>
-      <c r="B74" s="60">
+      <c r="B74" s="59">
         <v>15853063102</v>
       </c>
-      <c r="C74" s="61" t="s">
+      <c r="C74" s="60" t="s">
         <v>181</v>
       </c>
-      <c r="D74" s="59"/>
-      <c r="E74" s="59" t="s">
+      <c r="D74" s="58"/>
+      <c r="E74" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F74" s="65"/>
-      <c r="G74" s="66" t="s">
+      <c r="F74" s="64"/>
+      <c r="G74" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="H74" s="63" t="s">
+      <c r="H74" s="62" t="s">
         <v>314</v>
       </c>
-      <c r="I74" s="59">
+      <c r="I74" s="58">
         <v>26.03</v>
       </c>
-      <c r="J74" s="64">
+      <c r="J74" s="63">
         <v>0.75</v>
       </c>
-      <c r="K74" s="59"/>
+      <c r="K74" s="58"/>
     </row>
     <row r="75" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="55">
         <v>16</v>
       </c>
-      <c r="B75" s="60">
+      <c r="B75" s="59">
         <v>12748032816</v>
       </c>
-      <c r="C75" s="61" t="s">
+      <c r="C75" s="60" t="s">
         <v>182</v>
       </c>
-      <c r="D75" s="59"/>
-      <c r="E75" s="59" t="s">
+      <c r="D75" s="58"/>
+      <c r="E75" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F75" s="65"/>
-      <c r="G75" s="66" t="s">
+      <c r="F75" s="64"/>
+      <c r="G75" s="65" t="s">
         <v>183</v>
       </c>
-      <c r="H75" s="63" t="s">
+      <c r="H75" s="62" t="s">
         <v>315</v>
       </c>
-      <c r="I75" s="59">
+      <c r="I75" s="58">
         <v>26.03</v>
       </c>
-      <c r="J75" s="64">
+      <c r="J75" s="63">
         <v>0.80208333333333337</v>
       </c>
-      <c r="K75" s="59"/>
+      <c r="K75" s="58"/>
     </row>
     <row r="76" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="55">
         <v>17</v>
       </c>
-      <c r="B76" s="60">
+      <c r="B76" s="59">
         <v>38050348056</v>
       </c>
-      <c r="C76" s="61" t="s">
+      <c r="C76" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="D76" s="59"/>
-      <c r="E76" s="59" t="s">
+      <c r="D76" s="58"/>
+      <c r="E76" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F76" s="65"/>
-      <c r="G76" s="66" t="s">
+      <c r="F76" s="64"/>
+      <c r="G76" s="65" t="s">
         <v>185</v>
       </c>
-      <c r="H76" s="63" t="s">
+      <c r="H76" s="62" t="s">
         <v>316</v>
       </c>
-      <c r="I76" s="59">
+      <c r="I76" s="58">
         <v>31.03</v>
       </c>
-      <c r="J76" s="64">
+      <c r="J76" s="63">
         <v>0.75</v>
       </c>
-      <c r="K76" s="59"/>
+      <c r="K76" s="58"/>
     </row>
     <row r="77" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="54"/>
@@ -5160,91 +5162,91 @@
       <c r="K80" s="54"/>
     </row>
     <row r="81" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="59">
+      <c r="A81" s="58">
         <v>1</v>
       </c>
-      <c r="B81" s="60">
+      <c r="B81" s="59">
         <v>36583309018</v>
       </c>
-      <c r="C81" s="61" t="s">
+      <c r="C81" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="D81" s="59"/>
-      <c r="E81" s="59" t="s">
+      <c r="D81" s="58"/>
+      <c r="E81" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="F81" s="65"/>
-      <c r="G81" s="66" t="s">
+      <c r="F81" s="64"/>
+      <c r="G81" s="65" t="s">
         <v>187</v>
       </c>
-      <c r="H81" s="63" t="s">
+      <c r="H81" s="62" t="s">
         <v>317</v>
       </c>
-      <c r="I81" s="59">
+      <c r="I81" s="58">
         <v>23.03</v>
       </c>
-      <c r="J81" s="64">
+      <c r="J81" s="63">
         <v>0.75</v>
       </c>
-      <c r="K81" s="59"/>
+      <c r="K81" s="58"/>
     </row>
     <row r="82" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="59">
+      <c r="A82" s="58">
         <v>2</v>
       </c>
-      <c r="B82" s="60">
+      <c r="B82" s="59">
         <v>13417007722</v>
       </c>
-      <c r="C82" s="61" t="s">
+      <c r="C82" s="60" t="s">
         <v>188</v>
       </c>
-      <c r="D82" s="59"/>
-      <c r="E82" s="59" t="s">
+      <c r="D82" s="58"/>
+      <c r="E82" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="F82" s="65"/>
-      <c r="G82" s="66" t="s">
+      <c r="F82" s="64"/>
+      <c r="G82" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="H82" s="63" t="s">
+      <c r="H82" s="62" t="s">
         <v>190</v>
       </c>
-      <c r="I82" s="59">
+      <c r="I82" s="58">
         <v>26.03</v>
       </c>
-      <c r="J82" s="64">
+      <c r="J82" s="63">
         <v>0.75</v>
       </c>
-      <c r="K82" s="59"/>
+      <c r="K82" s="58"/>
     </row>
     <row r="83" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="55">
         <v>3</v>
       </c>
-      <c r="B83" s="60">
+      <c r="B83" s="59">
         <v>16239007772</v>
       </c>
-      <c r="C83" s="61" t="s">
+      <c r="C83" s="60" t="s">
         <v>191</v>
       </c>
-      <c r="D83" s="59"/>
-      <c r="E83" s="59" t="s">
+      <c r="D83" s="58"/>
+      <c r="E83" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="F83" s="65"/>
-      <c r="G83" s="66" t="s">
+      <c r="F83" s="64"/>
+      <c r="G83" s="65" t="s">
         <v>192</v>
       </c>
-      <c r="H83" s="63" t="s">
+      <c r="H83" s="62" t="s">
         <v>318</v>
       </c>
-      <c r="I83" s="59">
+      <c r="I83" s="58">
         <v>31.03</v>
       </c>
-      <c r="J83" s="64">
+      <c r="J83" s="63">
         <v>0.75</v>
       </c>
-      <c r="K83" s="59"/>
+      <c r="K83" s="58"/>
     </row>
     <row r="84" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="54"/>
@@ -5312,108 +5314,108 @@
       <c r="K88" s="54"/>
     </row>
     <row r="89" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="59">
+      <c r="A89" s="58">
         <v>1</v>
       </c>
-      <c r="B89" s="60">
+      <c r="B89" s="59">
         <v>10377141756</v>
       </c>
-      <c r="C89" s="61" t="s">
+      <c r="C89" s="60" t="s">
         <v>193</v>
       </c>
-      <c r="D89" s="59"/>
-      <c r="E89" s="59" t="s">
+      <c r="D89" s="58"/>
+      <c r="E89" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="F89" s="65"/>
-      <c r="G89" s="66" t="s">
+      <c r="F89" s="64"/>
+      <c r="G89" s="65" t="s">
         <v>195</v>
       </c>
-      <c r="H89" s="63" t="s">
+      <c r="H89" s="62" t="s">
         <v>319</v>
       </c>
-      <c r="I89" s="59"/>
-      <c r="J89" s="59"/>
-      <c r="K89" s="59"/>
+      <c r="I89" s="58"/>
+      <c r="J89" s="58"/>
+      <c r="K89" s="58"/>
     </row>
     <row r="90" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="55">
         <v>2</v>
       </c>
-      <c r="B90" s="60">
+      <c r="B90" s="59">
         <v>11579367166</v>
       </c>
-      <c r="C90" s="61" t="s">
+      <c r="C90" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="D90" s="59"/>
-      <c r="E90" s="59" t="s">
+      <c r="D90" s="58"/>
+      <c r="E90" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="F90" s="59"/>
-      <c r="G90" s="66" t="s">
+      <c r="F90" s="58"/>
+      <c r="G90" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="H90" s="63" t="s">
+      <c r="H90" s="62" t="s">
         <v>320</v>
       </c>
-      <c r="I90" s="59">
+      <c r="I90" s="58">
         <v>31.03</v>
       </c>
-      <c r="J90" s="64">
+      <c r="J90" s="63">
         <v>0.75</v>
       </c>
-      <c r="K90" s="59"/>
+      <c r="K90" s="58"/>
     </row>
     <row r="91" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="59">
+      <c r="A91" s="58">
         <v>3</v>
       </c>
-      <c r="B91" s="60">
+      <c r="B91" s="59">
         <v>12397043324</v>
       </c>
-      <c r="C91" s="61" t="s">
+      <c r="C91" s="60" t="s">
         <v>199</v>
       </c>
-      <c r="D91" s="59"/>
-      <c r="E91" s="59" t="s">
+      <c r="D91" s="58"/>
+      <c r="E91" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="F91" s="65"/>
-      <c r="G91" s="66" t="s">
+      <c r="F91" s="64"/>
+      <c r="G91" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="H91" s="63" t="s">
+      <c r="H91" s="62" t="s">
         <v>321</v>
       </c>
-      <c r="I91" s="59"/>
-      <c r="J91" s="59"/>
-      <c r="K91" s="59"/>
+      <c r="I91" s="58"/>
+      <c r="J91" s="58"/>
+      <c r="K91" s="58"/>
     </row>
     <row r="92" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="59">
+      <c r="A92" s="58">
         <v>4</v>
       </c>
-      <c r="B92" s="60">
+      <c r="B92" s="59">
         <v>10042245468</v>
       </c>
-      <c r="C92" s="61" t="s">
+      <c r="C92" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="D92" s="59"/>
-      <c r="E92" s="59" t="s">
+      <c r="D92" s="58"/>
+      <c r="E92" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="F92" s="59"/>
-      <c r="G92" s="66" t="s">
+      <c r="F92" s="58"/>
+      <c r="G92" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="H92" s="63" t="s">
+      <c r="H92" s="62" t="s">
         <v>322</v>
       </c>
-      <c r="I92" s="59"/>
-      <c r="J92" s="59"/>
-      <c r="K92" s="59"/>
+      <c r="I92" s="58"/>
+      <c r="J92" s="58"/>
+      <c r="K92" s="58"/>
     </row>
     <row r="93" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">

--- a/excel/ogrenciler.xlsx
+++ b/excel/ogrenciler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esad\surucu-kursu-app\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC254DBF-6D09-4DCD-9BC3-13D4BE2423FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB73C771-DE6A-4140-8418-6BE41B7702C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="394">
   <si>
     <t>E-SINAV</t>
   </si>
@@ -237,9 +237,6 @@
     <t>NEŞE ŞENTÜRK</t>
   </si>
   <si>
-    <t>EMİNE ÖZTAŞ</t>
-  </si>
-  <si>
     <t>NUMAN TAHA VAROL</t>
   </si>
   <si>
@@ -774,9 +771,6 @@
     <t>GÜLBAHAR AVCI</t>
   </si>
   <si>
-    <t>0538 497 72 67</t>
-  </si>
-  <si>
     <t>0545 856 06 08</t>
   </si>
   <si>
@@ -1222,6 +1216,9 @@
   </si>
   <si>
     <t>0543 885 56 25</t>
+  </si>
+  <si>
+    <t>E SINAV 25 NİSAN DAN SONRA OLACAK</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1403,7 @@
       <charset val="162"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1446,6 +1443,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1583,7 +1586,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1769,15 +1772,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1788,6 +1782,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2120,15 +2129,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="56"/>
       <c r="I1" s="44"/>
       <c r="J1" s="44"/>
@@ -2202,7 +2211,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="52" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I3" s="48">
         <v>9.0299999999999994</v>
@@ -2239,7 +2248,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I4" s="48">
         <v>19.02</v>
@@ -2276,12 +2285,12 @@
         <v>17</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I5" s="48"/>
       <c r="J5" s="48"/>
       <c r="K5" s="60" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="L5" s="44"/>
       <c r="M5" s="44"/>
@@ -2311,7 +2320,7 @@
         <v>19</v>
       </c>
       <c r="H6" s="52" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I6" s="48">
         <v>14.04</v>
@@ -2348,7 +2357,7 @@
         <v>21</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I7" s="48">
         <v>14.04</v>
@@ -2373,7 +2382,7 @@
       <c r="B8" s="59">
         <v>14314192016</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="63" t="s">
         <v>22</v>
       </c>
       <c r="D8" s="48"/>
@@ -2385,7 +2394,7 @@
         <v>23</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I8" s="48">
         <v>3.04</v>
@@ -2393,7 +2402,9 @@
       <c r="J8" s="53">
         <v>0.75</v>
       </c>
-      <c r="K8" s="48"/>
+      <c r="K8" s="49" t="s">
+        <v>393</v>
+      </c>
       <c r="L8" s="44"/>
       <c r="M8" s="44"/>
       <c r="N8" s="44"/>
@@ -2407,7 +2418,7 @@
       <c r="A9" s="45">
         <v>7</v>
       </c>
-      <c r="B9" s="59">
+      <c r="B9" s="72">
         <v>99144164198</v>
       </c>
       <c r="C9" s="21" t="s">
@@ -2417,12 +2428,12 @@
       <c r="E9" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="48"/>
+      <c r="F9" s="49"/>
       <c r="G9" s="55" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I9" s="48">
         <v>26.03</v>
@@ -2444,7 +2455,7 @@
       <c r="A10" s="45">
         <v>8</v>
       </c>
-      <c r="B10" s="48">
+      <c r="B10" s="72">
         <v>32632300470</v>
       </c>
       <c r="C10" s="21" t="s">
@@ -2459,7 +2470,7 @@
         <v>28</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I10" s="48"/>
       <c r="J10" s="48"/>
@@ -2492,7 +2503,7 @@
         <v>30</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I11" s="48">
         <v>14.04</v>
@@ -2514,7 +2525,7 @@
       <c r="A12" s="45">
         <v>10</v>
       </c>
-      <c r="B12" s="48">
+      <c r="B12" s="72">
         <v>10078164894</v>
       </c>
       <c r="C12" s="63" t="s">
@@ -2524,17 +2535,17 @@
       <c r="E12" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="48"/>
+      <c r="F12" s="49"/>
       <c r="G12" s="55" t="s">
         <v>32</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I12" s="48"/>
       <c r="J12" s="48"/>
       <c r="K12" s="49" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L12" s="44"/>
       <c r="M12" s="44"/>
@@ -2549,7 +2560,7 @@
       <c r="A13" s="45">
         <v>11</v>
       </c>
-      <c r="B13" s="48">
+      <c r="B13" s="72">
         <v>12419592328</v>
       </c>
       <c r="C13" s="21" t="s">
@@ -2559,12 +2570,12 @@
       <c r="E13" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="48"/>
+      <c r="F13" s="49"/>
       <c r="G13" s="55" t="s">
         <v>34</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I13" s="48"/>
       <c r="J13" s="48"/>
@@ -2597,7 +2608,7 @@
         <v>36</v>
       </c>
       <c r="H14" s="52" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I14" s="48"/>
       <c r="J14" s="48"/>
@@ -2636,7 +2647,7 @@
       <c r="A16" s="48">
         <v>1</v>
       </c>
-      <c r="B16" s="48">
+      <c r="B16" s="73">
         <v>49627120258</v>
       </c>
       <c r="C16" s="21" t="s">
@@ -2651,7 +2662,7 @@
         <v>39</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I16" s="48"/>
       <c r="J16" s="48"/>
@@ -2669,7 +2680,7 @@
       <c r="A17" s="48">
         <v>2</v>
       </c>
-      <c r="B17" s="48">
+      <c r="B17" s="72">
         <v>14038775274</v>
       </c>
       <c r="C17" s="63" t="s">
@@ -2679,17 +2690,17 @@
       <c r="E17" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="48"/>
+      <c r="F17" s="49"/>
       <c r="G17" s="55" t="s">
         <v>41</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I17" s="48"/>
       <c r="J17" s="48"/>
       <c r="K17" s="49" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -2719,7 +2730,7 @@
         <v>43</v>
       </c>
       <c r="H18" s="52" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="I18" s="48"/>
       <c r="J18" s="48"/>
@@ -2737,7 +2748,7 @@
       <c r="A19" s="48">
         <v>4</v>
       </c>
-      <c r="B19" s="48">
+      <c r="B19" s="72">
         <v>10312320574</v>
       </c>
       <c r="C19" s="63" t="s">
@@ -2747,17 +2758,17 @@
       <c r="E19" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="48"/>
+      <c r="F19" s="49"/>
       <c r="G19" s="55" t="s">
         <v>45</v>
       </c>
       <c r="H19" s="52" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I19" s="48"/>
       <c r="J19" s="48"/>
       <c r="K19" s="49" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -2787,12 +2798,12 @@
         <v>47</v>
       </c>
       <c r="H20" s="52" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I20" s="48"/>
       <c r="J20" s="48"/>
       <c r="K20" s="49" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -2822,7 +2833,7 @@
         <v>49</v>
       </c>
       <c r="H21" s="52" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I21" s="48"/>
       <c r="J21" s="48"/>
@@ -2840,7 +2851,7 @@
       <c r="A22" s="48">
         <v>7</v>
       </c>
-      <c r="B22" s="48">
+      <c r="B22" s="72">
         <v>10042247202</v>
       </c>
       <c r="C22" s="63" t="s">
@@ -2850,17 +2861,17 @@
       <c r="E22" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="48"/>
+      <c r="F22" s="49"/>
       <c r="G22" s="55" t="s">
         <v>51</v>
       </c>
       <c r="H22" s="52" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I22" s="48"/>
       <c r="J22" s="48"/>
       <c r="K22" s="49" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -2875,7 +2886,7 @@
       <c r="A23" s="48">
         <v>8</v>
       </c>
-      <c r="B23" s="48">
+      <c r="B23" s="73">
         <v>11209295852</v>
       </c>
       <c r="C23" s="21" t="s">
@@ -2885,12 +2896,12 @@
       <c r="E23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="48"/>
+      <c r="F23" s="54"/>
       <c r="G23" s="55" t="s">
         <v>53</v>
       </c>
       <c r="H23" s="52" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I23" s="48"/>
       <c r="J23" s="48"/>
@@ -2923,12 +2934,12 @@
         <v>55</v>
       </c>
       <c r="H24" s="52" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I24" s="48"/>
       <c r="J24" s="48"/>
       <c r="K24" s="49" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L24" s="44"/>
       <c r="M24" s="44"/>
@@ -2943,7 +2954,7 @@
       <c r="A25" s="48">
         <v>10</v>
       </c>
-      <c r="B25" s="48">
+      <c r="B25" s="73">
         <v>10242156304</v>
       </c>
       <c r="C25" s="21" t="s">
@@ -2958,7 +2969,7 @@
         <v>57</v>
       </c>
       <c r="H25" s="52" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I25" s="48"/>
       <c r="J25" s="48"/>
@@ -2976,7 +2987,7 @@
       <c r="A26" s="48">
         <v>11</v>
       </c>
-      <c r="B26" s="48">
+      <c r="B26" s="49">
         <v>10688046160</v>
       </c>
       <c r="C26" s="21" t="s">
@@ -2986,12 +2997,12 @@
       <c r="E26" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="48"/>
+      <c r="F26" s="49"/>
       <c r="G26" s="55" t="s">
         <v>59</v>
       </c>
       <c r="H26" s="52" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I26" s="48"/>
       <c r="J26" s="48"/>
@@ -3009,7 +3020,7 @@
       <c r="A27" s="48">
         <v>12</v>
       </c>
-      <c r="B27" s="48">
+      <c r="B27" s="72">
         <v>10051120886</v>
       </c>
       <c r="C27" s="21" t="s">
@@ -3019,12 +3030,12 @@
       <c r="E27" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="48"/>
+      <c r="F27" s="49"/>
       <c r="G27" s="55" t="s">
         <v>61</v>
       </c>
       <c r="H27" s="52" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I27" s="48"/>
       <c r="J27" s="48"/>
@@ -3057,7 +3068,7 @@
         <v>63</v>
       </c>
       <c r="H28" s="52" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I28" s="48"/>
       <c r="J28" s="48"/>
@@ -3100,7 +3111,7 @@
         <v>14347191628</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D30" s="48"/>
       <c r="E30" s="48" t="s">
@@ -3108,10 +3119,10 @@
       </c>
       <c r="F30" s="48"/>
       <c r="G30" s="55" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H30" s="52" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I30" s="48"/>
       <c r="J30" s="48"/>
@@ -3133,7 +3144,7 @@
         <v>14407189688</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D31" s="48"/>
       <c r="E31" s="48" t="s">
@@ -3141,10 +3152,10 @@
       </c>
       <c r="F31" s="48"/>
       <c r="G31" s="55" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H31" s="52" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I31" s="48"/>
       <c r="J31" s="48"/>
@@ -3166,7 +3177,7 @@
         <v>37663356526</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D32" s="48"/>
       <c r="E32" s="48" t="s">
@@ -3174,15 +3185,15 @@
       </c>
       <c r="F32" s="48"/>
       <c r="G32" s="55" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H32" s="52" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I32" s="48"/>
       <c r="J32" s="48"/>
       <c r="K32" s="49" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L32" s="44"/>
       <c r="M32" s="44"/>
@@ -3201,7 +3212,7 @@
         <v>14548183644</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D33" s="48"/>
       <c r="E33" s="48" t="s">
@@ -3209,10 +3220,10 @@
       </c>
       <c r="F33" s="48"/>
       <c r="G33" s="55" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H33" s="52" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I33" s="48"/>
       <c r="J33" s="48"/>
@@ -3234,18 +3245,18 @@
         <v>53743013714</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D34" s="48"/>
       <c r="E34" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="48"/>
+      <c r="F34" s="49"/>
       <c r="G34" s="55" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H34" s="52" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I34" s="48"/>
       <c r="J34" s="48"/>
@@ -3267,18 +3278,18 @@
         <v>12527356416</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D35" s="48"/>
       <c r="E35" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="48"/>
+      <c r="F35" s="49"/>
       <c r="G35" s="55" t="s">
         <v>36</v>
       </c>
       <c r="H35" s="52" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I35" s="48"/>
       <c r="J35" s="48"/>
@@ -3300,18 +3311,18 @@
         <v>19096743784</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D36" s="48"/>
       <c r="E36" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F36" s="48"/>
+      <c r="F36" s="49"/>
       <c r="G36" s="55" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H36" s="52" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I36" s="48"/>
       <c r="J36" s="48"/>
@@ -3333,7 +3344,7 @@
         <v>10054117302</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D37" s="48"/>
       <c r="E37" s="48" t="s">
@@ -3344,7 +3355,7 @@
         <v>49</v>
       </c>
       <c r="H37" s="52" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I37" s="48"/>
       <c r="J37" s="48"/>
@@ -3366,7 +3377,7 @@
         <v>99779406472</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D38" s="48"/>
       <c r="E38" s="48" t="s">
@@ -3374,10 +3385,10 @@
       </c>
       <c r="F38" s="48"/>
       <c r="G38" s="55" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H38" s="52" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I38" s="48"/>
       <c r="J38" s="48"/>
@@ -3399,7 +3410,7 @@
         <v>14237058246</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D39" s="48"/>
       <c r="E39" s="48" t="s">
@@ -3407,10 +3418,10 @@
       </c>
       <c r="F39" s="48"/>
       <c r="G39" s="55" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H39" s="52" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I39" s="48"/>
       <c r="J39" s="48"/>
@@ -3432,18 +3443,18 @@
         <v>10589773516</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D40" s="48"/>
       <c r="E40" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="48"/>
+      <c r="F40" s="49"/>
       <c r="G40" s="55" t="s">
         <v>57</v>
       </c>
       <c r="H40" s="52" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="I40" s="48"/>
       <c r="J40" s="48"/>
@@ -3465,7 +3476,7 @@
         <v>40237046792</v>
       </c>
       <c r="C41" s="63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D41" s="48"/>
       <c r="E41" s="48" t="s">
@@ -3473,15 +3484,15 @@
       </c>
       <c r="F41" s="54"/>
       <c r="G41" s="55" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H41" s="52" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I41" s="48"/>
       <c r="J41" s="48"/>
       <c r="K41" s="49" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L41" s="44"/>
       <c r="M41" s="44"/>
@@ -3500,7 +3511,7 @@
         <v>12523168198</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D42" s="48"/>
       <c r="E42" s="48" t="s">
@@ -3508,10 +3519,10 @@
       </c>
       <c r="F42" s="48"/>
       <c r="G42" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H42" s="52" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I42" s="48"/>
       <c r="J42" s="48"/>
@@ -3533,7 +3544,7 @@
         <v>13243016448</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D43" s="48"/>
       <c r="E43" s="48" t="s">
@@ -3541,10 +3552,10 @@
       </c>
       <c r="F43" s="48"/>
       <c r="G43" s="55" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H43" s="52" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I43" s="48"/>
       <c r="J43" s="48"/>
@@ -3566,18 +3577,18 @@
         <v>28324428676</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D44" s="48"/>
       <c r="E44" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="F44" s="48"/>
+      <c r="F44" s="49"/>
       <c r="G44" s="55" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H44" s="52" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="I44" s="48"/>
       <c r="J44" s="48"/>
@@ -3621,14 +3632,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71"/>
       <c r="G1" s="42"/>
       <c r="H1" s="43"/>
       <c r="I1" s="44"/>
@@ -3665,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="49">
-        <v>12961026456</v>
+        <v>14254194606</v>
       </c>
       <c r="C3" s="50" t="s">
         <v>66</v>
@@ -3674,18 +3685,18 @@
       <c r="E3" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="51" t="s">
-        <v>23</v>
+      <c r="F3" s="54"/>
+      <c r="G3" s="55" t="s">
+        <v>67</v>
       </c>
       <c r="H3" s="52" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I3" s="48">
-        <v>8.01</v>
+        <v>28.01</v>
       </c>
       <c r="J3" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K3" s="48"/>
     </row>
@@ -3694,10 +3705,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="49">
-        <v>14254194606</v>
+        <v>10306113588</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" s="48"/>
       <c r="E4" s="48" t="s">
@@ -3705,16 +3716,16 @@
       </c>
       <c r="F4" s="54"/>
       <c r="G4" s="55" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I4" s="48">
-        <v>28.01</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="J4" s="53">
-        <v>0.75</v>
+        <v>0.80208333333333337</v>
       </c>
       <c r="K4" s="48"/>
     </row>
@@ -3723,7 +3734,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="49">
-        <v>10306113588</v>
+        <v>12787254972</v>
       </c>
       <c r="C5" s="50" t="s">
         <v>69</v>
@@ -3732,18 +3743,18 @@
       <c r="E5" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="54"/>
+      <c r="F5" s="48"/>
       <c r="G5" s="55" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I5" s="48">
-        <v>5.0199999999999996</v>
+        <v>18.02</v>
       </c>
       <c r="J5" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K5" s="48"/>
     </row>
@@ -3752,21 +3763,21 @@
         <v>4</v>
       </c>
       <c r="B6" s="49">
-        <v>12787254972</v>
+        <v>11374289342</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" s="48"/>
       <c r="E6" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="48"/>
+      <c r="F6" s="54"/>
       <c r="G6" s="55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="52" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I6" s="48">
         <v>18.02</v>
@@ -3781,10 +3792,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="49">
-        <v>11374289342</v>
+        <v>19702011528</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="48"/>
       <c r="E7" s="48" t="s">
@@ -3792,10 +3803,10 @@
       </c>
       <c r="F7" s="54"/>
       <c r="G7" s="55" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I7" s="48">
         <v>18.02</v>
@@ -3810,27 +3821,27 @@
         <v>6</v>
       </c>
       <c r="B8" s="49">
-        <v>19702011528</v>
+        <v>14299193176</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8" s="48"/>
       <c r="E8" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="54"/>
+      <c r="F8" s="48"/>
       <c r="G8" s="55" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I8" s="48">
-        <v>18.02</v>
+        <v>19.02</v>
       </c>
       <c r="J8" s="53">
-        <v>0.75</v>
+        <v>0.80208333333333337</v>
       </c>
       <c r="K8" s="48"/>
     </row>
@@ -3839,10 +3850,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="49">
-        <v>14299193176</v>
+        <v>10039248120</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" s="48"/>
       <c r="E9" s="48" t="s">
@@ -3850,13 +3861,13 @@
       </c>
       <c r="F9" s="48"/>
       <c r="G9" s="55" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I9" s="48">
-        <v>19.02</v>
+        <v>23.02</v>
       </c>
       <c r="J9" s="53">
         <v>0.80208333333333337</v>
@@ -3868,10 +3879,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="49">
-        <v>10039248120</v>
+        <v>11323292362</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" s="48"/>
       <c r="E10" s="48" t="s">
@@ -3879,10 +3890,10 @@
       </c>
       <c r="F10" s="48"/>
       <c r="G10" s="55" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I10" s="48">
         <v>23.02</v>
@@ -3897,21 +3908,21 @@
         <v>9</v>
       </c>
       <c r="B11" s="49">
-        <v>11323292362</v>
+        <v>10147121568</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" s="48"/>
       <c r="E11" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="48"/>
+      <c r="F11" s="54"/>
       <c r="G11" s="55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I11" s="48">
         <v>23.02</v>
@@ -3926,10 +3937,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="49">
-        <v>10147121568</v>
+        <v>33668101604</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D12" s="48"/>
       <c r="E12" s="48" t="s">
@@ -3937,10 +3948,10 @@
       </c>
       <c r="F12" s="54"/>
       <c r="G12" s="55" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I12" s="48">
         <v>23.02</v>
@@ -3955,7 +3966,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="49">
-        <v>33668101604</v>
+        <v>11867067624</v>
       </c>
       <c r="C13" s="50" t="s">
         <v>84</v>
@@ -3969,7 +3980,7 @@
         <v>23</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I13" s="48">
         <v>23.02</v>
@@ -3984,7 +3995,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="49">
-        <v>11867067624</v>
+        <v>10031847734</v>
       </c>
       <c r="C14" s="50" t="s">
         <v>85</v>
@@ -3995,10 +4006,10 @@
       </c>
       <c r="F14" s="54"/>
       <c r="G14" s="55" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="H14" s="52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I14" s="48">
         <v>23.02</v>
@@ -4013,7 +4024,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="49">
-        <v>10031847734</v>
+        <v>12985235612</v>
       </c>
       <c r="C15" s="50" t="s">
         <v>86</v>
@@ -4024,10 +4035,10 @@
       </c>
       <c r="F15" s="54"/>
       <c r="G15" s="55" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="H15" s="52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I15" s="48">
         <v>23.02</v>
@@ -4042,24 +4053,24 @@
         <v>14</v>
       </c>
       <c r="B16" s="49">
-        <v>12985235612</v>
+        <v>14791267894</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" s="48"/>
       <c r="E16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="48"/>
+      <c r="F16" s="54"/>
       <c r="G16" s="55" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I16" s="48">
-        <v>23.02</v>
+        <v>25.02</v>
       </c>
       <c r="J16" s="53">
         <v>0.80208333333333337</v>
@@ -4071,28 +4082,24 @@
         <v>15</v>
       </c>
       <c r="B17" s="49">
-        <v>14791267894</v>
+        <v>26996448794</v>
       </c>
       <c r="C17" s="50" t="s">
         <v>89</v>
       </c>
       <c r="D17" s="48"/>
       <c r="E17" s="48" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="F17" s="54"/>
       <c r="G17" s="55" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>259</v>
-      </c>
-      <c r="I17" s="48">
-        <v>25.02</v>
-      </c>
-      <c r="J17" s="53">
-        <v>0.80208333333333337</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
       <c r="K17" s="48"/>
     </row>
     <row r="18" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4100,24 +4107,28 @@
         <v>16</v>
       </c>
       <c r="B18" s="49">
-        <v>26996448794</v>
+        <v>34198316858</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D18" s="48"/>
       <c r="E18" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="54"/>
+        <v>12</v>
+      </c>
+      <c r="F18" s="48"/>
       <c r="G18" s="55" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" s="52" t="s">
-        <v>260</v>
-      </c>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
+        <v>259</v>
+      </c>
+      <c r="I18" s="48">
+        <v>11.03</v>
+      </c>
+      <c r="J18" s="53">
+        <v>0.80208333333333337</v>
+      </c>
       <c r="K18" s="48"/>
     </row>
     <row r="19" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4125,27 +4136,27 @@
         <v>17</v>
       </c>
       <c r="B19" s="49">
-        <v>34198316858</v>
+        <v>16261043632</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" s="48"/>
       <c r="E19" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="48"/>
+      <c r="F19" s="54"/>
       <c r="G19" s="55" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H19" s="52" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I19" s="48">
-        <v>11.03</v>
+        <v>23.03</v>
       </c>
       <c r="J19" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K19" s="48"/>
     </row>
@@ -4154,10 +4165,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="49">
-        <v>16261043632</v>
+        <v>62251054904</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" s="48"/>
       <c r="E20" s="48" t="s">
@@ -4165,10 +4176,10 @@
       </c>
       <c r="F20" s="54"/>
       <c r="G20" s="55" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H20" s="52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I20" s="48">
         <v>23.03</v>
@@ -4183,21 +4194,21 @@
         <v>19</v>
       </c>
       <c r="B21" s="49">
-        <v>62251054904</v>
+        <v>10162209012</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" s="48"/>
       <c r="E21" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="54"/>
+      <c r="F21" s="48"/>
       <c r="G21" s="55" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H21" s="52" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I21" s="48">
         <v>23.03</v>
@@ -4212,21 +4223,21 @@
         <v>20</v>
       </c>
       <c r="B22" s="49">
-        <v>10162209012</v>
+        <v>15247077586</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D22" s="48"/>
       <c r="E22" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="48"/>
+      <c r="F22" s="54"/>
       <c r="G22" s="55" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H22" s="52" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I22" s="48">
         <v>23.03</v>
@@ -4241,10 +4252,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="49">
-        <v>15247077586</v>
+        <v>12484081840</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" s="48"/>
       <c r="E23" s="48" t="s">
@@ -4252,10 +4263,10 @@
       </c>
       <c r="F23" s="54"/>
       <c r="G23" s="55" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H23" s="52" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I23" s="48">
         <v>23.03</v>
@@ -4270,10 +4281,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="49">
-        <v>12484081840</v>
+        <v>10078077392</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D24" s="48"/>
       <c r="E24" s="48" t="s">
@@ -4281,7 +4292,7 @@
       </c>
       <c r="F24" s="54"/>
       <c r="G24" s="55" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="H24" s="52" t="s">
         <v>266</v>
@@ -4299,10 +4310,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="49">
-        <v>11749111162</v>
+        <v>10156079256</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D25" s="48"/>
       <c r="E25" s="48" t="s">
@@ -4310,16 +4321,16 @@
       </c>
       <c r="F25" s="54"/>
       <c r="G25" s="55" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="H25" s="52" t="s">
         <v>267</v>
       </c>
       <c r="I25" s="48">
-        <v>23.03</v>
+        <v>24.03</v>
       </c>
       <c r="J25" s="53">
-        <v>0.75</v>
+        <v>0.80208333333333337</v>
       </c>
       <c r="K25" s="48"/>
     </row>
@@ -4328,10 +4339,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="49">
-        <v>10078077392</v>
+        <v>49288319060</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D26" s="48"/>
       <c r="E26" s="48" t="s">
@@ -4339,16 +4350,16 @@
       </c>
       <c r="F26" s="54"/>
       <c r="G26" s="55" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="H26" s="52" t="s">
         <v>268</v>
       </c>
       <c r="I26" s="48">
-        <v>23.03</v>
+        <v>25.03</v>
       </c>
       <c r="J26" s="53">
-        <v>0.75</v>
+        <v>0.80208333333333337</v>
       </c>
       <c r="K26" s="48"/>
     </row>
@@ -4357,10 +4368,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="49">
-        <v>10156079256</v>
+        <v>19198002550</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D27" s="48"/>
       <c r="E27" s="48" t="s">
@@ -4368,16 +4379,16 @@
       </c>
       <c r="F27" s="54"/>
       <c r="G27" s="55" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="H27" s="52" t="s">
         <v>269</v>
       </c>
       <c r="I27" s="48">
-        <v>24.03</v>
+        <v>26.03</v>
       </c>
       <c r="J27" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K27" s="48"/>
     </row>
@@ -4386,10 +4397,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="49">
-        <v>49288319060</v>
+        <v>14992068672</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D28" s="48"/>
       <c r="E28" s="48" t="s">
@@ -4397,16 +4408,16 @@
       </c>
       <c r="F28" s="54"/>
       <c r="G28" s="55" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H28" s="52" t="s">
         <v>270</v>
       </c>
       <c r="I28" s="48">
-        <v>25.03</v>
+        <v>26.03</v>
       </c>
       <c r="J28" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K28" s="48"/>
     </row>
@@ -4415,10 +4426,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="49">
-        <v>19198002550</v>
+        <v>12649536826</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D29" s="48"/>
       <c r="E29" s="48" t="s">
@@ -4426,7 +4437,7 @@
       </c>
       <c r="F29" s="54"/>
       <c r="G29" s="55" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H29" s="52" t="s">
         <v>271</v>
@@ -4444,10 +4455,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="49">
-        <v>14992068672</v>
+        <v>34123446490</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D30" s="48"/>
       <c r="E30" s="48" t="s">
@@ -4455,7 +4466,7 @@
       </c>
       <c r="F30" s="54"/>
       <c r="G30" s="55" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H30" s="52" t="s">
         <v>272</v>
@@ -4473,10 +4484,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="49">
-        <v>12649536826</v>
+        <v>11144234640</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D31" s="48"/>
       <c r="E31" s="48" t="s">
@@ -4484,7 +4495,7 @@
       </c>
       <c r="F31" s="54"/>
       <c r="G31" s="55" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H31" s="52" t="s">
         <v>273</v>
@@ -4502,10 +4513,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="49">
-        <v>34123446490</v>
+        <v>10015118164</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D32" s="48"/>
       <c r="E32" s="48" t="s">
@@ -4513,7 +4524,7 @@
       </c>
       <c r="F32" s="54"/>
       <c r="G32" s="55" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H32" s="52" t="s">
         <v>274</v>
@@ -4531,10 +4542,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="49">
-        <v>11144234640</v>
+        <v>11482575542</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D33" s="48"/>
       <c r="E33" s="48" t="s">
@@ -4542,7 +4553,7 @@
       </c>
       <c r="F33" s="54"/>
       <c r="G33" s="55" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H33" s="52" t="s">
         <v>275</v>
@@ -4560,10 +4571,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="49">
-        <v>10015118164</v>
+        <v>11144234718</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D34" s="48"/>
       <c r="E34" s="48" t="s">
@@ -4571,7 +4582,7 @@
       </c>
       <c r="F34" s="54"/>
       <c r="G34" s="55" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H34" s="52" t="s">
         <v>276</v>
@@ -4580,7 +4591,7 @@
         <v>26.03</v>
       </c>
       <c r="J34" s="53">
-        <v>0.75</v>
+        <v>0.80208333333333337</v>
       </c>
       <c r="K34" s="48"/>
     </row>
@@ -4589,10 +4600,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="49">
-        <v>11482575542</v>
+        <v>10403070678</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D35" s="48"/>
       <c r="E35" s="48" t="s">
@@ -4600,7 +4611,7 @@
       </c>
       <c r="F35" s="54"/>
       <c r="G35" s="55" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H35" s="52" t="s">
         <v>277</v>
@@ -4609,7 +4620,7 @@
         <v>26.03</v>
       </c>
       <c r="J35" s="53">
-        <v>0.75</v>
+        <v>0.80208333333333337</v>
       </c>
       <c r="K35" s="48"/>
     </row>
@@ -4618,10 +4629,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="49">
-        <v>11144234718</v>
+        <v>10009120968</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D36" s="48"/>
       <c r="E36" s="48" t="s">
@@ -4629,7 +4640,7 @@
       </c>
       <c r="F36" s="54"/>
       <c r="G36" s="55" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="H36" s="52" t="s">
         <v>278</v>
@@ -4638,7 +4649,7 @@
         <v>26.03</v>
       </c>
       <c r="J36" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K36" s="48"/>
     </row>
@@ -4647,10 +4658,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="49">
-        <v>10403070678</v>
+        <v>10051120268</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D37" s="48"/>
       <c r="E37" s="48" t="s">
@@ -4658,7 +4669,7 @@
       </c>
       <c r="F37" s="54"/>
       <c r="G37" s="55" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H37" s="52" t="s">
         <v>279</v>
@@ -4667,7 +4678,7 @@
         <v>26.03</v>
       </c>
       <c r="J37" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K37" s="48"/>
     </row>
@@ -4676,10 +4687,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="49">
-        <v>10009120968</v>
+        <v>13507217994</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D38" s="48"/>
       <c r="E38" s="48" t="s">
@@ -4687,7 +4698,7 @@
       </c>
       <c r="F38" s="54"/>
       <c r="G38" s="55" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="H38" s="52" t="s">
         <v>280</v>
@@ -4705,10 +4716,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="49">
-        <v>10051120268</v>
+        <v>12068013786</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D39" s="48"/>
       <c r="E39" s="48" t="s">
@@ -4716,7 +4727,7 @@
       </c>
       <c r="F39" s="54"/>
       <c r="G39" s="55" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="H39" s="52" t="s">
         <v>281</v>
@@ -4734,10 +4745,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="49">
-        <v>13507217994</v>
+        <v>14377140894</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D40" s="48"/>
       <c r="E40" s="48" t="s">
@@ -4745,7 +4756,7 @@
       </c>
       <c r="F40" s="54"/>
       <c r="G40" s="55" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H40" s="52" t="s">
         <v>282</v>
@@ -4754,7 +4765,7 @@
         <v>26.03</v>
       </c>
       <c r="J40" s="53">
-        <v>0.75</v>
+        <v>0.80208333333333337</v>
       </c>
       <c r="K40" s="48"/>
     </row>
@@ -4763,10 +4774,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="49">
-        <v>12068013786</v>
+        <v>14695010084</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D41" s="48"/>
       <c r="E41" s="48" t="s">
@@ -4774,7 +4785,7 @@
       </c>
       <c r="F41" s="54"/>
       <c r="G41" s="55" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="H41" s="52" t="s">
         <v>283</v>
@@ -4783,7 +4794,7 @@
         <v>26.03</v>
       </c>
       <c r="J41" s="53">
-        <v>0.75</v>
+        <v>0.80208333333333337</v>
       </c>
       <c r="K41" s="48"/>
     </row>
@@ -4792,10 +4803,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="49">
-        <v>14377140894</v>
+        <v>10048117608</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D42" s="48"/>
       <c r="E42" s="48" t="s">
@@ -4803,16 +4814,16 @@
       </c>
       <c r="F42" s="54"/>
       <c r="G42" s="55" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H42" s="52" t="s">
         <v>284</v>
       </c>
       <c r="I42" s="48">
-        <v>26.03</v>
+        <v>31.03</v>
       </c>
       <c r="J42" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K42" s="48"/>
     </row>
@@ -4821,10 +4832,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="49">
-        <v>14695010084</v>
+        <v>23336716810</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D43" s="48"/>
       <c r="E43" s="48" t="s">
@@ -4832,16 +4843,16 @@
       </c>
       <c r="F43" s="54"/>
       <c r="G43" s="55" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="H43" s="52" t="s">
         <v>285</v>
       </c>
       <c r="I43" s="48">
-        <v>26.03</v>
+        <v>31.03</v>
       </c>
       <c r="J43" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K43" s="48"/>
     </row>
@@ -4850,10 +4861,10 @@
         <v>42</v>
       </c>
       <c r="B44" s="49">
-        <v>10048117608</v>
+        <v>11734411192</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D44" s="48"/>
       <c r="E44" s="48" t="s">
@@ -4861,7 +4872,7 @@
       </c>
       <c r="F44" s="54"/>
       <c r="G44" s="55" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="H44" s="52" t="s">
         <v>286</v>
@@ -4879,10 +4890,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="49">
-        <v>23336716810</v>
+        <v>14449188076</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D45" s="48"/>
       <c r="E45" s="48" t="s">
@@ -4890,7 +4901,7 @@
       </c>
       <c r="F45" s="54"/>
       <c r="G45" s="55" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="H45" s="52" t="s">
         <v>287</v>
@@ -4908,10 +4919,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="49">
-        <v>11734411192</v>
+        <v>11108938898</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D46" s="48"/>
       <c r="E46" s="48" t="s">
@@ -4919,7 +4930,7 @@
       </c>
       <c r="F46" s="54"/>
       <c r="G46" s="55" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="H46" s="52" t="s">
         <v>288</v>
@@ -4937,10 +4948,10 @@
         <v>45</v>
       </c>
       <c r="B47" s="49">
-        <v>14449188076</v>
+        <v>14458187930</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D47" s="48"/>
       <c r="E47" s="48" t="s">
@@ -4948,7 +4959,7 @@
       </c>
       <c r="F47" s="54"/>
       <c r="G47" s="55" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H47" s="52" t="s">
         <v>289</v>
@@ -4966,10 +4977,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="49">
-        <v>11108938898</v>
+        <v>10271074204</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D48" s="48"/>
       <c r="E48" s="48" t="s">
@@ -4977,7 +4988,7 @@
       </c>
       <c r="F48" s="54"/>
       <c r="G48" s="55" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="H48" s="52" t="s">
         <v>290</v>
@@ -4995,10 +5006,10 @@
         <v>47</v>
       </c>
       <c r="B49" s="49">
-        <v>14458187930</v>
+        <v>31768855328</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D49" s="48"/>
       <c r="E49" s="48" t="s">
@@ -5006,7 +5017,7 @@
       </c>
       <c r="F49" s="54"/>
       <c r="G49" s="55" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="H49" s="52" t="s">
         <v>291</v>
@@ -5024,10 +5035,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="49">
-        <v>10271074204</v>
+        <v>29573323330</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D50" s="48"/>
       <c r="E50" s="48" t="s">
@@ -5035,7 +5046,7 @@
       </c>
       <c r="F50" s="54"/>
       <c r="G50" s="55" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="H50" s="52" t="s">
         <v>292</v>
@@ -5053,28 +5064,24 @@
         <v>49</v>
       </c>
       <c r="B51" s="49">
-        <v>31768855328</v>
+        <v>10300318804</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D51" s="48"/>
       <c r="E51" s="48" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="F51" s="54"/>
       <c r="G51" s="55" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="H51" s="52" t="s">
         <v>293</v>
       </c>
-      <c r="I51" s="48">
-        <v>31.03</v>
-      </c>
-      <c r="J51" s="53">
-        <v>0.75</v>
-      </c>
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
       <c r="K51" s="48"/>
     </row>
     <row r="52" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5082,28 +5089,24 @@
         <v>50</v>
       </c>
       <c r="B52" s="49">
-        <v>29573323330</v>
+        <v>15505896638</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D52" s="48"/>
       <c r="E52" s="48" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="F52" s="54"/>
       <c r="G52" s="55" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="H52" s="52" t="s">
         <v>294</v>
       </c>
-      <c r="I52" s="48">
-        <v>31.03</v>
-      </c>
-      <c r="J52" s="53">
-        <v>0.75</v>
-      </c>
+      <c r="I52" s="48"/>
+      <c r="J52" s="48"/>
       <c r="K52" s="48"/>
     </row>
     <row r="53" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5111,18 +5114,18 @@
         <v>51</v>
       </c>
       <c r="B53" s="49">
-        <v>10300318804</v>
+        <v>17960854932</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D53" s="48"/>
       <c r="E53" s="48" t="s">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="F53" s="54"/>
       <c r="G53" s="55" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H53" s="52" t="s">
         <v>295</v>
@@ -5132,54 +5135,30 @@
       <c r="K53" s="48"/>
     </row>
     <row r="54" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="48">
-        <v>52</v>
-      </c>
-      <c r="B54" s="49">
-        <v>15505896638</v>
-      </c>
-      <c r="C54" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="F54" s="54"/>
-      <c r="G54" s="55" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="52" t="s">
-        <v>296</v>
-      </c>
-      <c r="I54" s="48"/>
-      <c r="J54" s="48"/>
-      <c r="K54" s="48"/>
+      <c r="A54" s="44"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="44"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="44"/>
     </row>
     <row r="55" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="48">
-        <v>53</v>
-      </c>
-      <c r="B55" s="49">
-        <v>17960854932</v>
-      </c>
-      <c r="C55" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="F55" s="54"/>
-      <c r="G55" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="H55" s="52" t="s">
-        <v>297</v>
-      </c>
-      <c r="I55" s="48"/>
-      <c r="J55" s="48"/>
-      <c r="K55" s="48"/>
+      <c r="A55" s="44"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="44"/>
     </row>
     <row r="56" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="44"/>
@@ -5208,65 +5187,97 @@
       <c r="K57" s="44"/>
     </row>
     <row r="58" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="44"/>
-      <c r="B58" s="44"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="44"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="43"/>
-      <c r="I58" s="44"/>
-      <c r="J58" s="44"/>
-      <c r="K58" s="44"/>
+      <c r="A58" s="45">
+        <v>1</v>
+      </c>
+      <c r="B58" s="49">
+        <v>15865049750</v>
+      </c>
+      <c r="C58" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="48"/>
+      <c r="G58" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="H58" s="52" t="s">
+        <v>296</v>
+      </c>
+      <c r="I58" s="48"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="48"/>
     </row>
     <row r="59" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="44"/>
-      <c r="B59" s="44"/>
-      <c r="C59" s="43"/>
-      <c r="D59" s="43"/>
-      <c r="E59" s="44"/>
-      <c r="F59" s="44"/>
-      <c r="G59" s="43"/>
-      <c r="H59" s="43"/>
-      <c r="I59" s="44"/>
-      <c r="J59" s="44"/>
-      <c r="K59" s="44"/>
+      <c r="A59" s="45">
+        <v>2</v>
+      </c>
+      <c r="B59" s="49">
+        <v>15616146684</v>
+      </c>
+      <c r="C59" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" s="48"/>
+      <c r="E59" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="48"/>
+      <c r="G59" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="H59" s="52" t="s">
+        <v>297</v>
+      </c>
+      <c r="I59" s="48">
+        <v>16.02</v>
+      </c>
+      <c r="J59" s="53">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="K59" s="48"/>
     </row>
     <row r="60" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B60" s="49">
-        <v>15865049750</v>
+        <v>14300484194</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D60" s="48"/>
       <c r="E60" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="F60" s="48"/>
+      <c r="F60" s="54"/>
       <c r="G60" s="55" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H60" s="52" t="s">
         <v>298</v>
       </c>
-      <c r="I60" s="48"/>
-      <c r="J60" s="48"/>
+      <c r="I60" s="48">
+        <v>18.02</v>
+      </c>
+      <c r="J60" s="53">
+        <v>0.75</v>
+      </c>
       <c r="K60" s="48"/>
     </row>
     <row r="61" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B61" s="49">
-        <v>15616146684</v>
+        <v>29896460262</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D61" s="48"/>
       <c r="E61" s="48" t="s">
@@ -5274,42 +5285,42 @@
       </c>
       <c r="F61" s="48"/>
       <c r="G61" s="55" t="s">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="H61" s="52" t="s">
         <v>299</v>
       </c>
       <c r="I61" s="48">
-        <v>16.02</v>
+        <v>19.02</v>
       </c>
       <c r="J61" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K61" s="48"/>
     </row>
     <row r="62" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B62" s="49">
-        <v>14300484194</v>
+        <v>17633210058</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D62" s="48"/>
       <c r="E62" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="F62" s="54"/>
+      <c r="F62" s="48"/>
       <c r="G62" s="55" t="s">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="H62" s="52" t="s">
         <v>300</v>
       </c>
       <c r="I62" s="48">
-        <v>18.02</v>
+        <v>19.02</v>
       </c>
       <c r="J62" s="53">
         <v>0.75</v>
@@ -5318,21 +5329,21 @@
     </row>
     <row r="63" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B63" s="49">
-        <v>29896460262</v>
+        <v>10169029378</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D63" s="48"/>
       <c r="E63" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="F63" s="48"/>
+      <c r="F63" s="54"/>
       <c r="G63" s="55" t="s">
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="H63" s="52" t="s">
         <v>301</v>
@@ -5341,33 +5352,33 @@
         <v>19.02</v>
       </c>
       <c r="J63" s="53">
-        <v>0.75</v>
+        <v>0.80208333333333337</v>
       </c>
       <c r="K63" s="48"/>
     </row>
     <row r="64" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B64" s="49">
-        <v>17633210058</v>
+        <v>13264143598</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D64" s="48"/>
       <c r="E64" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="F64" s="48"/>
+      <c r="F64" s="54"/>
       <c r="G64" s="55" t="s">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c r="H64" s="52" t="s">
         <v>302</v>
       </c>
       <c r="I64" s="48">
-        <v>19.02</v>
+        <v>23.03</v>
       </c>
       <c r="J64" s="53">
         <v>0.75</v>
@@ -5376,13 +5387,13 @@
     </row>
     <row r="65" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="45">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B65" s="49">
-        <v>10169029378</v>
+        <v>24808561532</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D65" s="48"/>
       <c r="E65" s="48" t="s">
@@ -5390,28 +5401,28 @@
       </c>
       <c r="F65" s="54"/>
       <c r="G65" s="55" t="s">
-        <v>164</v>
+        <v>36</v>
       </c>
       <c r="H65" s="52" t="s">
         <v>303</v>
       </c>
       <c r="I65" s="48">
-        <v>19.02</v>
+        <v>24.03</v>
       </c>
       <c r="J65" s="53">
-        <v>0.80208333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K65" s="48"/>
     </row>
     <row r="66" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="45">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B66" s="49">
-        <v>13264143598</v>
+        <v>22706535594</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D66" s="48"/>
       <c r="E66" s="48" t="s">
@@ -5419,13 +5430,13 @@
       </c>
       <c r="F66" s="54"/>
       <c r="G66" s="55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H66" s="52" t="s">
         <v>304</v>
       </c>
       <c r="I66" s="48">
-        <v>23.03</v>
+        <v>26.03</v>
       </c>
       <c r="J66" s="53">
         <v>0.75</v>
@@ -5434,13 +5445,13 @@
     </row>
     <row r="67" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B67" s="49">
-        <v>24808561532</v>
+        <v>11899063052</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D67" s="48"/>
       <c r="E67" s="48" t="s">
@@ -5448,13 +5459,13 @@
       </c>
       <c r="F67" s="54"/>
       <c r="G67" s="55" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H67" s="52" t="s">
         <v>305</v>
       </c>
       <c r="I67" s="48">
-        <v>24.03</v>
+        <v>26.03</v>
       </c>
       <c r="J67" s="53">
         <v>0.75</v>
@@ -5463,13 +5474,13 @@
     </row>
     <row r="68" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="45">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B68" s="49">
-        <v>22706535594</v>
+        <v>11230082704</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D68" s="48"/>
       <c r="E68" s="48" t="s">
@@ -5477,7 +5488,7 @@
       </c>
       <c r="F68" s="54"/>
       <c r="G68" s="55" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H68" s="52" t="s">
         <v>306</v>
@@ -5492,13 +5503,13 @@
     </row>
     <row r="69" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="45">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B69" s="49">
-        <v>11899063052</v>
+        <v>11407300792</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D69" s="48"/>
       <c r="E69" s="48" t="s">
@@ -5506,7 +5517,7 @@
       </c>
       <c r="F69" s="54"/>
       <c r="G69" s="55" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H69" s="52" t="s">
         <v>307</v>
@@ -5521,13 +5532,13 @@
     </row>
     <row r="70" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="45">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B70" s="49">
-        <v>11230082704</v>
+        <v>11221210932</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D70" s="48"/>
       <c r="E70" s="48" t="s">
@@ -5535,7 +5546,7 @@
       </c>
       <c r="F70" s="54"/>
       <c r="G70" s="55" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H70" s="52" t="s">
         <v>308</v>
@@ -5550,13 +5561,13 @@
     </row>
     <row r="71" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="45">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B71" s="49">
-        <v>11407300792</v>
+        <v>13327145668</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D71" s="48"/>
       <c r="E71" s="48" t="s">
@@ -5564,7 +5575,7 @@
       </c>
       <c r="F71" s="54"/>
       <c r="G71" s="55" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H71" s="52" t="s">
         <v>309</v>
@@ -5579,13 +5590,13 @@
     </row>
     <row r="72" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="45">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B72" s="49">
-        <v>11221210932</v>
+        <v>15853063102</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D72" s="48"/>
       <c r="E72" s="48" t="s">
@@ -5593,7 +5604,7 @@
       </c>
       <c r="F72" s="54"/>
       <c r="G72" s="55" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="H72" s="52" t="s">
         <v>310</v>
@@ -5608,13 +5619,13 @@
     </row>
     <row r="73" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="45">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B73" s="49">
-        <v>13327145668</v>
+        <v>12748032816</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D73" s="48"/>
       <c r="E73" s="48" t="s">
@@ -5622,7 +5633,7 @@
       </c>
       <c r="F73" s="54"/>
       <c r="G73" s="55" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H73" s="52" t="s">
         <v>311</v>
@@ -5631,19 +5642,19 @@
         <v>26.03</v>
       </c>
       <c r="J73" s="53">
-        <v>0.75</v>
+        <v>0.80208333333333337</v>
       </c>
       <c r="K73" s="48"/>
     </row>
     <row r="74" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="45">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B74" s="49">
-        <v>15853063102</v>
+        <v>38050348056</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D74" s="48"/>
       <c r="E74" s="48" t="s">
@@ -5651,13 +5662,13 @@
       </c>
       <c r="F74" s="54"/>
       <c r="G74" s="55" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="H74" s="52" t="s">
         <v>312</v>
       </c>
       <c r="I74" s="48">
-        <v>26.03</v>
+        <v>31.03</v>
       </c>
       <c r="J74" s="53">
         <v>0.75</v>
@@ -5665,87 +5676,55 @@
       <c r="K74" s="48"/>
     </row>
     <row r="75" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="45">
-        <v>16</v>
+      <c r="A75" s="48">
+        <v>18</v>
       </c>
       <c r="B75" s="49">
-        <v>12748032816</v>
+        <v>11749111162</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="D75" s="48"/>
       <c r="E75" s="48" t="s">
-        <v>25</v>
+        <v>387</v>
       </c>
       <c r="F75" s="54"/>
       <c r="G75" s="55" t="s">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="H75" s="52" t="s">
-        <v>313</v>
-      </c>
-      <c r="I75" s="48">
-        <v>26.03</v>
-      </c>
-      <c r="J75" s="53">
-        <v>0.80208333333333337</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
       <c r="K75" s="48"/>
     </row>
     <row r="76" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="45">
-        <v>17</v>
-      </c>
-      <c r="B76" s="49">
-        <v>38050348056</v>
-      </c>
-      <c r="C76" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="F76" s="54"/>
-      <c r="G76" s="55" t="s">
-        <v>184</v>
-      </c>
-      <c r="H76" s="52" t="s">
-        <v>314</v>
-      </c>
-      <c r="I76" s="48">
-        <v>31.03</v>
-      </c>
-      <c r="J76" s="53">
-        <v>0.75</v>
-      </c>
-      <c r="K76" s="48"/>
+      <c r="A76" s="44"/>
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="44"/>
+      <c r="E76" s="44"/>
+      <c r="F76" s="44"/>
+      <c r="G76" s="44"/>
+      <c r="H76" s="44"/>
+      <c r="I76" s="44"/>
+      <c r="J76" s="44"/>
+      <c r="K76" s="44"/>
     </row>
     <row r="77" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="48">
-        <v>18</v>
-      </c>
-      <c r="B77" s="49">
-        <v>11749111162</v>
-      </c>
-      <c r="C77" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="D77" s="48"/>
-      <c r="E77" s="48" t="s">
-        <v>389</v>
-      </c>
-      <c r="F77" s="54"/>
-      <c r="G77" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="H77" s="52" t="s">
-        <v>267</v>
-      </c>
-      <c r="I77" s="48"/>
-      <c r="J77" s="48"/>
-      <c r="K77" s="48"/>
+      <c r="A77" s="44"/>
+      <c r="B77" s="44"/>
+      <c r="C77" s="44"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="44"/>
+      <c r="G77" s="44"/>
+      <c r="H77" s="44"/>
+      <c r="I77" s="44"/>
+      <c r="J77" s="44"/>
+      <c r="K77" s="44"/>
     </row>
     <row r="78" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="44"/>
@@ -5787,40 +5766,72 @@
       <c r="K80" s="44"/>
     </row>
     <row r="81" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="44"/>
-      <c r="B81" s="44"/>
-      <c r="C81" s="44"/>
-      <c r="D81" s="44"/>
-      <c r="E81" s="44"/>
-      <c r="F81" s="44"/>
-      <c r="G81" s="44"/>
-      <c r="H81" s="44"/>
-      <c r="I81" s="44"/>
-      <c r="J81" s="44"/>
-      <c r="K81" s="44"/>
+      <c r="A81" s="48">
+        <v>1</v>
+      </c>
+      <c r="B81" s="49">
+        <v>36583309018</v>
+      </c>
+      <c r="C81" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="D81" s="48"/>
+      <c r="E81" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" s="54"/>
+      <c r="G81" s="55" t="s">
+        <v>185</v>
+      </c>
+      <c r="H81" s="52" t="s">
+        <v>313</v>
+      </c>
+      <c r="I81" s="48">
+        <v>23.03</v>
+      </c>
+      <c r="J81" s="53">
+        <v>0.75</v>
+      </c>
+      <c r="K81" s="48"/>
     </row>
     <row r="82" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="44"/>
-      <c r="B82" s="44"/>
-      <c r="C82" s="44"/>
-      <c r="D82" s="44"/>
-      <c r="E82" s="44"/>
-      <c r="F82" s="44"/>
-      <c r="G82" s="44"/>
-      <c r="H82" s="44"/>
-      <c r="I82" s="44"/>
-      <c r="J82" s="44"/>
-      <c r="K82" s="44"/>
+      <c r="A82" s="48">
+        <v>2</v>
+      </c>
+      <c r="B82" s="49">
+        <v>13417007722</v>
+      </c>
+      <c r="C82" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="D82" s="48"/>
+      <c r="E82" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="F82" s="54"/>
+      <c r="G82" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="H82" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="I82" s="48">
+        <v>26.03</v>
+      </c>
+      <c r="J82" s="53">
+        <v>0.75</v>
+      </c>
+      <c r="K82" s="48"/>
     </row>
     <row r="83" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="48">
-        <v>1</v>
+      <c r="A83" s="45">
+        <v>3</v>
       </c>
       <c r="B83" s="49">
-        <v>36583309018</v>
+        <v>16239007772</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D83" s="48"/>
       <c r="E83" s="48" t="s">
@@ -5828,13 +5839,13 @@
       </c>
       <c r="F83" s="54"/>
       <c r="G83" s="55" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H83" s="52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I83" s="48">
-        <v>23.03</v>
+        <v>31.03</v>
       </c>
       <c r="J83" s="53">
         <v>0.75</v>
@@ -5842,62 +5853,30 @@
       <c r="K83" s="48"/>
     </row>
     <row r="84" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="48">
-        <v>2</v>
-      </c>
-      <c r="B84" s="49">
-        <v>13417007722</v>
-      </c>
-      <c r="C84" s="50" t="s">
-        <v>187</v>
-      </c>
-      <c r="D84" s="48"/>
-      <c r="E84" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="F84" s="54"/>
-      <c r="G84" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="H84" s="52" t="s">
-        <v>189</v>
-      </c>
-      <c r="I84" s="48">
-        <v>26.03</v>
-      </c>
-      <c r="J84" s="53">
-        <v>0.75</v>
-      </c>
-      <c r="K84" s="48"/>
+      <c r="A84" s="44"/>
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="44"/>
+      <c r="J84" s="44"/>
+      <c r="K84" s="44"/>
     </row>
     <row r="85" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="45">
-        <v>3</v>
-      </c>
-      <c r="B85" s="49">
-        <v>16239007772</v>
-      </c>
-      <c r="C85" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="D85" s="48"/>
-      <c r="E85" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="F85" s="54"/>
-      <c r="G85" s="55" t="s">
-        <v>191</v>
-      </c>
-      <c r="H85" s="52" t="s">
-        <v>316</v>
-      </c>
-      <c r="I85" s="48">
-        <v>31.03</v>
-      </c>
-      <c r="J85" s="53">
-        <v>0.75</v>
-      </c>
-      <c r="K85" s="48"/>
+      <c r="A85" s="44"/>
+      <c r="B85" s="44"/>
+      <c r="C85" s="44"/>
+      <c r="D85" s="44"/>
+      <c r="E85" s="44"/>
+      <c r="F85" s="44"/>
+      <c r="G85" s="44"/>
+      <c r="H85" s="44"/>
+      <c r="I85" s="44"/>
+      <c r="J85" s="44"/>
+      <c r="K85" s="44"/>
     </row>
     <row r="86" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="44"/>
@@ -5939,48 +5918,76 @@
       <c r="K88" s="44"/>
     </row>
     <row r="89" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="44"/>
-      <c r="B89" s="44"/>
-      <c r="C89" s="44"/>
-      <c r="D89" s="44"/>
-      <c r="E89" s="44"/>
-      <c r="F89" s="44"/>
-      <c r="G89" s="44"/>
-      <c r="H89" s="44"/>
-      <c r="I89" s="44"/>
-      <c r="J89" s="44"/>
-      <c r="K89" s="44"/>
+      <c r="A89" s="48">
+        <v>1</v>
+      </c>
+      <c r="B89" s="49">
+        <v>10377141756</v>
+      </c>
+      <c r="C89" s="50" t="s">
+        <v>191</v>
+      </c>
+      <c r="D89" s="48"/>
+      <c r="E89" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="F89" s="54"/>
+      <c r="G89" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="H89" s="52" t="s">
+        <v>315</v>
+      </c>
+      <c r="I89" s="48"/>
+      <c r="J89" s="48"/>
+      <c r="K89" s="48"/>
     </row>
     <row r="90" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="44"/>
-      <c r="B90" s="44"/>
-      <c r="C90" s="44"/>
-      <c r="D90" s="44"/>
-      <c r="E90" s="44"/>
-      <c r="F90" s="44"/>
-      <c r="G90" s="44"/>
-      <c r="H90" s="44"/>
-      <c r="I90" s="44"/>
-      <c r="J90" s="44"/>
-      <c r="K90" s="44"/>
+      <c r="A90" s="45">
+        <v>2</v>
+      </c>
+      <c r="B90" s="49">
+        <v>11579367166</v>
+      </c>
+      <c r="C90" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="D90" s="48"/>
+      <c r="E90" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="F90" s="48"/>
+      <c r="G90" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="H90" s="52" t="s">
+        <v>316</v>
+      </c>
+      <c r="I90" s="48">
+        <v>31.03</v>
+      </c>
+      <c r="J90" s="53">
+        <v>0.75</v>
+      </c>
+      <c r="K90" s="48"/>
     </row>
     <row r="91" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B91" s="49">
-        <v>10377141756</v>
+        <v>12397043324</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D91" s="48"/>
       <c r="E91" s="48" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F91" s="54"/>
       <c r="G91" s="55" t="s">
-        <v>194</v>
+        <v>23</v>
       </c>
       <c r="H91" s="52" t="s">
         <v>317</v>
@@ -5990,54 +5997,50 @@
       <c r="K91" s="48"/>
     </row>
     <row r="92" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="45">
-        <v>2</v>
+      <c r="A92" s="48">
+        <v>4</v>
       </c>
       <c r="B92" s="49">
-        <v>11579367166</v>
+        <v>10042245468</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D92" s="48"/>
       <c r="E92" s="48" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F92" s="48"/>
       <c r="G92" s="55" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H92" s="52" t="s">
         <v>318</v>
       </c>
-      <c r="I92" s="48">
-        <v>31.03</v>
-      </c>
-      <c r="J92" s="53">
-        <v>0.75</v>
-      </c>
+      <c r="I92" s="48"/>
+      <c r="J92" s="48"/>
       <c r="K92" s="48"/>
     </row>
     <row r="93" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B93" s="49">
-        <v>12397043324</v>
+        <v>11070083640</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>198</v>
+        <v>388</v>
       </c>
       <c r="D93" s="48"/>
       <c r="E93" s="48" t="s">
-        <v>193</v>
-      </c>
-      <c r="F93" s="54"/>
-      <c r="G93" s="55" t="s">
-        <v>23</v>
+        <v>192</v>
+      </c>
+      <c r="F93" s="48"/>
+      <c r="G93" s="51" t="s">
+        <v>389</v>
       </c>
       <c r="H93" s="52" t="s">
-        <v>319</v>
+        <v>390</v>
       </c>
       <c r="I93" s="48"/>
       <c r="J93" s="48"/>
@@ -6045,24 +6048,24 @@
     </row>
     <row r="94" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B94" s="49">
-        <v>10042245468</v>
+        <v>10027246350</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>199</v>
+        <v>391</v>
       </c>
       <c r="D94" s="48"/>
       <c r="E94" s="48" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F94" s="48"/>
-      <c r="G94" s="55" t="s">
-        <v>200</v>
+      <c r="G94" s="51" t="s">
+        <v>389</v>
       </c>
       <c r="H94" s="52" t="s">
-        <v>320</v>
+        <v>392</v>
       </c>
       <c r="I94" s="48"/>
       <c r="J94" s="48"/>
@@ -6076,18 +6079,18 @@
         <v>11070083640</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D95" s="48"/>
       <c r="E95" s="48" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F95" s="48"/>
       <c r="G95" s="51" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H95" s="52" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I95" s="48"/>
       <c r="J95" s="48"/>
@@ -6101,18 +6104,18 @@
         <v>10027246350</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D96" s="48"/>
       <c r="E96" s="48" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F96" s="48"/>
       <c r="G96" s="51" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H96" s="52" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I96" s="48"/>
       <c r="J96" s="48"/>
@@ -6157,43 +6160,43 @@
         <v>3</v>
       </c>
       <c r="D1" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="F1" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="G1" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="H1" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="I1" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="J1" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="K1" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="L1" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="M1" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="N1" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="O1" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="O1" s="29" t="s">
+      <c r="P1" s="29" t="s">
         <v>212</v>
-      </c>
-      <c r="P1" s="29" t="s">
-        <v>213</v>
       </c>
       <c r="Q1" s="30"/>
     </row>
@@ -6205,38 +6208,38 @@
         <v>10717552334</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D2" s="35"/>
       <c r="E2" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J2" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M2" s="33"/>
       <c r="N2" s="33"/>
       <c r="O2" s="33"/>
       <c r="P2" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q2" s="30"/>
     </row>
@@ -6246,32 +6249,32 @@
       </c>
       <c r="B3" s="31"/>
       <c r="C3" s="32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I3" s="33"/>
       <c r="J3" s="33"/>
       <c r="K3" s="33"/>
       <c r="L3" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M3" s="33"/>
       <c r="N3" s="33"/>
       <c r="O3" s="33"/>
       <c r="P3" s="34" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q3" s="30"/>
     </row>
@@ -6281,38 +6284,38 @@
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D4" s="35"/>
       <c r="E4" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M4" s="33"/>
       <c r="N4" s="33"/>
       <c r="O4" s="33"/>
       <c r="P4" s="34" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q4" s="30"/>
     </row>
@@ -13908,41 +13911,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
+      <c r="A1" s="65" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>241</v>
-      </c>
       <c r="E3" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="F3" s="19" t="s">
         <v>220</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -13950,11 +13953,11 @@
         <v>1</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="26">
@@ -13966,11 +13969,11 @@
         <v>2</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="26">
@@ -13982,11 +13985,11 @@
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E6" s="22"/>
       <c r="F6" s="26">
@@ -13998,12 +14001,12 @@
         <v>4</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
       <c r="E7" s="22" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F7" s="26">
         <v>46122</v>
@@ -14014,12 +14017,12 @@
         <v>5</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
       <c r="E8" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F8" s="26">
         <v>46122</v>
@@ -14030,12 +14033,12 @@
         <v>6</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
       <c r="E9" s="22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F9" s="26">
         <v>46118</v>
@@ -14046,12 +14049,12 @@
         <v>7</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
       <c r="E10" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F10" s="26">
         <v>46118</v>
@@ -14062,12 +14065,12 @@
         <v>8</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
       <c r="E11" s="22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F11" s="26">
         <v>46119</v>
@@ -14078,12 +14081,12 @@
         <v>9</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F12" s="26">
         <v>46118</v>
@@ -14094,12 +14097,12 @@
         <v>10</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
       <c r="E13" s="22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F13" s="26">
         <v>46119</v>
@@ -14110,12 +14113,12 @@
         <v>11</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
       <c r="E14" s="22" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F14" s="26">
         <v>46119</v>
@@ -14126,12 +14129,12 @@
         <v>12</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
       <c r="E15" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F15" s="26">
         <v>46118</v>
@@ -14142,11 +14145,11 @@
         <v>13</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C16" s="21"/>
       <c r="D16" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="26">
@@ -14158,12 +14161,12 @@
         <v>14</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
       <c r="E17" s="22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F17" s="26">
         <v>46118</v>
@@ -14174,12 +14177,12 @@
         <v>15</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C18" s="21"/>
       <c r="D18" s="21"/>
       <c r="E18" s="22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F18" s="26">
         <v>46122</v>
@@ -14190,11 +14193,11 @@
         <v>16</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C19" s="21"/>
       <c r="D19" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="26">
@@ -14206,11 +14209,11 @@
         <v>17</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="21"/>
       <c r="D20" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="26">
@@ -14222,11 +14225,11 @@
         <v>18</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C21" s="21"/>
       <c r="D21" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="26">
@@ -14238,12 +14241,12 @@
         <v>19</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F22" s="26">
         <v>46118</v>
@@ -14254,11 +14257,11 @@
         <v>20</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C23" s="21"/>
       <c r="D23" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="26">
@@ -14274,7 +14277,7 @@
       </c>
       <c r="C24" s="21"/>
       <c r="D24" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="26">
@@ -14286,11 +14289,11 @@
         <v>22</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="21"/>
       <c r="D25" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="26">
@@ -14302,11 +14305,11 @@
         <v>23</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C26" s="21"/>
       <c r="D26" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E26" s="22"/>
       <c r="F26" s="26">
@@ -14318,11 +14321,11 @@
         <v>24</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="21"/>
       <c r="D27" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="26">
@@ -14334,11 +14337,11 @@
         <v>25</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" s="21"/>
       <c r="D28" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="26">
@@ -14350,11 +14353,11 @@
         <v>26</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="26">
@@ -14366,11 +14369,11 @@
         <v>27</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C30" s="21"/>
       <c r="D30" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="26">
@@ -14382,11 +14385,11 @@
         <v>28</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="26">
@@ -14398,11 +14401,11 @@
         <v>29</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C32" s="21"/>
       <c r="D32" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="26">
@@ -14414,11 +14417,11 @@
         <v>30</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C33" s="21"/>
       <c r="D33" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="26">
@@ -14430,11 +14433,11 @@
         <v>31</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="26">
@@ -14446,11 +14449,11 @@
         <v>32</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="26">
@@ -14462,11 +14465,11 @@
         <v>33</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C36" s="21"/>
       <c r="D36" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="26">
@@ -14478,11 +14481,11 @@
         <v>34</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C37" s="21"/>
       <c r="D37" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="26">
@@ -14494,11 +14497,11 @@
         <v>35</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C38" s="21"/>
       <c r="D38" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="26">
@@ -14513,7 +14516,7 @@
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
       <c r="E39" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F39" s="26"/>
     </row>
@@ -14525,7 +14528,7 @@
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
       <c r="E40" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F40" s="26"/>
     </row>
@@ -14537,7 +14540,7 @@
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F41" s="26"/>
     </row>
@@ -14549,7 +14552,7 @@
       <c r="C42" s="21"/>
       <c r="D42" s="21"/>
       <c r="E42" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F42" s="26"/>
     </row>
@@ -14561,7 +14564,7 @@
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
       <c r="E43" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F43" s="26"/>
     </row>
@@ -14573,7 +14576,7 @@
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
       <c r="E44" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F44" s="26"/>
     </row>
@@ -14585,7 +14588,7 @@
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
       <c r="E45" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F45" s="26"/>
     </row>
@@ -14597,7 +14600,7 @@
       <c r="C46" s="23"/>
       <c r="D46" s="23"/>
       <c r="E46" s="24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F46" s="25">
         <v>213</v>

--- a/excel/ogrenciler.xlsx
+++ b/excel/ogrenciler.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB73C771-DE6A-4140-8418-6BE41B7702C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E-SINAV " sheetId="182" r:id="rId1"/>
@@ -1772,6 +1772,12 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1791,12 +1797,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2129,15 +2129,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="56"/>
       <c r="I1" s="44"/>
       <c r="J1" s="44"/>
@@ -2418,7 +2418,7 @@
       <c r="A9" s="45">
         <v>7</v>
       </c>
-      <c r="B9" s="72">
+      <c r="B9" s="65">
         <v>99144164198</v>
       </c>
       <c r="C9" s="21" t="s">
@@ -2455,7 +2455,7 @@
       <c r="A10" s="45">
         <v>8</v>
       </c>
-      <c r="B10" s="72">
+      <c r="B10" s="65">
         <v>32632300470</v>
       </c>
       <c r="C10" s="21" t="s">
@@ -2525,7 +2525,7 @@
       <c r="A12" s="45">
         <v>10</v>
       </c>
-      <c r="B12" s="72">
+      <c r="B12" s="65">
         <v>10078164894</v>
       </c>
       <c r="C12" s="63" t="s">
@@ -2560,7 +2560,7 @@
       <c r="A13" s="45">
         <v>11</v>
       </c>
-      <c r="B13" s="72">
+      <c r="B13" s="65">
         <v>12419592328</v>
       </c>
       <c r="C13" s="21" t="s">
@@ -2647,7 +2647,7 @@
       <c r="A16" s="48">
         <v>1</v>
       </c>
-      <c r="B16" s="73">
+      <c r="B16" s="66">
         <v>49627120258</v>
       </c>
       <c r="C16" s="21" t="s">
@@ -2680,7 +2680,7 @@
       <c r="A17" s="48">
         <v>2</v>
       </c>
-      <c r="B17" s="72">
+      <c r="B17" s="65">
         <v>14038775274</v>
       </c>
       <c r="C17" s="63" t="s">
@@ -2748,7 +2748,7 @@
       <c r="A19" s="48">
         <v>4</v>
       </c>
-      <c r="B19" s="72">
+      <c r="B19" s="65">
         <v>10312320574</v>
       </c>
       <c r="C19" s="63" t="s">
@@ -2851,7 +2851,7 @@
       <c r="A22" s="48">
         <v>7</v>
       </c>
-      <c r="B22" s="72">
+      <c r="B22" s="65">
         <v>10042247202</v>
       </c>
       <c r="C22" s="63" t="s">
@@ -2886,7 +2886,7 @@
       <c r="A23" s="48">
         <v>8</v>
       </c>
-      <c r="B23" s="73">
+      <c r="B23" s="66">
         <v>11209295852</v>
       </c>
       <c r="C23" s="21" t="s">
@@ -2954,7 +2954,7 @@
       <c r="A25" s="48">
         <v>10</v>
       </c>
-      <c r="B25" s="73">
+      <c r="B25" s="66">
         <v>10242156304</v>
       </c>
       <c r="C25" s="21" t="s">
@@ -3020,7 +3020,7 @@
       <c r="A27" s="48">
         <v>12</v>
       </c>
-      <c r="B27" s="72">
+      <c r="B27" s="65">
         <v>10051120886</v>
       </c>
       <c r="C27" s="21" t="s">
@@ -3632,14 +3632,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="71"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="73"/>
       <c r="G1" s="42"/>
       <c r="H1" s="43"/>
       <c r="I1" s="44"/>
@@ -13911,22 +13911,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="67" t="s">
         <v>217</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
+      <c r="A2" s="69"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">

--- a/excel/ogrenciler.xlsx
+++ b/excel/ogrenciler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esad\surucu-kursu-app\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB73C771-DE6A-4140-8418-6BE41B7702C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4941868A-49C9-47FC-BCC2-95123C5B0220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E-SINAV " sheetId="182" r:id="rId1"/>
@@ -51,9 +51,6 @@
     <t>ADI SOYADI</t>
   </si>
   <si>
-    <t>HAK</t>
-  </si>
-  <si>
     <t>SINIF</t>
   </si>
   <si>
@@ -1219,6 +1216,9 @@
   </si>
   <si>
     <t>E SINAV 25 NİSAN DAN SONRA OLACAK</t>
+  </si>
+  <si>
+    <t>SON ÖDEME</t>
   </si>
 </sst>
 </file>
@@ -2110,7 +2110,7 @@
     <col min="1" max="1" width="5.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="36.28515625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" style="1" customWidth="1"/>
     <col min="7" max="7" width="37.140625" style="4" customWidth="1"/>
@@ -2162,25 +2162,25 @@
         <v>3</v>
       </c>
       <c r="D2" s="45" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="F2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="G2" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="H2" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="58" t="s">
+      <c r="I2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="J2" s="47" t="s">
         <v>9</v>
-      </c>
-      <c r="J2" s="47" t="s">
-        <v>10</v>
       </c>
       <c r="K2" s="44"/>
       <c r="L2" s="44"/>
@@ -2200,18 +2200,18 @@
         <v>12847240198</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="48"/>
       <c r="E3" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" s="48"/>
       <c r="G3" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H3" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I3" s="48">
         <v>9.0299999999999994</v>
@@ -2237,18 +2237,18 @@
         <v>30265941886</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="48"/>
       <c r="E4" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="48"/>
       <c r="G4" s="55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I4" s="48">
         <v>19.02</v>
@@ -2274,23 +2274,23 @@
         <v>22096643282</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="48"/>
       <c r="E5" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="54"/>
       <c r="G5" s="62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I5" s="48"/>
       <c r="J5" s="48"/>
       <c r="K5" s="60" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L5" s="44"/>
       <c r="M5" s="44"/>
@@ -2309,18 +2309,18 @@
         <v>11110087492</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="48"/>
       <c r="E6" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="49"/>
       <c r="G6" s="55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" s="52" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I6" s="48">
         <v>14.04</v>
@@ -2346,18 +2346,18 @@
         <v>18115063162</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="48"/>
       <c r="E7" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="54"/>
       <c r="G7" s="55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I7" s="48">
         <v>14.04</v>
@@ -2383,18 +2383,18 @@
         <v>14314192016</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="48"/>
       <c r="E8" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" s="48"/>
       <c r="G8" s="55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I8" s="48">
         <v>3.04</v>
@@ -2403,7 +2403,7 @@
         <v>0.75</v>
       </c>
       <c r="K8" s="49" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L8" s="44"/>
       <c r="M8" s="44"/>
@@ -2422,18 +2422,18 @@
         <v>99144164198</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="48"/>
       <c r="E9" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" s="49"/>
       <c r="G9" s="55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I9" s="48">
         <v>26.03</v>
@@ -2459,18 +2459,18 @@
         <v>32632300470</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="48"/>
       <c r="E10" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="49"/>
       <c r="G10" s="55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I10" s="48"/>
       <c r="J10" s="48"/>
@@ -2492,18 +2492,18 @@
         <v>10813947058</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="48"/>
       <c r="E11" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" s="54"/>
       <c r="G11" s="55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I11" s="48">
         <v>14.04</v>
@@ -2529,23 +2529,23 @@
         <v>10078164894</v>
       </c>
       <c r="C12" s="63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="48"/>
       <c r="E12" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="49"/>
       <c r="G12" s="55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I12" s="48"/>
       <c r="J12" s="48"/>
       <c r="K12" s="49" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L12" s="44"/>
       <c r="M12" s="44"/>
@@ -2564,18 +2564,18 @@
         <v>12419592328</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="49"/>
       <c r="G13" s="55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I13" s="48"/>
       <c r="J13" s="48"/>
@@ -2597,18 +2597,18 @@
         <v>39115862296</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="48"/>
       <c r="E14" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" s="48"/>
       <c r="G14" s="55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H14" s="52" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I14" s="48"/>
       <c r="J14" s="48"/>
@@ -2651,18 +2651,20 @@
         <v>49627120258</v>
       </c>
       <c r="C16" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="48">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="E16" s="48" t="s">
         <v>37</v>
-      </c>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48" t="s">
-        <v>38</v>
       </c>
       <c r="F16" s="54"/>
       <c r="G16" s="55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I16" s="48"/>
       <c r="J16" s="48"/>
@@ -2684,23 +2686,25 @@
         <v>14038775274</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="48"/>
+        <v>39</v>
+      </c>
+      <c r="D17" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E17" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F17" s="49"/>
       <c r="G17" s="55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I17" s="48"/>
       <c r="J17" s="48"/>
       <c r="K17" s="49" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -2719,18 +2723,20 @@
         <v>14527184440</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="48"/>
+        <v>41</v>
+      </c>
+      <c r="D18" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E18" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" s="48"/>
       <c r="G18" s="55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H18" s="52" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I18" s="48"/>
       <c r="J18" s="48"/>
@@ -2752,23 +2758,25 @@
         <v>10312320574</v>
       </c>
       <c r="C19" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="48"/>
+        <v>43</v>
+      </c>
+      <c r="D19" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E19" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" s="49"/>
       <c r="G19" s="55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H19" s="52" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I19" s="48"/>
       <c r="J19" s="48"/>
       <c r="K19" s="49" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -2787,23 +2795,25 @@
         <v>13351060166</v>
       </c>
       <c r="C20" s="63" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="48"/>
+        <v>45</v>
+      </c>
+      <c r="D20" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E20" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F20" s="48"/>
       <c r="G20" s="55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H20" s="52" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I20" s="48"/>
       <c r="J20" s="48"/>
       <c r="K20" s="49" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -2822,18 +2832,20 @@
         <v>13939204012</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="48"/>
+        <v>47</v>
+      </c>
+      <c r="D21" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E21" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="48"/>
       <c r="G21" s="55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H21" s="52" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I21" s="48"/>
       <c r="J21" s="48"/>
@@ -2855,23 +2867,25 @@
         <v>10042247202</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="48"/>
+        <v>49</v>
+      </c>
+      <c r="D22" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E22" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F22" s="49"/>
       <c r="G22" s="55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H22" s="52" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I22" s="48"/>
       <c r="J22" s="48"/>
       <c r="K22" s="49" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -2890,18 +2904,20 @@
         <v>11209295852</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="48"/>
+        <v>51</v>
+      </c>
+      <c r="D23" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E23" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F23" s="54"/>
       <c r="G23" s="55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H23" s="52" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I23" s="48"/>
       <c r="J23" s="48"/>
@@ -2923,23 +2939,25 @@
         <v>10042247370</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="48"/>
+        <v>53</v>
+      </c>
+      <c r="D24" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E24" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F24" s="48"/>
       <c r="G24" s="55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H24" s="52" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I24" s="48"/>
       <c r="J24" s="48"/>
       <c r="K24" s="49" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L24" s="44"/>
       <c r="M24" s="44"/>
@@ -2958,18 +2976,20 @@
         <v>10242156304</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="48"/>
+        <v>55</v>
+      </c>
+      <c r="D25" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E25" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" s="54"/>
       <c r="G25" s="55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H25" s="52" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I25" s="48"/>
       <c r="J25" s="48"/>
@@ -2991,18 +3011,20 @@
         <v>10688046160</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="48"/>
+        <v>57</v>
+      </c>
+      <c r="D26" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E26" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F26" s="49"/>
       <c r="G26" s="55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H26" s="52" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I26" s="48"/>
       <c r="J26" s="48"/>
@@ -3024,18 +3046,20 @@
         <v>10051120886</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="48"/>
+        <v>59</v>
+      </c>
+      <c r="D27" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E27" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F27" s="49"/>
       <c r="G27" s="55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H27" s="52" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I27" s="48"/>
       <c r="J27" s="48"/>
@@ -3057,18 +3081,20 @@
         <v>38486042184</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="48"/>
+        <v>61</v>
+      </c>
+      <c r="D28" s="48">
+        <v>10.039999999999999</v>
+      </c>
       <c r="E28" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F28" s="48"/>
       <c r="G28" s="55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H28" s="52" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I28" s="48"/>
       <c r="J28" s="48"/>
@@ -3111,18 +3137,20 @@
         <v>14347191628</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="D30" s="48"/>
+        <v>212</v>
+      </c>
+      <c r="D30" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E30" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F30" s="48"/>
       <c r="G30" s="55" t="s">
+        <v>346</v>
+      </c>
+      <c r="H30" s="52" t="s">
         <v>347</v>
-      </c>
-      <c r="H30" s="52" t="s">
-        <v>348</v>
       </c>
       <c r="I30" s="48"/>
       <c r="J30" s="48"/>
@@ -3144,18 +3172,20 @@
         <v>14407189688</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="D31" s="48"/>
+        <v>348</v>
+      </c>
+      <c r="D31" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E31" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" s="48"/>
       <c r="G31" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="H31" s="52" t="s">
         <v>350</v>
-      </c>
-      <c r="H31" s="52" t="s">
-        <v>351</v>
       </c>
       <c r="I31" s="48"/>
       <c r="J31" s="48"/>
@@ -3177,23 +3207,25 @@
         <v>37663356526</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>352</v>
-      </c>
-      <c r="D32" s="48"/>
+        <v>351</v>
+      </c>
+      <c r="D32" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E32" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F32" s="48"/>
       <c r="G32" s="55" t="s">
+        <v>352</v>
+      </c>
+      <c r="H32" s="52" t="s">
         <v>353</v>
-      </c>
-      <c r="H32" s="52" t="s">
-        <v>354</v>
       </c>
       <c r="I32" s="48"/>
       <c r="J32" s="48"/>
       <c r="K32" s="49" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L32" s="44"/>
       <c r="M32" s="44"/>
@@ -3212,18 +3244,20 @@
         <v>14548183644</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="D33" s="48"/>
+        <v>355</v>
+      </c>
+      <c r="D33" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E33" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F33" s="48"/>
       <c r="G33" s="55" t="s">
+        <v>356</v>
+      </c>
+      <c r="H33" s="52" t="s">
         <v>357</v>
-      </c>
-      <c r="H33" s="52" t="s">
-        <v>358</v>
       </c>
       <c r="I33" s="48"/>
       <c r="J33" s="48"/>
@@ -3245,18 +3279,20 @@
         <v>53743013714</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>228</v>
-      </c>
-      <c r="D34" s="48"/>
+        <v>227</v>
+      </c>
+      <c r="D34" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E34" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F34" s="49"/>
       <c r="G34" s="55" t="s">
+        <v>358</v>
+      </c>
+      <c r="H34" s="52" t="s">
         <v>359</v>
-      </c>
-      <c r="H34" s="52" t="s">
-        <v>360</v>
       </c>
       <c r="I34" s="48"/>
       <c r="J34" s="48"/>
@@ -3278,18 +3314,20 @@
         <v>12527356416</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>361</v>
-      </c>
-      <c r="D35" s="48"/>
+        <v>360</v>
+      </c>
+      <c r="D35" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E35" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F35" s="49"/>
       <c r="G35" s="55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H35" s="52" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I35" s="48"/>
       <c r="J35" s="48"/>
@@ -3311,18 +3349,20 @@
         <v>19096743784</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="D36" s="48"/>
+        <v>362</v>
+      </c>
+      <c r="D36" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E36" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F36" s="49"/>
       <c r="G36" s="55" t="s">
+        <v>363</v>
+      </c>
+      <c r="H36" s="52" t="s">
         <v>364</v>
-      </c>
-      <c r="H36" s="52" t="s">
-        <v>365</v>
       </c>
       <c r="I36" s="48"/>
       <c r="J36" s="48"/>
@@ -3344,18 +3384,20 @@
         <v>10054117302</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>366</v>
-      </c>
-      <c r="D37" s="48"/>
+        <v>365</v>
+      </c>
+      <c r="D37" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E37" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" s="48"/>
       <c r="G37" s="55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H37" s="52" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I37" s="48"/>
       <c r="J37" s="48"/>
@@ -3377,18 +3419,20 @@
         <v>99779406472</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="D38" s="48"/>
+        <v>367</v>
+      </c>
+      <c r="D38" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E38" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F38" s="48"/>
       <c r="G38" s="55" t="s">
+        <v>368</v>
+      </c>
+      <c r="H38" s="52" t="s">
         <v>369</v>
-      </c>
-      <c r="H38" s="52" t="s">
-        <v>370</v>
       </c>
       <c r="I38" s="48"/>
       <c r="J38" s="48"/>
@@ -3410,18 +3454,20 @@
         <v>14237058246</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="D39" s="48"/>
+        <v>370</v>
+      </c>
+      <c r="D39" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E39" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F39" s="48"/>
       <c r="G39" s="55" t="s">
+        <v>371</v>
+      </c>
+      <c r="H39" s="52" t="s">
         <v>372</v>
-      </c>
-      <c r="H39" s="52" t="s">
-        <v>373</v>
       </c>
       <c r="I39" s="48"/>
       <c r="J39" s="48"/>
@@ -3443,18 +3489,20 @@
         <v>10589773516</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="D40" s="48"/>
+        <v>373</v>
+      </c>
+      <c r="D40" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E40" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F40" s="49"/>
       <c r="G40" s="55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H40" s="52" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I40" s="48"/>
       <c r="J40" s="48"/>
@@ -3476,23 +3524,25 @@
         <v>40237046792</v>
       </c>
       <c r="C41" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="D41" s="48"/>
+        <v>214</v>
+      </c>
+      <c r="D41" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E41" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F41" s="54"/>
       <c r="G41" s="55" t="s">
+        <v>375</v>
+      </c>
+      <c r="H41" s="52" t="s">
         <v>376</v>
-      </c>
-      <c r="H41" s="52" t="s">
-        <v>377</v>
       </c>
       <c r="I41" s="48"/>
       <c r="J41" s="48"/>
       <c r="K41" s="49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L41" s="44"/>
       <c r="M41" s="44"/>
@@ -3511,18 +3561,20 @@
         <v>12523168198</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="D42" s="48"/>
+        <v>378</v>
+      </c>
+      <c r="D42" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E42" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F42" s="48"/>
       <c r="G42" s="55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H42" s="52" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I42" s="48"/>
       <c r="J42" s="48"/>
@@ -3544,18 +3596,20 @@
         <v>13243016448</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>381</v>
-      </c>
-      <c r="D43" s="48"/>
+        <v>380</v>
+      </c>
+      <c r="D43" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E43" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F43" s="48"/>
       <c r="G43" s="55" t="s">
+        <v>381</v>
+      </c>
+      <c r="H43" s="52" t="s">
         <v>382</v>
-      </c>
-      <c r="H43" s="52" t="s">
-        <v>383</v>
       </c>
       <c r="I43" s="48"/>
       <c r="J43" s="48"/>
@@ -3577,18 +3631,20 @@
         <v>28324428676</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="D44" s="48"/>
+        <v>383</v>
+      </c>
+      <c r="D44" s="48">
+        <v>15.04</v>
+      </c>
       <c r="E44" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F44" s="49"/>
       <c r="G44" s="55" t="s">
+        <v>384</v>
+      </c>
+      <c r="H44" s="52" t="s">
         <v>385</v>
-      </c>
-      <c r="H44" s="52" t="s">
-        <v>386</v>
       </c>
       <c r="I44" s="48"/>
       <c r="J44" s="48"/>
@@ -3633,7 +3689,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="71" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -3658,14 +3714,14 @@
       </c>
       <c r="D2" s="46"/>
       <c r="E2" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="45" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>6</v>
       </c>
       <c r="G2" s="46"/>
       <c r="H2" s="64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2" s="47"/>
       <c r="J2" s="47"/>
@@ -3679,18 +3735,18 @@
         <v>14254194606</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" s="48"/>
       <c r="E3" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" s="54"/>
       <c r="G3" s="55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" s="52" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I3" s="48">
         <v>28.01</v>
@@ -3708,18 +3764,18 @@
         <v>10306113588</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" s="48"/>
       <c r="E4" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="54"/>
       <c r="G4" s="55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I4" s="48">
         <v>5.0199999999999996</v>
@@ -3737,18 +3793,18 @@
         <v>12787254972</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" s="48"/>
       <c r="E5" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="48"/>
       <c r="G5" s="55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I5" s="48">
         <v>18.02</v>
@@ -3766,18 +3822,18 @@
         <v>11374289342</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="48"/>
       <c r="E6" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="54"/>
       <c r="G6" s="55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H6" s="52" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I6" s="48">
         <v>18.02</v>
@@ -3795,18 +3851,18 @@
         <v>19702011528</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D7" s="48"/>
       <c r="E7" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="54"/>
       <c r="G7" s="55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I7" s="48">
         <v>18.02</v>
@@ -3824,18 +3880,18 @@
         <v>14299193176</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="48"/>
       <c r="E8" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" s="48"/>
       <c r="G8" s="55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I8" s="48">
         <v>19.02</v>
@@ -3853,18 +3909,18 @@
         <v>10039248120</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9" s="48"/>
       <c r="E9" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="48"/>
       <c r="G9" s="55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I9" s="48">
         <v>23.02</v>
@@ -3882,18 +3938,18 @@
         <v>11323292362</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D10" s="48"/>
       <c r="E10" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="48"/>
       <c r="G10" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I10" s="48">
         <v>23.02</v>
@@ -3911,18 +3967,18 @@
         <v>10147121568</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D11" s="48"/>
       <c r="E11" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" s="54"/>
       <c r="G11" s="55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I11" s="48">
         <v>23.02</v>
@@ -3940,18 +3996,18 @@
         <v>33668101604</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" s="48"/>
       <c r="E12" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="54"/>
       <c r="G12" s="55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I12" s="48">
         <v>23.02</v>
@@ -3969,18 +4025,18 @@
         <v>11867067624</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="54"/>
       <c r="G13" s="55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I13" s="48">
         <v>23.02</v>
@@ -3998,18 +4054,18 @@
         <v>10031847734</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" s="48"/>
       <c r="E14" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="54"/>
       <c r="G14" s="55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H14" s="52" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I14" s="48">
         <v>23.02</v>
@@ -4027,18 +4083,18 @@
         <v>12985235612</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D15" s="48"/>
       <c r="E15" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F15" s="54"/>
       <c r="G15" s="55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H15" s="52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I15" s="48">
         <v>23.02</v>
@@ -4056,18 +4112,18 @@
         <v>14791267894</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D16" s="48"/>
       <c r="E16" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F16" s="54"/>
       <c r="G16" s="55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I16" s="48">
         <v>25.02</v>
@@ -4085,18 +4141,18 @@
         <v>26996448794</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D17" s="48"/>
       <c r="E17" s="48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F17" s="54"/>
       <c r="G17" s="55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I17" s="48"/>
       <c r="J17" s="48"/>
@@ -4110,18 +4166,18 @@
         <v>34198316858</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D18" s="48"/>
       <c r="E18" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" s="48"/>
       <c r="G18" s="55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H18" s="52" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I18" s="48">
         <v>11.03</v>
@@ -4139,18 +4195,18 @@
         <v>16261043632</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D19" s="48"/>
       <c r="E19" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" s="54"/>
       <c r="G19" s="55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H19" s="52" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I19" s="48">
         <v>23.03</v>
@@ -4168,18 +4224,18 @@
         <v>62251054904</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D20" s="48"/>
       <c r="E20" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F20" s="54"/>
       <c r="G20" s="55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H20" s="52" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I20" s="48">
         <v>23.03</v>
@@ -4197,18 +4253,18 @@
         <v>10162209012</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" s="48"/>
       <c r="E21" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="48"/>
       <c r="G21" s="55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H21" s="52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I21" s="48">
         <v>23.03</v>
@@ -4226,18 +4282,18 @@
         <v>15247077586</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D22" s="48"/>
       <c r="E22" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F22" s="54"/>
       <c r="G22" s="55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H22" s="52" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I22" s="48">
         <v>23.03</v>
@@ -4255,18 +4311,18 @@
         <v>12484081840</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D23" s="48"/>
       <c r="E23" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F23" s="54"/>
       <c r="G23" s="55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H23" s="52" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I23" s="48">
         <v>23.03</v>
@@ -4284,18 +4340,18 @@
         <v>10078077392</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" s="48"/>
       <c r="E24" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F24" s="54"/>
       <c r="G24" s="55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H24" s="52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I24" s="48">
         <v>23.03</v>
@@ -4313,18 +4369,18 @@
         <v>10156079256</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" s="48"/>
       <c r="E25" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" s="54"/>
       <c r="G25" s="55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H25" s="52" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I25" s="48">
         <v>24.03</v>
@@ -4342,18 +4398,18 @@
         <v>49288319060</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" s="48"/>
       <c r="E26" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F26" s="54"/>
       <c r="G26" s="55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H26" s="52" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I26" s="48">
         <v>25.03</v>
@@ -4371,18 +4427,18 @@
         <v>19198002550</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D27" s="48"/>
       <c r="E27" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F27" s="54"/>
       <c r="G27" s="55" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H27" s="52" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I27" s="48">
         <v>26.03</v>
@@ -4400,18 +4456,18 @@
         <v>14992068672</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D28" s="48"/>
       <c r="E28" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F28" s="54"/>
       <c r="G28" s="55" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H28" s="52" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I28" s="48">
         <v>26.03</v>
@@ -4429,18 +4485,18 @@
         <v>12649536826</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D29" s="48"/>
       <c r="E29" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F29" s="54"/>
       <c r="G29" s="55" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H29" s="52" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I29" s="48">
         <v>26.03</v>
@@ -4458,18 +4514,18 @@
         <v>34123446490</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D30" s="48"/>
       <c r="E30" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F30" s="54"/>
       <c r="G30" s="55" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H30" s="52" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I30" s="48">
         <v>26.03</v>
@@ -4487,18 +4543,18 @@
         <v>11144234640</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D31" s="48"/>
       <c r="E31" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" s="54"/>
       <c r="G31" s="55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H31" s="52" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I31" s="48">
         <v>26.03</v>
@@ -4516,18 +4572,18 @@
         <v>10015118164</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D32" s="48"/>
       <c r="E32" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F32" s="54"/>
       <c r="G32" s="55" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H32" s="52" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I32" s="48">
         <v>26.03</v>
@@ -4545,18 +4601,18 @@
         <v>11482575542</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D33" s="48"/>
       <c r="E33" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F33" s="54"/>
       <c r="G33" s="55" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H33" s="52" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I33" s="48">
         <v>26.03</v>
@@ -4574,18 +4630,18 @@
         <v>11144234718</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D34" s="48"/>
       <c r="E34" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F34" s="54"/>
       <c r="G34" s="55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H34" s="52" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I34" s="48">
         <v>26.03</v>
@@ -4603,18 +4659,18 @@
         <v>10403070678</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D35" s="48"/>
       <c r="E35" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F35" s="54"/>
       <c r="G35" s="55" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H35" s="52" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I35" s="48">
         <v>26.03</v>
@@ -4632,18 +4688,18 @@
         <v>10009120968</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D36" s="48"/>
       <c r="E36" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F36" s="54"/>
       <c r="G36" s="55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H36" s="52" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I36" s="48">
         <v>26.03</v>
@@ -4661,18 +4717,18 @@
         <v>10051120268</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D37" s="48"/>
       <c r="E37" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" s="54"/>
       <c r="G37" s="55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H37" s="52" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I37" s="48">
         <v>26.03</v>
@@ -4690,18 +4746,18 @@
         <v>13507217994</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D38" s="48"/>
       <c r="E38" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F38" s="54"/>
       <c r="G38" s="55" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H38" s="52" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I38" s="48">
         <v>26.03</v>
@@ -4719,18 +4775,18 @@
         <v>12068013786</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D39" s="48"/>
       <c r="E39" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F39" s="54"/>
       <c r="G39" s="55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H39" s="52" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I39" s="48">
         <v>26.03</v>
@@ -4748,18 +4804,18 @@
         <v>14377140894</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D40" s="48"/>
       <c r="E40" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F40" s="54"/>
       <c r="G40" s="55" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H40" s="52" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I40" s="48">
         <v>26.03</v>
@@ -4777,18 +4833,18 @@
         <v>14695010084</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D41" s="48"/>
       <c r="E41" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F41" s="54"/>
       <c r="G41" s="55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H41" s="52" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I41" s="48">
         <v>26.03</v>
@@ -4806,18 +4862,18 @@
         <v>10048117608</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D42" s="48"/>
       <c r="E42" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F42" s="54"/>
       <c r="G42" s="55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H42" s="52" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I42" s="48">
         <v>31.03</v>
@@ -4835,18 +4891,18 @@
         <v>23336716810</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D43" s="48"/>
       <c r="E43" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F43" s="54"/>
       <c r="G43" s="55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" s="52" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I43" s="48">
         <v>31.03</v>
@@ -4864,18 +4920,18 @@
         <v>11734411192</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D44" s="48"/>
       <c r="E44" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F44" s="54"/>
       <c r="G44" s="55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H44" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I44" s="48">
         <v>31.03</v>
@@ -4893,18 +4949,18 @@
         <v>14449188076</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D45" s="48"/>
       <c r="E45" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F45" s="54"/>
       <c r="G45" s="55" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H45" s="52" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I45" s="48">
         <v>31.03</v>
@@ -4922,18 +4978,18 @@
         <v>11108938898</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D46" s="48"/>
       <c r="E46" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F46" s="54"/>
       <c r="G46" s="55" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H46" s="52" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I46" s="48">
         <v>31.03</v>
@@ -4951,18 +5007,18 @@
         <v>14458187930</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D47" s="48"/>
       <c r="E47" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F47" s="54"/>
       <c r="G47" s="55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H47" s="52" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I47" s="48">
         <v>31.03</v>
@@ -4980,18 +5036,18 @@
         <v>10271074204</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D48" s="48"/>
       <c r="E48" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F48" s="54"/>
       <c r="G48" s="55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H48" s="52" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I48" s="48">
         <v>31.03</v>
@@ -5009,18 +5065,18 @@
         <v>31768855328</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D49" s="48"/>
       <c r="E49" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F49" s="54"/>
       <c r="G49" s="55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H49" s="52" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I49" s="48">
         <v>31.03</v>
@@ -5038,18 +5094,18 @@
         <v>29573323330</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D50" s="48"/>
       <c r="E50" s="48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F50" s="54"/>
       <c r="G50" s="55" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H50" s="52" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I50" s="48">
         <v>31.03</v>
@@ -5067,18 +5123,18 @@
         <v>10300318804</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D51" s="48"/>
       <c r="E51" s="48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F51" s="54"/>
       <c r="G51" s="55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H51" s="52" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I51" s="48"/>
       <c r="J51" s="48"/>
@@ -5092,18 +5148,18 @@
         <v>15505896638</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D52" s="48"/>
       <c r="E52" s="48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F52" s="54"/>
       <c r="G52" s="55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H52" s="52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I52" s="48"/>
       <c r="J52" s="48"/>
@@ -5117,18 +5173,18 @@
         <v>17960854932</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D53" s="48"/>
       <c r="E53" s="48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F53" s="54"/>
       <c r="G53" s="55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H53" s="52" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I53" s="48"/>
       <c r="J53" s="48"/>
@@ -5194,18 +5250,18 @@
         <v>15865049750</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D58" s="48"/>
       <c r="E58" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F58" s="48"/>
       <c r="G58" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H58" s="52" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I58" s="48"/>
       <c r="J58" s="48"/>
@@ -5219,18 +5275,18 @@
         <v>15616146684</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D59" s="48"/>
       <c r="E59" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F59" s="48"/>
       <c r="G59" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H59" s="52" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I59" s="48">
         <v>16.02</v>
@@ -5248,18 +5304,18 @@
         <v>14300484194</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D60" s="48"/>
       <c r="E60" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F60" s="54"/>
       <c r="G60" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H60" s="52" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I60" s="48">
         <v>18.02</v>
@@ -5277,18 +5333,18 @@
         <v>29896460262</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D61" s="48"/>
       <c r="E61" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F61" s="48"/>
       <c r="G61" s="55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H61" s="52" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I61" s="48">
         <v>19.02</v>
@@ -5306,18 +5362,18 @@
         <v>17633210058</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D62" s="48"/>
       <c r="E62" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F62" s="48"/>
       <c r="G62" s="55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H62" s="52" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I62" s="48">
         <v>19.02</v>
@@ -5335,18 +5391,18 @@
         <v>10169029378</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D63" s="48"/>
       <c r="E63" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F63" s="54"/>
       <c r="G63" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H63" s="52" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I63" s="48">
         <v>19.02</v>
@@ -5364,18 +5420,18 @@
         <v>13264143598</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D64" s="48"/>
       <c r="E64" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F64" s="54"/>
       <c r="G64" s="55" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H64" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I64" s="48">
         <v>23.03</v>
@@ -5393,18 +5449,18 @@
         <v>24808561532</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D65" s="48"/>
       <c r="E65" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F65" s="54"/>
       <c r="G65" s="55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H65" s="52" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I65" s="48">
         <v>24.03</v>
@@ -5422,18 +5478,18 @@
         <v>22706535594</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D66" s="48"/>
       <c r="E66" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F66" s="54"/>
       <c r="G66" s="55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H66" s="52" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I66" s="48">
         <v>26.03</v>
@@ -5451,18 +5507,18 @@
         <v>11899063052</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D67" s="48"/>
       <c r="E67" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F67" s="54"/>
       <c r="G67" s="55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H67" s="52" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I67" s="48">
         <v>26.03</v>
@@ -5480,18 +5536,18 @@
         <v>11230082704</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D68" s="48"/>
       <c r="E68" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F68" s="54"/>
       <c r="G68" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H68" s="52" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I68" s="48">
         <v>26.03</v>
@@ -5509,18 +5565,18 @@
         <v>11407300792</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D69" s="48"/>
       <c r="E69" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F69" s="54"/>
       <c r="G69" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H69" s="52" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I69" s="48">
         <v>26.03</v>
@@ -5538,18 +5594,18 @@
         <v>11221210932</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D70" s="48"/>
       <c r="E70" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F70" s="54"/>
       <c r="G70" s="55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H70" s="52" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I70" s="48">
         <v>26.03</v>
@@ -5567,18 +5623,18 @@
         <v>13327145668</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D71" s="48"/>
       <c r="E71" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F71" s="54"/>
       <c r="G71" s="55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H71" s="52" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I71" s="48">
         <v>26.03</v>
@@ -5596,18 +5652,18 @@
         <v>15853063102</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D72" s="48"/>
       <c r="E72" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F72" s="54"/>
       <c r="G72" s="55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H72" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I72" s="48">
         <v>26.03</v>
@@ -5625,18 +5681,18 @@
         <v>12748032816</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D73" s="48"/>
       <c r="E73" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F73" s="54"/>
       <c r="G73" s="55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H73" s="52" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I73" s="48">
         <v>26.03</v>
@@ -5654,18 +5710,18 @@
         <v>38050348056</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D74" s="48"/>
       <c r="E74" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F74" s="54"/>
       <c r="G74" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H74" s="52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I74" s="48">
         <v>31.03</v>
@@ -5683,18 +5739,18 @@
         <v>11749111162</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D75" s="48"/>
       <c r="E75" s="48" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F75" s="54"/>
       <c r="G75" s="55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H75" s="52" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I75" s="48"/>
       <c r="J75" s="48"/>
@@ -5773,18 +5829,18 @@
         <v>36583309018</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D81" s="48"/>
       <c r="E81" s="48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F81" s="54"/>
       <c r="G81" s="55" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H81" s="52" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I81" s="48">
         <v>23.03</v>
@@ -5802,18 +5858,18 @@
         <v>13417007722</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D82" s="48"/>
       <c r="E82" s="48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F82" s="54"/>
       <c r="G82" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="H82" s="52" t="s">
         <v>187</v>
-      </c>
-      <c r="H82" s="52" t="s">
-        <v>188</v>
       </c>
       <c r="I82" s="48">
         <v>26.03</v>
@@ -5831,18 +5887,18 @@
         <v>16239007772</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D83" s="48"/>
       <c r="E83" s="48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F83" s="54"/>
       <c r="G83" s="55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H83" s="52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I83" s="48">
         <v>31.03</v>
@@ -5925,18 +5981,18 @@
         <v>10377141756</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D89" s="48"/>
       <c r="E89" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F89" s="54"/>
       <c r="G89" s="55" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H89" s="52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I89" s="48"/>
       <c r="J89" s="48"/>
@@ -5950,18 +6006,18 @@
         <v>11579367166</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D90" s="48"/>
       <c r="E90" s="48" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F90" s="48"/>
       <c r="G90" s="55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H90" s="52" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I90" s="48">
         <v>31.03</v>
@@ -5979,18 +6035,18 @@
         <v>12397043324</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D91" s="48"/>
       <c r="E91" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F91" s="54"/>
       <c r="G91" s="55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H91" s="52" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I91" s="48"/>
       <c r="J91" s="48"/>
@@ -6004,18 +6060,18 @@
         <v>10042245468</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D92" s="48"/>
       <c r="E92" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F92" s="48"/>
       <c r="G92" s="55" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H92" s="52" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I92" s="48"/>
       <c r="J92" s="48"/>
@@ -6029,18 +6085,18 @@
         <v>11070083640</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D93" s="48"/>
       <c r="E93" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F93" s="48"/>
       <c r="G93" s="51" t="s">
+        <v>388</v>
+      </c>
+      <c r="H93" s="52" t="s">
         <v>389</v>
-      </c>
-      <c r="H93" s="52" t="s">
-        <v>390</v>
       </c>
       <c r="I93" s="48"/>
       <c r="J93" s="48"/>
@@ -6054,18 +6110,18 @@
         <v>10027246350</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D94" s="48"/>
       <c r="E94" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F94" s="48"/>
       <c r="G94" s="51" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H94" s="52" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I94" s="48"/>
       <c r="J94" s="48"/>
@@ -6079,18 +6135,18 @@
         <v>11070083640</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D95" s="48"/>
       <c r="E95" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F95" s="48"/>
       <c r="G95" s="51" t="s">
+        <v>388</v>
+      </c>
+      <c r="H95" s="52" t="s">
         <v>389</v>
-      </c>
-      <c r="H95" s="52" t="s">
-        <v>390</v>
       </c>
       <c r="I95" s="48"/>
       <c r="J95" s="48"/>
@@ -6104,18 +6160,18 @@
         <v>10027246350</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D96" s="48"/>
       <c r="E96" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F96" s="48"/>
       <c r="G96" s="51" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H96" s="52" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I96" s="48"/>
       <c r="J96" s="48"/>
@@ -6160,43 +6216,43 @@
         <v>3</v>
       </c>
       <c r="D1" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="F1" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="G1" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="H1" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="I1" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="J1" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="K1" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="L1" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="M1" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="N1" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="O1" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="O1" s="29" t="s">
+      <c r="P1" s="29" t="s">
         <v>211</v>
-      </c>
-      <c r="P1" s="29" t="s">
-        <v>212</v>
       </c>
       <c r="Q1" s="30"/>
     </row>
@@ -6208,38 +6264,38 @@
         <v>10717552334</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D2" s="35"/>
       <c r="E2" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J2" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M2" s="33"/>
       <c r="N2" s="33"/>
       <c r="O2" s="33"/>
       <c r="P2" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q2" s="30"/>
     </row>
@@ -6249,32 +6305,32 @@
       </c>
       <c r="B3" s="31"/>
       <c r="C3" s="32" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I3" s="33"/>
       <c r="J3" s="33"/>
       <c r="K3" s="33"/>
       <c r="L3" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M3" s="33"/>
       <c r="N3" s="33"/>
       <c r="O3" s="33"/>
       <c r="P3" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q3" s="30"/>
     </row>
@@ -6284,38 +6340,38 @@
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D4" s="35"/>
       <c r="E4" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M4" s="33"/>
       <c r="N4" s="33"/>
       <c r="O4" s="33"/>
       <c r="P4" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q4" s="30"/>
     </row>
@@ -13912,7 +13968,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B1" s="68"/>
       <c r="C1" s="68"/>
@@ -13930,22 +13986,22 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D3" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>240</v>
-      </c>
       <c r="E3" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F3" s="19" t="s">
         <v>219</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -13953,11 +14009,11 @@
         <v>1</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="26">
@@ -13969,11 +14025,11 @@
         <v>2</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="26">
@@ -13985,11 +14041,11 @@
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E6" s="22"/>
       <c r="F6" s="26">
@@ -14001,12 +14057,12 @@
         <v>4</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
       <c r="E7" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F7" s="26">
         <v>46122</v>
@@ -14017,12 +14073,12 @@
         <v>5</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
       <c r="E8" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F8" s="26">
         <v>46122</v>
@@ -14033,12 +14089,12 @@
         <v>6</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
       <c r="E9" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F9" s="26">
         <v>46118</v>
@@ -14049,12 +14105,12 @@
         <v>7</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
       <c r="E10" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F10" s="26">
         <v>46118</v>
@@ -14065,12 +14121,12 @@
         <v>8</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
       <c r="E11" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F11" s="26">
         <v>46119</v>
@@ -14081,12 +14137,12 @@
         <v>9</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F12" s="26">
         <v>46118</v>
@@ -14097,12 +14153,12 @@
         <v>10</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
       <c r="E13" s="22" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F13" s="26">
         <v>46119</v>
@@ -14113,12 +14169,12 @@
         <v>11</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
       <c r="E14" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F14" s="26">
         <v>46119</v>
@@ -14129,12 +14185,12 @@
         <v>12</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
       <c r="E15" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F15" s="26">
         <v>46118</v>
@@ -14145,11 +14201,11 @@
         <v>13</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C16" s="21"/>
       <c r="D16" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="26">
@@ -14161,12 +14217,12 @@
         <v>14</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
       <c r="E17" s="22" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F17" s="26">
         <v>46118</v>
@@ -14177,12 +14233,12 @@
         <v>15</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="21"/>
       <c r="D18" s="21"/>
       <c r="E18" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F18" s="26">
         <v>46122</v>
@@ -14193,11 +14249,11 @@
         <v>16</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C19" s="21"/>
       <c r="D19" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="26">
@@ -14209,11 +14265,11 @@
         <v>17</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C20" s="21"/>
       <c r="D20" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="26">
@@ -14225,11 +14281,11 @@
         <v>18</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C21" s="21"/>
       <c r="D21" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="26">
@@ -14241,12 +14297,12 @@
         <v>19</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="22" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F22" s="26">
         <v>46118</v>
@@ -14257,11 +14313,11 @@
         <v>20</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C23" s="21"/>
       <c r="D23" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="26">
@@ -14273,11 +14329,11 @@
         <v>21</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C24" s="21"/>
       <c r="D24" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="26">
@@ -14289,11 +14345,11 @@
         <v>22</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C25" s="21"/>
       <c r="D25" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="26">
@@ -14305,11 +14361,11 @@
         <v>23</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C26" s="21"/>
       <c r="D26" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E26" s="22"/>
       <c r="F26" s="26">
@@ -14321,11 +14377,11 @@
         <v>24</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C27" s="21"/>
       <c r="D27" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="26">
@@ -14337,11 +14393,11 @@
         <v>25</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" s="21"/>
       <c r="D28" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="26">
@@ -14353,11 +14409,11 @@
         <v>26</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="26">
@@ -14369,11 +14425,11 @@
         <v>27</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" s="21"/>
       <c r="D30" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="26">
@@ -14385,11 +14441,11 @@
         <v>28</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="26">
@@ -14401,11 +14457,11 @@
         <v>29</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C32" s="21"/>
       <c r="D32" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="26">
@@ -14417,11 +14473,11 @@
         <v>30</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C33" s="21"/>
       <c r="D33" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="26">
@@ -14433,11 +14489,11 @@
         <v>31</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="26">
@@ -14449,11 +14505,11 @@
         <v>32</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="26">
@@ -14465,11 +14521,11 @@
         <v>33</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C36" s="21"/>
       <c r="D36" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="26">
@@ -14481,11 +14537,11 @@
         <v>34</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C37" s="21"/>
       <c r="D37" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="26">
@@ -14497,11 +14553,11 @@
         <v>35</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C38" s="21"/>
       <c r="D38" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="26">
@@ -14516,7 +14572,7 @@
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
       <c r="E39" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F39" s="26"/>
     </row>
@@ -14528,7 +14584,7 @@
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
       <c r="E40" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F40" s="26"/>
     </row>
@@ -14540,7 +14596,7 @@
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F41" s="26"/>
     </row>
@@ -14552,7 +14608,7 @@
       <c r="C42" s="21"/>
       <c r="D42" s="21"/>
       <c r="E42" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F42" s="26"/>
     </row>
@@ -14564,7 +14620,7 @@
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
       <c r="E43" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F43" s="26"/>
     </row>
@@ -14576,7 +14632,7 @@
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
       <c r="E44" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F44" s="26"/>
     </row>
@@ -14588,7 +14644,7 @@
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
       <c r="E45" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F45" s="26"/>
     </row>
@@ -14600,7 +14656,7 @@
       <c r="C46" s="23"/>
       <c r="D46" s="23"/>
       <c r="E46" s="24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F46" s="25">
         <v>213</v>

--- a/excel/ogrenciler.xlsx
+++ b/excel/ogrenciler.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4941868A-49C9-47FC-BCC2-95123C5B0220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E-SINAV " sheetId="182" r:id="rId1"/>

--- a/excel/ogrenciler.xlsx
+++ b/excel/ogrenciler.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4941868A-49C9-47FC-BCC2-95123C5B0220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E-SINAV " sheetId="182" r:id="rId1"/>

--- a/excel/ogrenciler.xlsx
+++ b/excel/ogrenciler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esad\surucu-kursu-app\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4941868A-49C9-47FC-BCC2-95123C5B0220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FCFB3A-D6ED-4569-8A93-28560CFA4374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="394">
   <si>
     <t>E-SINAV</t>
   </si>
@@ -14568,24 +14568,28 @@
       <c r="A39" s="20">
         <v>36</v>
       </c>
-      <c r="B39" s="21"/>
+      <c r="B39" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="22" t="s">
-        <v>236</v>
-      </c>
+      <c r="D39" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="E39" s="22"/>
       <c r="F39" s="26"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="20">
         <v>37</v>
       </c>
-      <c r="B40" s="21"/>
+      <c r="B40" s="21" t="s">
+        <v>183</v>
+      </c>
       <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="22" t="s">
-        <v>236</v>
-      </c>
+      <c r="D40" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="E40" s="22"/>
       <c r="F40" s="26"/>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -14595,9 +14599,7 @@
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
-      <c r="E41" s="22" t="s">
-        <v>236</v>
-      </c>
+      <c r="E41" s="22"/>
       <c r="F41" s="26"/>
     </row>
     <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">

--- a/excel/ogrenciler.xlsx
+++ b/excel/ogrenciler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esad\surucu-kursu-app\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FCFB3A-D6ED-4569-8A93-28560CFA4374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867288EE-C3EC-4FA2-90A7-592A04E431C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="997" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14576,7 +14576,9 @@
         <v>220</v>
       </c>
       <c r="E39" s="22"/>
-      <c r="F39" s="26"/>
+      <c r="F39" s="26">
+        <v>46122</v>
+      </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="20">
@@ -14590,7 +14592,9 @@
         <v>220</v>
       </c>
       <c r="E40" s="22"/>
-      <c r="F40" s="26"/>
+      <c r="F40" s="26">
+        <v>46122</v>
+      </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="20">
